--- a/Fishing Sim Encylopedia.xlsx
+++ b/Fishing Sim Encylopedia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\xampp\htdocs\fishing-sim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp74\htdocs\fishing-sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F94512B3-AA0C-480D-AD16-9378E181CB6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13600B3A-A1D6-46AC-A553-B2CF43075A5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" activeTab="5" xr2:uid="{9977F37B-D2C6-4802-9F43-18753E2C43C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{9977F37B-D2C6-4802-9F43-18753E2C43C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Glossary" sheetId="4" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1903" uniqueCount="852">
   <si>
     <t>Name</t>
   </si>
@@ -1913,9 +1913,6 @@
     <t>Kaca Lake, Seribu Arus River, Mentari Pond, Seroja Marsh, Seroja Darah Swamp</t>
   </si>
   <si>
-    <t>Saint Luke Pond, Merman Marsh, Wisp Swamp, Sofia River</t>
-  </si>
-  <si>
     <t>Evrys River, Iremia River, Sofia River, Seribu Arus River, Ormr River, Freyja River</t>
   </si>
   <si>
@@ -2072,12 +2069,6 @@
     <t>A mutated archerfish with scales as hard as a rock to prevent predators from eating them.</t>
   </si>
   <si>
-    <t>An archerfish that shoots hot water to hunt, its mutation make them able to boil the water inside its mouth.</t>
-  </si>
-  <si>
-    <t>Horned Archerfish used its horn to defend themselves and as a way to attract the female</t>
-  </si>
-  <si>
     <t>Its fin mutated to have a razor-sharp claw to penetrate the mouth of a fish unfortunate enough to eat it.</t>
   </si>
   <si>
@@ -2087,9 +2078,6 @@
     <t>Bream that hunt at night, using their faint glow to attract smaller fish to come closer.</t>
   </si>
   <si>
-    <t>A mucus-covered bream makes its body sleek and slippery; it has a foul taste prevent predators from eating it.</t>
-  </si>
-  <si>
     <t>Helmet Catfish</t>
   </si>
   <si>
@@ -2111,9 +2099,6 @@
     <t>Venomous Catfish</t>
   </si>
   <si>
-    <t>This catfish has a red eye that makes it able to see in the night very well.</t>
-  </si>
-  <si>
     <t>Draconic Traits</t>
   </si>
   <si>
@@ -2189,15 +2174,9 @@
     <t>Giant Orange Chromide</t>
   </si>
   <si>
-    <t>This fish became so big because of mana circulating through its body, it become carnivorous too.</t>
-  </si>
-  <si>
     <t>Scaly Tilapia</t>
   </si>
   <si>
-    <t>This fish evolves to have harder scales, the scales are shining under the sunlight.</t>
-  </si>
-  <si>
     <t>Hookfin Tilapia</t>
   </si>
   <si>
@@ -2231,9 +2210,6 @@
     <t>Lightning-eyes Fish</t>
   </si>
   <si>
-    <t>This fish swam so fast, it was almost impossible to see it when it was moving; it only stopped when it was eating.</t>
-  </si>
-  <si>
     <t>Its skin have a tiny needles on its skin, whenever something or someone even touches it, it will inject a deadly toxin that clogs the blood.</t>
   </si>
   <si>
@@ -2246,9 +2222,6 @@
     <t>Sawtoothed Mudskipper</t>
   </si>
   <si>
-    <t>This mudskipper use it tooth to saw into the roots of a tree near the water,</t>
-  </si>
-  <si>
     <t>Flaming Goby</t>
   </si>
   <si>
@@ -2261,9 +2234,6 @@
     <t>9.2</t>
   </si>
   <si>
-    <t>The behaviour of this fish becomes so erratic because of its enhanced sense of territorial boundaries.</t>
-  </si>
-  <si>
     <t>Soldier Goby</t>
   </si>
   <si>
@@ -2285,13 +2255,376 @@
     <t>The skin of this goby is covered with a potent poison, one of the deadliest toxins among freshwater fish</t>
   </si>
   <si>
-    <t>This goby can raise its body temperature enough to scald nearby predators.</t>
-  </si>
-  <si>
     <t>The extra pair of eyes made this fish have 360° eyesight. Its expanded field of vision allows it to detect predators and prey from almost any direction.</t>
   </si>
   <si>
     <t>Its scales become as hard as a rock, a hammer sometime need to be used to even descale it.</t>
+  </si>
+  <si>
+    <t>Poison-ring Goby</t>
+  </si>
+  <si>
+    <t>Antler Goby</t>
+  </si>
+  <si>
+    <t>It has a large horn resembling a deer antler in front of its head, used to dig a hole and ram a predator that got too close.</t>
+  </si>
+  <si>
+    <t>Mugwort Goby</t>
+  </si>
+  <si>
+    <t>Gleaming Goby</t>
+  </si>
+  <si>
+    <t>This white colored goby is an aggressive goby that will attack anything that it thinks would pose a threat to its territory.</t>
+  </si>
+  <si>
+    <t>8.3</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>67.5</t>
+  </si>
+  <si>
+    <t>Spear-jaw Halfbeak</t>
+  </si>
+  <si>
+    <t>Its lower jaw evolved to become as sharp as a spear. It kills its prey by swimming really fast and impaling them, then slowly eating the prey when it is stuck on its jaw.</t>
+  </si>
+  <si>
+    <t>Charred Halfbeak</t>
+  </si>
+  <si>
+    <t>Mana contamination is slowly making its body decay from within. The charred flesh began to peel from its body and detach; it instinctively fed on its own rotting flesh, delaying its inevitable death.</t>
+  </si>
+  <si>
+    <t>Butterfish</t>
+  </si>
+  <si>
+    <t>Cheesefish</t>
+  </si>
+  <si>
+    <t>The flesh of this fish emits a pungent odor resembling aged cheese. The smell attracts smaller school fish, providing it with an endless supply of prey, but the downside, it also draws a bigger predator to its location.</t>
+  </si>
+  <si>
+    <t>A highly prized fish among the nobles of Rosegleam, this fish is believed to ease chronic pain and restore vitality. While some nobles reported positive changes in their body, the long-term effects remain poorly understood, as few people can even afford to eat it.</t>
+  </si>
+  <si>
+    <t>Hog Moony</t>
+  </si>
+  <si>
+    <t>Steamgill Moony</t>
+  </si>
+  <si>
+    <t>A schooling fish that releases a hot steam out of their gill to deter predators that come close to it. When the predator gets confused, it will bolt out and escape.</t>
+  </si>
+  <si>
+    <t>Radiance Moony</t>
+  </si>
+  <si>
+    <t>The mana inside this fish makes its scent sensory go into overdrive; it can no longer detect prey or predator, and they will attack anything that they can smell.</t>
+  </si>
+  <si>
+    <t>Bladedfin Moony</t>
+  </si>
+  <si>
+    <t>Its fin evolves into a sharp blade like a knife. This fish surrounds its prey and slowly slashes them, and eats the chunks that fly out.</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>Fireblood Mullet</t>
+  </si>
+  <si>
+    <t>Paunch Mullet</t>
+  </si>
+  <si>
+    <t>Its brain has been manipulated so much by mana that it can't feel full anymore, it will keep eating until its belly bursts.</t>
+  </si>
+  <si>
+    <t>Rapierfish</t>
+  </si>
+  <si>
+    <t>Leaping Needlefish</t>
+  </si>
+  <si>
+    <t>This fish has a behaviour of jumping into the air to hunt small birds that get too close to the surface of the water. Because of this, fishermen sometimes get hurt because of their sharp fin.</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>Giant Mangrove Jack</t>
+  </si>
+  <si>
+    <t>Megamouth Jack</t>
+  </si>
+  <si>
+    <t>This fish evolved to eat almost nothing but plankton, but they occasionally eat smaller fish that got suck by their mouth too.</t>
+  </si>
+  <si>
+    <t>Whiptail Bream</t>
+  </si>
+  <si>
+    <t>Bronze-skin Bream</t>
+  </si>
+  <si>
+    <t>Its skin becomes hard as bronze; some smiths even use it as an alternative to real bronze. But, this fish skin is thinner than bronze, making the tools that use the skin easier to break.</t>
+  </si>
+  <si>
+    <t>An archerfish that shoots hot water to hunt, mana allows it to superheat the water inside its mouth before shooting it.</t>
+  </si>
+  <si>
+    <t>Horned Archerfish uses its horn to defend itself and as a way to attract the female</t>
+  </si>
+  <si>
+    <t>A mucus-covered bream makes its body sleek and slippery; it has a foul taste that discourage predators from eating it.</t>
+  </si>
+  <si>
+    <t>This catfish has a red eye that enables it to see exceptionally well in a low-light area.</t>
+  </si>
+  <si>
+    <t>This fish became so big because of mana circulating through its body; it has also become carnivorous.</t>
+  </si>
+  <si>
+    <t>This fish evolves to have harder scales; its hardened scales protect it from larger predators while also reflecting sunlight with a metallic sheen.</t>
+  </si>
+  <si>
+    <t>This fish swam so fast, its explosive burst of speed makes it nearly impossible to follow with the naked eye.</t>
+  </si>
+  <si>
+    <t>The territorial behaviour of this fish became so intense that it will relentlessly patrol and defend their territory no matter how big the predators are.</t>
+  </si>
+  <si>
+    <t>At first glance, this goby doesn't seem dangerous, but it has one of the deadliest poisons surrounding the body.</t>
+  </si>
+  <si>
+    <t>The flesh of this fish has been altered by mana, making it unusually rich and buttery. Despite its tender meat, its behavior is nothing but aggressive; it will attack anything that even comes too close to its territory.</t>
+  </si>
+  <si>
+    <t>This fish can generate light by manipulating mana inside of them when they feel threatened and hunting. They will surround their prey and then eat them when paralyzed.</t>
+  </si>
+  <si>
+    <t>The blood inside this fish is warmer than the surrounding water, which enables it to move even in a colder environment without any troubles.</t>
+  </si>
+  <si>
+    <t>The tail elongated into a whip-like appendage that provided excellent maneuverability, allowing it to make a sudden change in its trajectory while chasing prey or escaping from predators.</t>
+  </si>
+  <si>
+    <t>The jaw of this fish has evolved into a sharp point when their mouth closes, usually used by them to fight predators and their own kind for territory.</t>
+  </si>
+  <si>
+    <t>Clear Bream</t>
+  </si>
+  <si>
+    <t>Mana exposure causes this fish to grow bigger and bigger; the more condensed the mana around their habitat, the bigger it gets.</t>
+  </si>
+  <si>
+    <t>Rock-body Bream</t>
+  </si>
+  <si>
+    <t>Mana inside its body makes this fish's body hard as a rock; not only that, their body also weighs as heavy as a rock, which makes the fish almost incapable of swimming for too long.</t>
+  </si>
+  <si>
+    <t>Trance Bream</t>
+  </si>
+  <si>
+    <t>Chirping Bream</t>
+  </si>
+  <si>
+    <t>This mudskipper use it tooth to saw into the roots of a tree near the water, eating the root bit by bit.</t>
+  </si>
+  <si>
+    <t>This goby can raise its body temperature enough to scald nearby predators that dare to bite it.</t>
+  </si>
+  <si>
+    <t>Fishermen claim that at night, Nøkken will make a chirping sound to lure them into deeper water, until one day a scholar catches a fish that continues to chirp even when out of the water.</t>
+  </si>
+  <si>
+    <t>Sharkfin Bream</t>
+  </si>
+  <si>
+    <t>The dorsal fin of this bream becomes hard, almost like a shark fin, making it excel at sudden turn when swimming from predators.</t>
+  </si>
+  <si>
+    <t>Icy Blue Bream</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>This carp can open its mouth so wide that it almost eats almost all its prey whole. Because of this, its mouth sometimes gets ripped from overextension.</t>
+  </si>
+  <si>
+    <t>Widemouth Carp</t>
+  </si>
+  <si>
+    <t>45.5</t>
+  </si>
+  <si>
+    <t>42.5</t>
+  </si>
+  <si>
+    <t>Glowing Heart Carp</t>
+  </si>
+  <si>
+    <t>Mana circulation made this carp's heart glow, it makes hunting at night easier and harder to escaping the predators.</t>
+  </si>
+  <si>
+    <t>Hairy Grass Carp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hair like thorns covered this carp's body, which helped the carp to camouflage itself between the grass or algae below the water. </t>
+  </si>
+  <si>
+    <t>Glassbone Carp</t>
+  </si>
+  <si>
+    <t>The bone in this carp is so brittle that even the lightest drop will break all of its bones. It makes this carp swim so slowly and become more passive.</t>
+  </si>
+  <si>
+    <t>The mana circulating in its body makes the body of this bream nearly transparent, making it hard for predators and even potential mates to see each other.</t>
+  </si>
+  <si>
+    <t>Exposure to mana makes this fish unable to swim sometimes, and the older it gets, the weirder its behavior. Some fishermen even claim that they saw some fish come to the surface and remain motionless for hours.</t>
+  </si>
+  <si>
+    <t>Mentari Pond, Seribu Arus River, Saint Luke Pond, Merman Marsh, Wisp Swamp, Sofia River</t>
+  </si>
+  <si>
+    <t>Stone Carp</t>
+  </si>
+  <si>
+    <t>Jumping Mud Carp</t>
+  </si>
+  <si>
+    <t>Arrow Carp</t>
+  </si>
+  <si>
+    <t>Fanged Carp</t>
+  </si>
+  <si>
+    <t>Its mouth is covered with a lot of sharp teeth, and it can even chew through the wood of the boat that fishermen use.</t>
+  </si>
+  <si>
+    <t>Twin Horned Carp</t>
+  </si>
+  <si>
+    <t>Sailtail Carp</t>
+  </si>
+  <si>
+    <t>The dorsal fin grows until the end of its tail. This sail-like dorsal fin is used to make a barrier when it circles the fish.</t>
+  </si>
+  <si>
+    <t>This fish has a lower body temperature than other fish, making it sluggish in colder water; even in warmer water, it will move slowly.</t>
+  </si>
+  <si>
+    <t>Obsidian Carp</t>
+  </si>
+  <si>
+    <t>Overgrown Carp</t>
+  </si>
+  <si>
+    <t>Humphead Carp</t>
+  </si>
+  <si>
+    <t>Insatiable Carp</t>
+  </si>
+  <si>
+    <t>Monstrous Carp</t>
+  </si>
+  <si>
+    <t>A tale in a nearby village tells a story of boogeymen snatching and gobbling up children whenever they go to murky water. Some scholars suggested that maybe this fish is the one responsible for the missing children.</t>
+  </si>
+  <si>
+    <t>Dwarf Carp</t>
+  </si>
+  <si>
+    <t>Rat Carp</t>
+  </si>
+  <si>
+    <t>This fish got its name for its reproductive capability; the mana circulation makes this fish have a high sexual reproductivity and keeps reproducing.</t>
+  </si>
+  <si>
+    <t>Scarred Carp</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Gillless Carp</t>
+  </si>
+  <si>
+    <t>Scholars can't seem to agree about how this fish even breathes; some suggest that maybe it breathes through its mouth, while others argue that maybe it uses their skin to breathe.</t>
+  </si>
+  <si>
+    <t>This voracious fish will eat anything that they can, whether it is fish, shellfish, or even an insect that has drowned until its die.</t>
+  </si>
+  <si>
+    <t>Snow Carp</t>
+  </si>
+  <si>
+    <t>Serpentine Catfish</t>
+  </si>
+  <si>
+    <t>Thunder Catfish</t>
+  </si>
+  <si>
+    <t>The head of this fish becomes so big that it will block its eyes, and the inside of the hump is filled with mucus and water.</t>
+  </si>
+  <si>
+    <t>Bone Plate Catfish</t>
+  </si>
+  <si>
+    <t>Bone plates occasionally grow on its body, protecting it from predator attack. This bone can be fetched for a high price, mostly used for a shield by a smith.</t>
+  </si>
+  <si>
+    <t>Hunter Catfish</t>
+  </si>
+  <si>
+    <t>This catfish is infamous for its persistent of chasing its prey. Fishermen claim that this catfish will chase its prey even after its prey has already been brought to the boat.</t>
+  </si>
+  <si>
+    <t>The fins have been reinforced by mana, allowing this carp to support its entire body out of the water and move from one body of water to another.</t>
+  </si>
+  <si>
+    <t>This carp leaps out of the water whenever it gets startled, the mana inside its body making it hyper aware.</t>
+  </si>
+  <si>
+    <t>Scholars speculate that this type of mana-evolve carp will not stop growing as long as it keeps eating. No specimen has ever shown signs of maturity.</t>
+  </si>
+  <si>
+    <t>Its skin glows magnificently under the moonlight, and when underwater, this fish is nearly invisible beneath the moonlit surface, making it a great predator.</t>
+  </si>
+  <si>
+    <t>The pattern on its body is a sign of mana constantly escape though its body; the excessive mana inside its body prevent its to swim.</t>
+  </si>
+  <si>
+    <t>This carp gets really active when the temperature gets low enough to have snow; when the temperature gets high, it usually stops hunting and becomes almost dormant.</t>
+  </si>
+  <si>
+    <t>Its serpentine-like body sometime get mistaken for a river serpent; It even behaves like one, swallowing its prey whole, even if the fish is big.</t>
+  </si>
+  <si>
+    <t>The food that gets inside this fish becomes fuel for the mana reservoir rather than its body, making its body smaller over time.</t>
+  </si>
+  <si>
+    <t>Scholars believe this catfish can shock their prey using a specialized organ that stores mana and releases that mana as a thunderbolt-like jolt. But, after dissection, no such organ has been identified to have that kind of function.</t>
+  </si>
+  <si>
+    <t>Scholars are still unsure how the fish covers itself and rolls into a ball during droughts, and some even suggest that the carp uses mana to cover itself.</t>
+  </si>
+  <si>
+    <t>Its streamlined body has evolved into something akin to an arrow, allowing it to swim so fast, even against a strong current.</t>
   </si>
 </sst>
 </file>
@@ -2463,9 +2796,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2503,7 +2836,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2609,7 +2942,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2751,7 +3084,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2761,20 +3094,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5724260D-1473-4B2E-8F80-948837984D02}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" style="7"/>
-    <col min="3" max="3" width="15.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="7"/>
+    <col min="1" max="1" width="48.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="7"/>
+    <col min="3" max="3" width="15.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>39</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,7 +3118,7 @@
         <v>66</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,7 +3126,7 @@
         <v>67</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,7 +3134,7 @@
         <v>68</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2809,7 +3142,7 @@
         <v>69</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2822,7 +3155,7 @@
         <v>71</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2835,7 +3168,7 @@
         <v>73</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2843,7 +3176,7 @@
         <v>74</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2851,7 +3184,7 @@
         <v>57</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,7 +3192,7 @@
         <v>75</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2872,7 +3205,7 @@
         <v>77</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -2883,21 +3216,21 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="9"/>
       <c r="C17" s="7" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>79</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8"/>
       <c r="C19" s="7" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2905,7 +3238,7 @@
         <v>80</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2918,7 +3251,7 @@
         <v>82</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2931,7 +3264,7 @@
         <v>84</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2939,64 +3272,64 @@
         <v>85</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="9"/>
       <c r="C26" s="7" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="8"/>
     </row>
-    <row r="29" spans="1:3" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="13.9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>95</v>
       </c>
@@ -3010,18 +3343,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80E2325F-7566-4EAC-9652-45A711BDD2B5}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" style="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="7"/>
+    <col min="5" max="5" width="11.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>230</v>
       </c>
@@ -3041,7 +3374,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>229</v>
       </c>
@@ -3061,7 +3394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>235</v>
       </c>
@@ -3081,7 +3414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>236</v>
       </c>
@@ -3101,7 +3434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>237</v>
       </c>
@@ -3121,7 +3454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>238</v>
       </c>
@@ -3141,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>239</v>
       </c>
@@ -3170,13 +3503,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE740DA-B477-45BF-81B5-E0EFA8CDE1AC}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D44"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="44.5703125" style="11" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="7"/>
+    <col min="1" max="1" width="20.88671875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="44.5546875" style="11" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -3193,7 +3526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>444</v>
       </c>
@@ -3207,7 +3540,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>446</v>
       </c>
@@ -3221,7 +3554,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="22" t="s">
         <v>491</v>
       </c>
@@ -3235,7 +3568,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="22" t="s">
         <v>447</v>
       </c>
@@ -3249,7 +3582,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A6" s="22" t="s">
         <v>460</v>
       </c>
@@ -3263,7 +3596,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="22" t="s">
         <v>462</v>
       </c>
@@ -3277,7 +3610,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>463</v>
       </c>
@@ -3291,7 +3624,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>464</v>
       </c>
@@ -3305,7 +3638,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>489</v>
       </c>
@@ -3319,7 +3652,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>454</v>
       </c>
@@ -3333,7 +3666,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>449</v>
       </c>
@@ -3347,7 +3680,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>448</v>
       </c>
@@ -3361,7 +3694,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>453</v>
       </c>
@@ -3375,7 +3708,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>466</v>
       </c>
@@ -3389,7 +3722,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>467</v>
       </c>
@@ -3403,7 +3736,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>450</v>
       </c>
@@ -3417,7 +3750,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>451</v>
       </c>
@@ -3431,7 +3764,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>469</v>
       </c>
@@ -3445,7 +3778,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>452</v>
       </c>
@@ -3459,7 +3792,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>470</v>
       </c>
@@ -3473,7 +3806,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>456</v>
       </c>
@@ -3487,7 +3820,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
         <v>455</v>
       </c>
@@ -3501,7 +3834,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>488</v>
       </c>
@@ -3515,7 +3848,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>472</v>
       </c>
@@ -3529,7 +3862,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>473</v>
       </c>
@@ -3543,7 +3876,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>6</v>
       </c>
@@ -3557,7 +3890,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>474</v>
       </c>
@@ -3571,7 +3904,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>475</v>
       </c>
@@ -3585,7 +3918,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>476</v>
       </c>
@@ -3613,7 +3946,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>481</v>
       </c>
@@ -3627,7 +3960,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>480</v>
       </c>
@@ -3641,7 +3974,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>479</v>
       </c>
@@ -3655,7 +3988,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
         <v>482</v>
       </c>
@@ -3669,7 +4002,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
         <v>483</v>
       </c>
@@ -3683,7 +4016,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
         <v>3</v>
       </c>
@@ -3697,7 +4030,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
         <v>5</v>
       </c>
@@ -3711,7 +4044,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>458</v>
       </c>
@@ -3725,7 +4058,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>457</v>
       </c>
@@ -3739,7 +4072,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>445</v>
       </c>
@@ -3753,7 +4086,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>485</v>
       </c>
@@ -3767,7 +4100,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>486</v>
       </c>
@@ -3781,7 +4114,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
         <v>487</v>
       </c>
@@ -3806,12 +4139,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE2F214-A82C-481F-A2D1-0726174E9268}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="46" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="8.85546875" style="7"/>
+    <col min="4" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -3825,7 +4158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>536</v>
       </c>
@@ -3836,7 +4169,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>570</v>
       </c>
@@ -3847,7 +4180,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>537</v>
       </c>
@@ -3858,7 +4191,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>538</v>
       </c>
@@ -3869,7 +4202,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>571</v>
       </c>
@@ -3880,7 +4213,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>572</v>
       </c>
@@ -3891,7 +4224,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>539</v>
       </c>
@@ -3902,7 +4235,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>540</v>
       </c>
@@ -3913,7 +4246,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>541</v>
       </c>
@@ -3924,7 +4257,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>542</v>
       </c>
@@ -3935,7 +4268,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>544</v>
       </c>
@@ -3946,7 +4279,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>543</v>
       </c>
@@ -3957,7 +4290,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>545</v>
       </c>
@@ -3968,7 +4301,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>546</v>
       </c>
@@ -3979,7 +4312,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>547</v>
       </c>
@@ -3990,7 +4323,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>548</v>
       </c>
@@ -4001,7 +4334,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>552</v>
       </c>
@@ -4012,7 +4345,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>554</v>
       </c>
@@ -4032,24 +4365,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72DDB04-9343-4C49-91F5-9D2C45772DD9}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:M102"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="17" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" style="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="69.140625" style="18" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="3"/>
+    <col min="10" max="10" width="44.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="69.109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -4090,7 +4423,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>343</v>
       </c>
@@ -4131,7 +4464,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
         <v>341</v>
       </c>
@@ -4172,7 +4505,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
         <v>174</v>
       </c>
@@ -4213,7 +4546,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
         <v>182</v>
       </c>
@@ -4254,7 +4587,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
         <v>258</v>
       </c>
@@ -4295,7 +4628,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>262</v>
       </c>
@@ -4336,7 +4669,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>289</v>
       </c>
@@ -4377,7 +4710,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>293</v>
       </c>
@@ -4418,7 +4751,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>349</v>
       </c>
@@ -4459,7 +4792,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>351</v>
       </c>
@@ -4500,7 +4833,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>356</v>
       </c>
@@ -4541,7 +4874,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>360</v>
       </c>
@@ -4582,7 +4915,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>271</v>
       </c>
@@ -4623,7 +4956,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>287</v>
       </c>
@@ -4664,7 +4997,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>285</v>
       </c>
@@ -4705,7 +5038,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>344</v>
       </c>
@@ -4740,13 +5073,13 @@
         <v>345</v>
       </c>
       <c r="L17" s="18" t="s">
-        <v>58</v>
+        <v>259</v>
       </c>
       <c r="M17" s="18" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>347</v>
       </c>
@@ -4787,7 +5120,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>421</v>
       </c>
@@ -4828,7 +5161,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>410</v>
       </c>
@@ -4869,7 +5202,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>279</v>
       </c>
@@ -4910,7 +5243,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
         <v>283</v>
       </c>
@@ -4951,7 +5284,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>418</v>
       </c>
@@ -4992,7 +5325,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>363</v>
       </c>
@@ -5033,7 +5366,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>412</v>
       </c>
@@ -5074,7 +5407,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>33</v>
       </c>
@@ -5115,7 +5448,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>172</v>
       </c>
@@ -5141,7 +5474,7 @@
         <v>5</v>
       </c>
       <c r="I27" s="17">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J27" s="18" t="s">
         <v>173</v>
@@ -5153,10 +5486,10 @@
         <v>63</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>189</v>
       </c>
@@ -5194,10 +5527,10 @@
         <v>61</v>
       </c>
       <c r="M28" s="18" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>187</v>
       </c>
@@ -5235,10 +5568,10 @@
         <v>56</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="69" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>13</v>
       </c>
@@ -5276,10 +5609,10 @@
         <v>56</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>147</v>
       </c>
@@ -5320,7 +5653,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A32" s="16" t="s">
         <v>153</v>
       </c>
@@ -5352,16 +5685,16 @@
         <v>154</v>
       </c>
       <c r="K32" s="18" t="s">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>59</v>
+        <v>358</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>19</v>
       </c>
@@ -5402,7 +5735,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>16</v>
       </c>
@@ -5440,10 +5773,10 @@
         <v>59</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>149</v>
       </c>
@@ -5481,10 +5814,10 @@
         <v>250</v>
       </c>
       <c r="M35" s="18" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>151</v>
       </c>
@@ -5522,10 +5855,10 @@
         <v>249</v>
       </c>
       <c r="M36" s="18" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>334</v>
       </c>
@@ -5566,7 +5899,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A38" s="16" t="s">
         <v>156</v>
       </c>
@@ -5604,10 +5937,10 @@
         <v>56</v>
       </c>
       <c r="M38" s="18" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A39" s="16" t="s">
         <v>158</v>
       </c>
@@ -5645,10 +5978,10 @@
         <v>160</v>
       </c>
       <c r="M39" s="18" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>225</v>
       </c>
@@ -5686,10 +6019,10 @@
         <v>427</v>
       </c>
       <c r="M40" s="18" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>252</v>
       </c>
@@ -5730,7 +6063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>228</v>
       </c>
@@ -5768,10 +6101,10 @@
         <v>60</v>
       </c>
       <c r="M42" s="18" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>245</v>
       </c>
@@ -5809,10 +6142,10 @@
         <v>63</v>
       </c>
       <c r="M43" s="18" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>247</v>
       </c>
@@ -5850,10 +6183,10 @@
         <v>250</v>
       </c>
       <c r="M44" s="18" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>255</v>
       </c>
@@ -5891,10 +6224,10 @@
         <v>60</v>
       </c>
       <c r="M45" s="18" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
         <v>280</v>
       </c>
@@ -5932,10 +6265,10 @@
         <v>63</v>
       </c>
       <c r="M46" s="18" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
         <v>395</v>
       </c>
@@ -5973,10 +6306,10 @@
         <v>388</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
         <v>399</v>
       </c>
@@ -6014,10 +6347,10 @@
         <v>160</v>
       </c>
       <c r="M48" s="18" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
         <v>402</v>
       </c>
@@ -6055,10 +6388,10 @@
         <v>56</v>
       </c>
       <c r="M49" s="18" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A50" s="16" t="s">
         <v>405</v>
       </c>
@@ -6096,10 +6429,10 @@
         <v>358</v>
       </c>
       <c r="M50" s="18" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A51" s="16" t="s">
         <v>407</v>
       </c>
@@ -6137,10 +6470,10 @@
         <v>297</v>
       </c>
       <c r="M51" s="18" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A52" s="16" t="s">
         <v>384</v>
       </c>
@@ -6178,10 +6511,10 @@
         <v>253</v>
       </c>
       <c r="M52" s="18" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A53" s="16" t="s">
         <v>387</v>
       </c>
@@ -6219,10 +6552,10 @@
         <v>388</v>
       </c>
       <c r="M53" s="18" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A54" s="16" t="s">
         <v>390</v>
       </c>
@@ -6260,10 +6593,10 @@
         <v>58</v>
       </c>
       <c r="M54" s="18" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A55" s="16" t="s">
         <v>392</v>
       </c>
@@ -6301,10 +6634,10 @@
         <v>393</v>
       </c>
       <c r="M55" s="18" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A56" s="16" t="s">
         <v>36</v>
       </c>
@@ -6339,13 +6672,13 @@
         <v>54</v>
       </c>
       <c r="L56" s="18" t="s">
+        <v>624</v>
+      </c>
+      <c r="M56" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="M56" s="18" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A57" s="16" t="s">
         <v>198</v>
       </c>
@@ -6383,10 +6716,10 @@
         <v>63</v>
       </c>
       <c r="M57" s="18" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A58" s="16" t="s">
         <v>204</v>
       </c>
@@ -6424,10 +6757,10 @@
         <v>63</v>
       </c>
       <c r="M58" s="18" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A59" s="16" t="s">
         <v>223</v>
       </c>
@@ -6468,7 +6801,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A60" s="16" t="s">
         <v>201</v>
       </c>
@@ -6506,10 +6839,10 @@
         <v>56</v>
       </c>
       <c r="M60" s="18" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A61" s="16" t="s">
         <v>208</v>
       </c>
@@ -6547,10 +6880,10 @@
         <v>62</v>
       </c>
       <c r="M61" s="18" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A62" s="19" t="s">
         <v>211</v>
       </c>
@@ -6588,10 +6921,10 @@
         <v>213</v>
       </c>
       <c r="M62" s="18" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
         <v>215</v>
       </c>
@@ -6629,10 +6962,10 @@
         <v>63</v>
       </c>
       <c r="M63" s="18" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A64" s="16" t="s">
         <v>217</v>
       </c>
@@ -6670,10 +7003,10 @@
         <v>56</v>
       </c>
       <c r="M64" s="18" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A65" s="16" t="s">
         <v>221</v>
       </c>
@@ -6711,10 +7044,10 @@
         <v>56</v>
       </c>
       <c r="M65" s="18" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A66" s="16" t="s">
         <v>26</v>
       </c>
@@ -6752,10 +7085,10 @@
         <v>367</v>
       </c>
       <c r="M66" s="18" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A67" s="16" t="s">
         <v>335</v>
       </c>
@@ -6793,10 +7126,10 @@
         <v>63</v>
       </c>
       <c r="M67" s="18" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A68" s="16" t="s">
         <v>168</v>
       </c>
@@ -6831,13 +7164,13 @@
         <v>64</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="M68" s="18" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A69" s="16" t="s">
         <v>30</v>
       </c>
@@ -6878,7 +7211,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A70" s="16" t="s">
         <v>332</v>
       </c>
@@ -6919,7 +7252,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="16" t="s">
         <v>163</v>
       </c>
@@ -6960,7 +7293,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A72" s="16" t="s">
         <v>22</v>
       </c>
@@ -6998,10 +7331,10 @@
         <v>56</v>
       </c>
       <c r="M72" s="18" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A73" s="16" t="s">
         <v>161</v>
       </c>
@@ -7039,10 +7372,10 @@
         <v>250</v>
       </c>
       <c r="M73" s="18" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A74" s="16" t="s">
         <v>336</v>
       </c>
@@ -7080,10 +7413,10 @@
         <v>250</v>
       </c>
       <c r="M74" s="18" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A75" s="16" t="s">
         <v>164</v>
       </c>
@@ -7121,10 +7454,10 @@
         <v>160</v>
       </c>
       <c r="M75" s="18" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A76" s="16" t="s">
         <v>296</v>
       </c>
@@ -7165,7 +7498,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A77" s="16" t="s">
         <v>313</v>
       </c>
@@ -7206,7 +7539,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A78" s="16" t="s">
         <v>365</v>
       </c>
@@ -7247,7 +7580,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A79" s="16" t="s">
         <v>316</v>
       </c>
@@ -7288,7 +7621,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A80" s="16" t="s">
         <v>380</v>
       </c>
@@ -7329,7 +7662,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A81" s="16" t="s">
         <v>382</v>
       </c>
@@ -7370,7 +7703,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A82" s="16" t="s">
         <v>195</v>
       </c>
@@ -7411,7 +7744,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A83" s="16" t="s">
         <v>183</v>
       </c>
@@ -7452,7 +7785,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A84" s="16" t="s">
         <v>191</v>
       </c>
@@ -7493,7 +7826,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A85" s="16" t="s">
         <v>193</v>
       </c>
@@ -7534,7 +7867,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A86" s="16" t="s">
         <v>266</v>
       </c>
@@ -7575,7 +7908,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A87" s="16" t="s">
         <v>269</v>
       </c>
@@ -7616,7 +7949,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A88" s="16" t="s">
         <v>311</v>
       </c>
@@ -7657,7 +7990,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A89" s="16" t="s">
         <v>369</v>
       </c>
@@ -7698,7 +8031,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A90" s="16" t="s">
         <v>434</v>
       </c>
@@ -7739,7 +8072,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A91" s="16" t="s">
         <v>437</v>
       </c>
@@ -7780,7 +8113,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A92" s="16" t="s">
         <v>440</v>
       </c>
@@ -7821,7 +8154,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A93" s="16" t="s">
         <v>308</v>
       </c>
@@ -7862,7 +8195,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A94" s="16" t="s">
         <v>303</v>
       </c>
@@ -7903,7 +8236,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A95" s="16" t="s">
         <v>376</v>
       </c>
@@ -7944,7 +8277,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
         <v>431</v>
       </c>
@@ -7985,7 +8318,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A97" s="16" t="s">
         <v>299</v>
       </c>
@@ -8026,7 +8359,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A98" s="16" t="s">
         <v>371</v>
       </c>
@@ -8067,7 +8400,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A99" s="16" t="s">
         <v>374</v>
       </c>
@@ -8108,7 +8441,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A100" s="16" t="s">
         <v>424</v>
       </c>
@@ -8149,7 +8482,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A101" s="16" t="s">
         <v>426</v>
       </c>
@@ -8190,7 +8523,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="L102" s="21" t="s">
         <v>441</v>
       </c>
@@ -8209,18 +8542,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6919E62F-263C-414E-A448-8B21530BFE26}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H81"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="16" customWidth="1"/>
-    <col min="2" max="2" width="22.5703125" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" style="16" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="7.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="50" style="18" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="7"/>
+    <col min="4" max="7" width="7.6640625" style="17" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="71.88671875" style="18" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>146</v>
       </c>
@@ -8228,7 +8561,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D1" s="15" t="s">
         <v>9</v>
@@ -8246,12 +8579,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>343</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>27</v>
@@ -8269,15 +8602,15 @@
         <v>15</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
         <v>343</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>27</v>
@@ -8295,15 +8628,15 @@
         <v>20</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="16" t="s">
         <v>341</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>219</v>
@@ -8312,7 +8645,7 @@
         <v>218</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F4" s="17">
         <v>4</v>
@@ -8321,15 +8654,15 @@
         <v>45</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
         <v>341</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>199</v>
@@ -8338,7 +8671,7 @@
         <v>209</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>176</v>
@@ -8347,15 +8680,15 @@
         <v>47</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>174</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>209</v>
@@ -8373,15 +8706,15 @@
         <v>39</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>174</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="C7" s="17" t="s">
         <v>353</v>
@@ -8399,15 +8732,15 @@
         <v>24</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>182</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C8" s="17" t="s">
         <v>199</v>
@@ -8425,15 +8758,15 @@
         <v>38</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>182</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>219</v>
@@ -8451,15 +8784,15 @@
         <v>60</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>258</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>205</v>
@@ -8477,15 +8810,15 @@
         <v>52</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>258</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>218</v>
@@ -8494,7 +8827,7 @@
         <v>353</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="F11" s="17">
         <v>12</v>
@@ -8503,15 +8836,15 @@
         <v>38</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>262</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>209</v>
@@ -8529,15 +8862,15 @@
         <v>26</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>262</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>353</v>
@@ -8555,15 +8888,15 @@
         <v>45</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>289</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>202</v>
@@ -8581,15 +8914,15 @@
         <v>10</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>289</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>212</v>
@@ -8607,15 +8940,15 @@
         <v>35</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>293</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>219</v>
@@ -8633,15 +8966,15 @@
         <v>20</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>293</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>199</v>
@@ -8659,15 +8992,15 @@
         <v>7</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>349</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>209</v>
@@ -8685,15 +9018,15 @@
         <v>50</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>349</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>353</v>
@@ -8711,15 +9044,15 @@
         <v>45</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>351</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>199</v>
@@ -8728,7 +9061,7 @@
         <v>219</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="F20" s="17">
         <v>7</v>
@@ -8737,15 +9070,15 @@
         <v>55</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>351</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>219</v>
@@ -8763,15 +9096,15 @@
         <v>42</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>356</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>219</v>
@@ -8789,15 +9122,15 @@
         <v>22</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>356</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>199</v>
@@ -8815,15 +9148,15 @@
         <v>30</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>360</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
       <c r="C24" s="17" t="s">
         <v>209</v>
@@ -8841,15 +9174,15 @@
         <v>30</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>360</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>353</v>
@@ -8867,15 +9200,15 @@
         <v>31</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>271</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="C26" s="17" t="s">
         <v>202</v>
@@ -8893,15 +9226,15 @@
         <v>30</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>271</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>212</v>
@@ -8919,15 +9252,15 @@
         <v>59</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>287</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="C28" s="17" t="s">
         <v>199</v>
@@ -8945,15 +9278,15 @@
         <v>55</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>287</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="C29" s="17" t="s">
         <v>219</v>
@@ -8971,15 +9304,15 @@
         <v>65</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>285</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="C30" s="17" t="s">
         <v>27</v>
@@ -8994,18 +9327,18 @@
         <v>263</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>285</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="C31" s="17" t="s">
         <v>27</v>
@@ -9023,7 +9356,1307 @@
         <v>246</v>
       </c>
       <c r="H31" s="18" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>731</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E32" s="17">
+        <v>2</v>
+      </c>
+      <c r="F32" s="17">
+        <v>2</v>
+      </c>
+      <c r="G32" s="17">
+        <v>8</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G33" s="17">
+        <v>6</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>737</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="69" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>733</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="17">
+        <v>2</v>
+      </c>
+      <c r="E35" s="17">
+        <v>15</v>
+      </c>
+      <c r="F35" s="17">
+        <v>20</v>
+      </c>
+      <c r="G35" s="17">
+        <v>100</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D36" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="G36" s="17">
+        <v>6</v>
+      </c>
+      <c r="H36" s="18" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="G37" s="17">
+        <v>9</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>740</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>744</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="E38" s="17">
+        <v>23</v>
+      </c>
+      <c r="F38" s="17">
+        <v>50</v>
+      </c>
+      <c r="G38" s="17">
+        <v>130</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" s="17">
+        <v>25</v>
+      </c>
+      <c r="F39" s="17">
+        <v>70</v>
+      </c>
+      <c r="G39" s="17">
+        <v>200</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D40" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F40" s="17">
+        <v>6</v>
+      </c>
+      <c r="G40" s="17">
+        <v>20</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>747</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F41" s="17">
+        <v>8</v>
+      </c>
+      <c r="G41" s="17">
+        <v>27</v>
+      </c>
+      <c r="H41" s="18" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>752</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="G42" s="17">
+        <v>29</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A43" s="16" t="s">
+        <v>283</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>750</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="17">
+        <v>6</v>
+      </c>
+      <c r="G43" s="17">
+        <v>30</v>
+      </c>
+      <c r="H43" s="18" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D44" s="17">
+        <v>2</v>
+      </c>
+      <c r="E44" s="17">
+        <v>10</v>
+      </c>
+      <c r="F44" s="17">
+        <v>21</v>
+      </c>
+      <c r="G44" s="17">
+        <v>97</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="E45" s="17">
+        <v>9</v>
+      </c>
+      <c r="F45" s="17">
+        <v>25</v>
+      </c>
+      <c r="G45" s="17">
+        <v>110</v>
+      </c>
+      <c r="H45" s="18" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A46" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E46" s="17">
+        <v>1</v>
+      </c>
+      <c r="F46" s="17">
+        <v>4</v>
+      </c>
+      <c r="G46" s="17">
+        <v>32</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A47" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="F47" s="17">
+        <v>4</v>
+      </c>
+      <c r="G47" s="17">
+        <v>35</v>
+      </c>
+      <c r="H47" s="18" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A48" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="E48" s="17">
+        <v>18</v>
+      </c>
+      <c r="F48" s="17">
+        <v>50</v>
+      </c>
+      <c r="G48" s="17">
+        <v>175</v>
+      </c>
+      <c r="H48" s="18" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A49" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="E49" s="17">
+        <v>27</v>
+      </c>
+      <c r="F49" s="17">
+        <v>80</v>
+      </c>
+      <c r="G49" s="17">
+        <v>200</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A50" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="17">
+        <v>5</v>
+      </c>
+      <c r="E50" s="17">
+        <v>16</v>
+      </c>
+      <c r="F50" s="17">
+        <v>32</v>
+      </c>
+      <c r="G50" s="17">
+        <v>90</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A51" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D51" s="17">
+        <v>6</v>
+      </c>
+      <c r="E51" s="17">
+        <v>15</v>
+      </c>
+      <c r="F51" s="17">
+        <v>25</v>
+      </c>
+      <c r="G51" s="17">
+        <v>95</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A52" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>784</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D52" s="17">
+        <v>2</v>
+      </c>
+      <c r="E52" s="17">
+        <v>5</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A53" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="F53" s="17">
+        <v>4</v>
+      </c>
+      <c r="G53" s="17">
+        <v>8</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="F54" s="17">
+        <v>17</v>
+      </c>
+      <c r="G54" s="17">
+        <v>52</v>
+      </c>
+      <c r="H54" s="18" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>786</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="F55" s="17">
+        <v>10</v>
+      </c>
+      <c r="G55" s="17">
+        <v>40</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>658</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="F56" s="17">
+        <v>19</v>
+      </c>
+      <c r="G56" s="17">
+        <v>49</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D57" s="17">
+        <v>2</v>
+      </c>
+      <c r="E57" s="17">
+        <v>6</v>
+      </c>
+      <c r="F57" s="17">
+        <v>28</v>
+      </c>
+      <c r="G57" s="17">
+        <v>60</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="17">
+        <v>7</v>
+      </c>
+      <c r="E58" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="F58" s="17" t="s">
+        <v>798</v>
+      </c>
+      <c r="G58" s="17">
+        <v>125</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D59" s="17">
+        <v>8</v>
+      </c>
+      <c r="E59" s="17">
+        <v>50</v>
+      </c>
+      <c r="F59" s="17">
+        <v>45</v>
+      </c>
+      <c r="G59" s="17">
+        <v>120</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A60" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D60" s="17">
+        <v>6</v>
+      </c>
+      <c r="E60" s="17">
+        <v>48</v>
+      </c>
+      <c r="F60" s="17">
+        <v>22</v>
+      </c>
+      <c r="G60" s="17">
+        <v>105</v>
+      </c>
+      <c r="H60" s="18" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A61" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D61" s="17">
+        <v>7</v>
+      </c>
+      <c r="E61" s="17">
+        <v>50</v>
+      </c>
+      <c r="F61" s="17">
+        <v>25</v>
+      </c>
+      <c r="G61" s="17">
+        <v>100</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A62" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="17">
+        <v>4</v>
+      </c>
+      <c r="E62" s="17">
+        <v>9</v>
+      </c>
+      <c r="F62" s="17">
+        <v>22</v>
+      </c>
+      <c r="G62" s="17">
+        <v>76</v>
+      </c>
+      <c r="H62" s="18" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>808</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D63" s="17">
+        <v>3</v>
+      </c>
+      <c r="E63" s="17">
+        <v>7</v>
+      </c>
+      <c r="F63" s="17">
+        <v>25</v>
+      </c>
+      <c r="G63" s="17">
+        <v>80</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D64" s="17">
+        <v>3</v>
+      </c>
+      <c r="E64" s="17">
+        <v>15</v>
+      </c>
+      <c r="F64" s="17">
+        <v>12</v>
+      </c>
+      <c r="G64" s="17">
+        <v>90</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A65" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" s="17">
+        <v>5</v>
+      </c>
+      <c r="E65" s="17">
+        <v>25</v>
+      </c>
+      <c r="F65" s="17">
+        <v>17</v>
+      </c>
+      <c r="G65" s="17">
+        <v>125</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D66" s="17">
+        <v>8</v>
+      </c>
+      <c r="E66" s="17">
+        <v>55</v>
+      </c>
+      <c r="F66" s="17">
+        <v>37</v>
+      </c>
+      <c r="G66" s="17">
+        <v>100</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A67" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="17">
+        <v>8</v>
+      </c>
+      <c r="E67" s="17">
+        <v>60</v>
+      </c>
+      <c r="F67" s="17">
+        <v>40</v>
+      </c>
+      <c r="G67" s="17">
+        <v>120</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A68" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D68" s="17">
+        <v>7</v>
+      </c>
+      <c r="E68" s="17">
+        <v>77</v>
+      </c>
+      <c r="F68" s="17">
+        <v>77</v>
+      </c>
+      <c r="G68" s="17">
+        <v>177</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A69" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D69" s="17">
+        <v>8</v>
+      </c>
+      <c r="E69" s="17">
+        <v>40</v>
+      </c>
+      <c r="F69" s="17">
+        <v>65</v>
+      </c>
+      <c r="G69" s="17">
+        <v>120</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A70" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D70" s="17">
+        <v>10</v>
+      </c>
+      <c r="E70" s="17">
+        <v>50</v>
+      </c>
+      <c r="F70" s="17">
+        <v>55</v>
+      </c>
+      <c r="G70" s="17">
+        <v>125</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A71" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D71" s="17">
+        <v>12</v>
+      </c>
+      <c r="E71" s="17">
+        <v>62</v>
+      </c>
+      <c r="F71" s="17">
+        <v>42</v>
+      </c>
+      <c r="G71" s="17">
+        <v>162</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A72" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D72" s="17">
+        <v>2</v>
+      </c>
+      <c r="E72" s="17">
+        <v>15</v>
+      </c>
+      <c r="F72" s="17">
+        <v>10</v>
+      </c>
+      <c r="G72" s="17">
+        <v>30</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A73" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D73" s="17">
+        <v>40</v>
+      </c>
+      <c r="E73" s="17">
+        <v>200</v>
+      </c>
+      <c r="F73" s="17">
+        <v>90</v>
+      </c>
+      <c r="G73" s="17">
+        <v>300</v>
+      </c>
+      <c r="H73" s="18" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A74" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>202</v>
+      </c>
+      <c r="D74" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="G74" s="17">
+        <v>30</v>
+      </c>
+      <c r="H74" s="18" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A75" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="D75" s="17">
+        <v>1</v>
+      </c>
+      <c r="E75" s="17">
+        <v>4</v>
+      </c>
+      <c r="F75" s="17">
+        <v>7</v>
+      </c>
+      <c r="G75" s="17">
+        <v>20</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A76" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B76" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="F76" s="17">
+        <v>17</v>
+      </c>
+      <c r="G76" s="17">
+        <v>57</v>
+      </c>
+      <c r="H76" s="18" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A77" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D77" s="17">
+        <v>2</v>
+      </c>
+      <c r="E77" s="17">
+        <v>6</v>
+      </c>
+      <c r="F77" s="17">
+        <v>12</v>
+      </c>
+      <c r="G77" s="17">
+        <v>41</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A78" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="D78" s="17">
+        <v>5</v>
+      </c>
+      <c r="E78" s="17">
+        <v>28</v>
+      </c>
+      <c r="F78" s="17">
+        <v>21</v>
+      </c>
+      <c r="G78" s="17">
+        <v>110</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A79" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" s="17">
+        <v>7</v>
+      </c>
+      <c r="E79" s="17">
+        <v>36</v>
+      </c>
+      <c r="F79" s="17">
+        <v>50</v>
+      </c>
+      <c r="G79" s="17">
+        <v>160</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A80" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D80" s="17">
+        <v>20</v>
+      </c>
+      <c r="E80" s="17">
+        <v>75</v>
+      </c>
+      <c r="F80" s="17">
+        <v>15</v>
+      </c>
+      <c r="G80" s="17">
+        <v>75</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A81" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D81" s="17">
+        <v>45</v>
+      </c>
+      <c r="E81" s="17">
+        <v>175</v>
+      </c>
+      <c r="F81" s="17">
+        <v>40</v>
+      </c>
+      <c r="G81" s="17">
+        <v>230</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -9034,15 +10667,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF8A856-5E3F-4F82-AC87-CA307D114298}">
-  <sheetPr codeName="Sheet7" filterMode="1"/>
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" style="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.85546875" style="12"/>
+    <col min="1" max="1" width="20.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -9059,7 +10692,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>42</v>
       </c>
@@ -9073,7 +10706,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>40</v>
       </c>
@@ -9087,7 +10720,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
         <v>41</v>
       </c>
@@ -9101,7 +10734,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>43</v>
       </c>
@@ -9115,7 +10748,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
         <v>44</v>
       </c>
@@ -9129,7 +10762,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
         <v>108</v>
       </c>
@@ -9143,7 +10776,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="46.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="46.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
         <v>50</v>
       </c>
@@ -9157,7 +10790,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A9" s="22" t="s">
         <v>116</v>
       </c>
@@ -9171,7 +10804,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A10" s="22" t="s">
         <v>122</v>
       </c>
@@ -9185,7 +10818,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A11" s="22" t="s">
         <v>127</v>
       </c>
@@ -9199,7 +10832,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
         <v>119</v>
       </c>
@@ -9213,7 +10846,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A13" s="22" t="s">
         <v>120</v>
       </c>
@@ -9227,7 +10860,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>124</v>
       </c>
@@ -9241,21 +10874,21 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="33.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
         <v>45</v>
       </c>
@@ -9269,7 +10902,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
         <v>48</v>
       </c>
@@ -9283,7 +10916,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A18" s="22" t="s">
         <v>51</v>
       </c>
@@ -9297,7 +10930,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A19" s="22" t="s">
         <v>65</v>
       </c>
@@ -9311,7 +10944,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A20" s="22" t="s">
         <v>100</v>
       </c>
@@ -9325,7 +10958,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A21" s="22" t="s">
         <v>103</v>
       </c>
@@ -9339,35 +10972,35 @@
         <v>105</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>133</v>
       </c>
@@ -9381,7 +11014,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
         <v>135</v>
       </c>
@@ -9395,7 +11028,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="69" x14ac:dyDescent="0.25">
       <c r="A26" s="22" t="s">
         <v>138</v>
       </c>
@@ -9409,7 +11042,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>139</v>
       </c>
@@ -9423,7 +11056,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A28" s="22" t="s">
         <v>142</v>
       </c>
@@ -9437,7 +11070,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A29" s="22" t="s">
         <v>144</v>
       </c>
@@ -9451,98 +11084,92 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="30" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="11" t="s">
+    <row r="30" spans="1:4" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A30" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="11" t="s">
+    <row r="31" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A31" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="32" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="11" t="s">
+    <row r="32" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="22" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:4" ht="55.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="18" t="s">
         <v>576</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="18" t="s">
         <v>577</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="11" t="s">
+    <row r="34" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A34" s="22" t="s">
         <v>578</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="22" t="s">
         <v>579</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="22" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+    <row r="35" spans="1:4" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A35" s="18" t="s">
         <v>582</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="18" t="s">
         <v>55</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D35" xr:uid="{6DF8A856-5E3F-4F82-AC87-CA307D114298}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Freshwater"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D35" xr:uid="{6DF8A856-5E3F-4F82-AC87-CA307D114298}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D29">
     <sortCondition ref="D2:D35"/>
     <sortCondition ref="B2:B35"/>
@@ -9555,18 +11182,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B1612E-A437-4A38-BD7B-1482265E1A30}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:N34"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="7"/>
+    <col min="1" max="2" width="8.88671875" style="7"/>
     <col min="3" max="3" width="11" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.85546875" style="7"/>
-    <col min="7" max="7" width="9.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.88671875" style="7"/>
+    <col min="7" max="7" width="9.88671875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="7"/>
+    <col min="9" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
@@ -9604,7 +11231,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>321</v>
       </c>
@@ -9646,7 +11273,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>321</v>
       </c>
@@ -9687,7 +11314,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>321</v>
       </c>
@@ -9716,20 +11343,20 @@
         <v>2</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M4" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="N4" s="7">
-        <f>COUNTA(Location!A:A)-1</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="7" cm="1">
+        <f t="array" ref="N4">ROWS(_xlfn.UNIQUE(_xlfn._xlws.FILTER(Mutation!A2:A1000,Mutation!A2:A1000&lt;&gt;"")))</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>146</v>
       </c>
@@ -9757,7 +11384,7 @@
         <v>2</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>322</v>
+        <v>52</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>330</v>
@@ -9766,8 +11393,8 @@
         <v>320</v>
       </c>
       <c r="N5" s="7">
-        <f>COUNTA(Rod!A:A)-1</f>
-        <v>18</v>
+        <f>COUNTA(Location!A:A)-1</f>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -9809,7 +11436,7 @@
       </c>
       <c r="N6" s="7">
         <f>COUNTA(Mutation!A:A)-1</f>
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -9840,6 +11467,19 @@
         <f>COUNTIFS(Fish!C:C,H7,Fish!B:B,G7)</f>
         <v>4</v>
       </c>
+      <c r="K7" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="N7" s="7">
+        <f>COUNTA(Rod!A:A)-1</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -9870,7 +11510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>146</v>
       </c>
@@ -9899,7 +11539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>146</v>
       </c>
@@ -9928,7 +11568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>146</v>
       </c>
@@ -9957,7 +11597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>146</v>
       </c>
@@ -9986,7 +11626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>146</v>
       </c>
@@ -10015,7 +11655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>52</v>
       </c>
@@ -10044,7 +11684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>52</v>
       </c>
@@ -10073,7 +11713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="15" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>52</v>
       </c>
@@ -10102,7 +11742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>52</v>
       </c>
@@ -10131,7 +11771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>52</v>
       </c>
@@ -10160,7 +11800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>52</v>
       </c>
@@ -10189,7 +11829,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>52</v>
       </c>
@@ -10218,7 +11858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F21" s="7" t="s">
         <v>146</v>
       </c>
@@ -10234,7 +11874,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F22" s="7" t="s">
         <v>146</v>
       </c>
@@ -10250,7 +11890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F23" s="7" t="s">
         <v>146</v>
       </c>
@@ -10266,7 +11906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F24" s="7" t="s">
         <v>146</v>
       </c>
@@ -10282,7 +11922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F25" s="7" t="s">
         <v>146</v>
       </c>
@@ -10298,7 +11938,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F26" s="7" t="s">
         <v>146</v>
       </c>
@@ -10313,7 +11953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F27" s="7" t="s">
         <v>146</v>
       </c>
@@ -10328,7 +11968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F28" s="7" t="s">
         <v>146</v>
       </c>
@@ -10344,7 +11984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F29" s="7" t="s">
         <v>146</v>
       </c>
@@ -10359,7 +11999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F30" s="7" t="s">
         <v>146</v>
       </c>
@@ -10375,7 +12015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F31" s="7" t="s">
         <v>146</v>
       </c>
@@ -10391,7 +12031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F32" s="7" t="s">
         <v>146</v>
       </c>
@@ -10407,7 +12047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="6:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F33" s="7" t="s">
         <v>146</v>
       </c>
@@ -10423,7 +12063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="6:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="6:9" ht="15" x14ac:dyDescent="0.25">
       <c r="F34" s="7" t="s">
         <v>146</v>
       </c>
@@ -10441,9 +12081,8 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N1" xr:uid="{30B1612E-A437-4A38-BD7B-1482265E1A30}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F2:I34">
-    <sortCondition ref="G2:G34"/>
-    <sortCondition ref="H2:H34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K2:N34">
+    <sortCondition ref="K2:K34"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Fishing Sim Encylopedia.xlsx
+++ b/Fishing Sim Encylopedia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\fishing-sim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41D2C894-0FE0-441E-97A9-A3B75EFC7FF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11695FD-8DFE-4368-B614-59C4E56F0A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{9977F37B-D2C6-4802-9F43-18753E2C43C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{9977F37B-D2C6-4802-9F43-18753E2C43C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Glossary" sheetId="4" r:id="rId1"/>
@@ -24,7 +24,7 @@
     <sheet name="Total" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Bait!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Bait!$B$1:$E$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Fish!$A$1:$M$102</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Location!$A$1:$D$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Mutation!$A$1:$H$1</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3713,7 +3713,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3794,10 +3794,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4768,807 +4765,937 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE740DA-B477-45BF-81B5-E0EFA8CDE1AC}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="44.5546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="20.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="44.5546875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="5" hidden="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="B2" s="18">
-        <v>1</v>
-      </c>
-      <c r="C2" s="20">
+      <c r="C2" s="18">
+        <v>1</v>
+      </c>
+      <c r="D2" s="20">
         <v>1.2</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="E2" s="5" t="str">
-        <f>_xlfn.CONCAT("('",A2,"',",B2,",","'",D2,"'),")</f>
+      <c r="F2" s="5" t="str">
+        <f>_xlfn.CONCAT("('",B2,"',",C2,",","'",E2,"'),")</f>
         <v>('Earthworm',1,'The basic natural bait that attract wide range of bottom-feeding fish and omnivorous fish.'),</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="B3" s="18">
-        <v>1</v>
-      </c>
-      <c r="C3" s="20">
+      <c r="C3" s="18">
+        <v>1</v>
+      </c>
+      <c r="D3" s="20">
         <v>1.2</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="E3" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="E3" s="5" t="str">
-        <f t="shared" ref="E3:E44" si="0">_xlfn.CONCAT("('",A3,"',",B3,",","'",D3,"'),")</f>
+      <c r="F3" s="5" t="str">
+        <f t="shared" ref="F3:F44" si="0">_xlfn.CONCAT("('",B3,"',",C3,",","'",E3,"'),")</f>
         <v>('Nightcrawler',1,'A large and lively worm that attracts bigger fish looking for an easy prey because of its movement.'),</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="B4" s="18">
-        <v>1</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="C4" s="18">
+        <v>1</v>
+      </c>
+      <c r="D4" s="20">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="E4" s="5" t="str">
+      <c r="F4" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Ragworm',1,'A tough marine worm that attracts aggressive predators lives in brackish and seawater.'),</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="5" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="B5" s="18">
-        <v>1</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="18">
+        <v>1</v>
+      </c>
+      <c r="D5" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>471</v>
       </c>
-      <c r="E5" s="5" t="str">
+      <c r="F5" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Bloodworm',1,'Bright red larvae rich in nutrients, irresistible to many insect-eating and bottom-feeding fish.'),</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>442</v>
       </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="20">
+      <c r="C6" s="18">
+        <v>1</v>
+      </c>
+      <c r="D6" s="20">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="E6" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="E6" s="5" t="str">
+      <c r="F6" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Sandworm',1,'A worm living inside a sandy bottom is targeted by fish that forage on the bottom of the water.'),</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="B7" s="18">
+      <c r="C7" s="18">
         <v>2</v>
       </c>
-      <c r="C7" s="20">
+      <c r="D7" s="20">
         <v>1.2</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="E7" s="5" t="str">
+      <c r="F7" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('River Shrimp',2,'A type of crustacean favored by freshwater and brackish predators.'),</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="B8" s="18">
+      <c r="C8" s="18">
         <v>2</v>
       </c>
-      <c r="C8" s="20">
+      <c r="D8" s="20">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="E8" s="5" t="str">
+      <c r="F8" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Small Crab',2,'A small crustacean, a highly sought-after fish not bothered by the shell.'),</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="B9" s="18">
+      <c r="C9" s="18">
         <v>2</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="D9" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="E9" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="E9" s="5" t="str">
+      <c r="F9" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Prawn',2,'A large meaty crustacean, irresistible to omnivorous fish and predator alike.'),</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+    <row r="10" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>465</v>
       </c>
-      <c r="B10" s="18">
+      <c r="C10" s="18">
         <v>2</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="D10" s="20" t="s">
         <v>466</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="E10" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="E10" s="5" t="str">
+      <c r="F10" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Shrimp',2,'A small freshwater crustacean that attracts fish that hunting aquatic prey.'),</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="18">
+      <c r="C11" s="18">
         <v>2</v>
       </c>
-      <c r="C11" s="20">
-        <v>1</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="20">
+        <v>1</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="E11" s="5" t="str">
+      <c r="F11" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Crayfish',2,'A freshwater crustacean is highly effective in attracting large predatory fish lurking near the bottom.'),</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+    <row r="12" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>431</v>
       </c>
-      <c r="B12" s="15">
+      <c r="C12" s="15">
         <v>3</v>
       </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="13">
+        <v>1</v>
+      </c>
+      <c r="E12" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="E12" s="5" t="str">
+      <c r="F12" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Beetle Grub',3,'A soft-bodied larva packed with protein necessary to attracts insect lover fish.'),</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>12</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>430</v>
       </c>
-      <c r="B13" s="15">
+      <c r="C13" s="15">
         <v>3</v>
       </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="13">
+        <v>1</v>
+      </c>
+      <c r="E13" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="E13" s="5" t="str">
+      <c r="F13" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Mealworm',3,'A wriggling larvae that appeals to fish hunting for food near the surface of the water.'),</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+    <row r="14" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="B14" s="15">
+      <c r="C14" s="15">
         <v>3</v>
       </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="13">
+        <v>1</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="E14" s="5" t="str">
+      <c r="F14" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Dragonfly Nymph',3,'An aquatic insect larva is preyed upon by many freshwater fish.'),</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>14</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>446</v>
       </c>
-      <c r="B15" s="15">
+      <c r="C15" s="15">
         <v>3</v>
       </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="13">
+        <v>1</v>
+      </c>
+      <c r="E15" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="E15" s="5" t="str">
+      <c r="F15" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Water Beetle Larva',3,'A juicy aquatic larva that is hunted by fish searching for underwater insects.'),</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>15</v>
+      </c>
+      <c r="B16" s="15" t="s">
         <v>447</v>
       </c>
-      <c r="B16" s="15">
+      <c r="C16" s="15">
         <v>3</v>
       </c>
-      <c r="C16" s="13">
-        <v>1</v>
-      </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="13">
+        <v>1</v>
+      </c>
+      <c r="E16" s="18" t="s">
         <v>482</v>
       </c>
-      <c r="E16" s="5" t="str">
+      <c r="F16" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Superworm',3,'A larger worm that attracts bigger insectivorous fish.'),</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>16</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="B17" s="15">
+      <c r="C17" s="15">
         <v>4</v>
       </c>
-      <c r="C17" s="13">
+      <c r="D17" s="13">
         <v>1.2</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="E17" s="18" t="s">
         <v>483</v>
       </c>
-      <c r="E17" s="5" t="str">
+      <c r="F17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Grasshopper',4,'A surface insect that draws attention from fish that are waiting for an insect to fall into the water.'),</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="15" t="s">
         <v>433</v>
       </c>
-      <c r="B18" s="15">
+      <c r="C18" s="15">
         <v>4</v>
       </c>
-      <c r="C18" s="13">
+      <c r="D18" s="13">
         <v>1.2</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="E18" s="18" t="s">
         <v>484</v>
       </c>
-      <c r="E18" s="5" t="str">
+      <c r="F18" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Cricket',4,'A lively insect that moves constantly, attracting opportunistic fish.'),</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="B19" s="15">
+      <c r="C19" s="15">
         <v>4</v>
       </c>
-      <c r="C19" s="13">
-        <v>1</v>
-      </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="13">
+        <v>1</v>
+      </c>
+      <c r="E19" s="18" t="s">
         <v>485</v>
       </c>
-      <c r="E19" s="5" t="str">
+      <c r="F19" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Locust',4,'A large insect offering a big meal for surface-feeding fish.'),</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="B20" s="15">
+      <c r="C20" s="15">
         <v>4</v>
       </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="13">
+        <v>1</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="E20" s="5" t="str">
+      <c r="F20" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Cicada',4,'A seasonal insect that fish loved, eagerly waiting for it to drop to water.'),</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>449</v>
       </c>
-      <c r="B21" s="15">
+      <c r="C21" s="15">
         <v>4</v>
       </c>
-      <c r="C21" s="13">
-        <v>1</v>
-      </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="13">
+        <v>1</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="E21" s="5" t="str">
+      <c r="F21" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Termite',4,'A small insect is often consumed by a swarm of fish or a school of fish.'),</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="15" t="s">
         <v>438</v>
       </c>
-      <c r="B22" s="15">
+      <c r="C22" s="15">
         <v>5</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="E22" s="5" t="str">
+      <c r="F22" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Mussel Meat',5,'Soft shellfish meat that has a strong scent that attracts bottom-feeding fish.'),</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
+    <row r="23" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="B23" s="15">
+      <c r="C23" s="15">
         <v>5</v>
       </c>
-      <c r="C23" s="13">
-        <v>1</v>
-      </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="13">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="s">
         <v>489</v>
       </c>
-      <c r="E23" s="5" t="str">
+      <c r="F23" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Pond Snail',5,'A common freshwater mollusk that loves the taste of shelled animal.'),</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
+    <row r="24" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="B24" s="15">
+      <c r="C24" s="15">
         <v>5</v>
       </c>
-      <c r="C24" s="13">
-        <v>1</v>
-      </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="13">
+        <v>1</v>
+      </c>
+      <c r="E24" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="E24" s="5" t="str">
+      <c r="F24" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Clam Meat',5,'Tender clam meat that releases a scent, irresistible to bottom-feeding fish, even humans.'),</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
+    <row r="25" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="s">
         <v>450</v>
       </c>
-      <c r="B25" s="15">
+      <c r="C25" s="15">
         <v>5</v>
       </c>
-      <c r="C25" s="13">
+      <c r="D25" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="E25" s="18" t="s">
         <v>491</v>
       </c>
-      <c r="E25" s="5" t="str">
+      <c r="F25" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Cockle Meat',5,'A salty shellfish popular among brackish and coastal fish.'),</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+    <row r="26" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="B26" s="15">
+      <c r="C26" s="15">
         <v>5</v>
       </c>
-      <c r="C26" s="13">
+      <c r="D26" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="E26" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="E26" s="5" t="str">
+      <c r="F26" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Oyster Meat',5,'Rich, oily meat that attracts fish relying on scent to locate their food.'),</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>26</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="15">
+      <c r="C27" s="15">
         <v>6</v>
       </c>
-      <c r="C27" s="13">
+      <c r="D27" s="13">
         <v>1.2</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="E27" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="E27" s="5" t="str">
+      <c r="F27" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Minnow',6,'A live baitfish that attracts larger fish that are hunting small fish.'),</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+    <row r="28" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>27</v>
+      </c>
+      <c r="B28" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="B28" s="15">
+      <c r="C28" s="15">
         <v>6</v>
       </c>
-      <c r="C28" s="13">
+      <c r="D28" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="E28" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="E28" s="5" t="str">
+      <c r="F28" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Sardine',6,'An oily baitfish that produces a scent trail irresistible to marine predators.'),</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>28</v>
+      </c>
+      <c r="B29" s="15" t="s">
         <v>453</v>
       </c>
-      <c r="B29" s="15">
+      <c r="C29" s="15">
         <v>6</v>
       </c>
-      <c r="C29" s="13">
+      <c r="D29" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="E29" s="18" t="s">
         <v>495</v>
       </c>
-      <c r="E29" s="5" t="str">
+      <c r="F29" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Anchovy',6,'A small baitfish is attractive to schooling predators.'),</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>29</v>
+      </c>
+      <c r="B30" s="15" t="s">
         <v>454</v>
       </c>
-      <c r="B30" s="15">
+      <c r="C30" s="15">
         <v>6</v>
       </c>
-      <c r="C30" s="13">
-        <v>1</v>
-      </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="13">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="E30" s="5" t="str">
+      <c r="F30" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Juvenile Carp',6,'A small carp that attracts larger freshwater predators.'),</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>30</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>455</v>
       </c>
-      <c r="B31" s="15">
+      <c r="C31" s="15">
         <v>6</v>
       </c>
-      <c r="C31" s="13">
-        <v>1</v>
-      </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="13">
+        <v>1</v>
+      </c>
+      <c r="E31" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="E31" s="5" t="str">
+      <c r="F31" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Juvenile Perch',6,'A natural prey for some large carnivorous fish.'),</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+    <row r="32" spans="1:6" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>31</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>458</v>
       </c>
-      <c r="B32" s="15">
+      <c r="C32" s="15">
         <v>7</v>
       </c>
-      <c r="C32" s="13">
-        <v>1</v>
-      </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="13">
+        <v>1</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>498</v>
       </c>
-      <c r="E32" s="5" t="str">
+      <c r="F32" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Beef Meat',7,'A chunk of meat whose strong scent is really effective to attracts scavenger and opportunistic predator fish.'),</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>32</v>
+      </c>
+      <c r="B33" s="15" t="s">
         <v>457</v>
       </c>
-      <c r="B33" s="15">
+      <c r="C33" s="15">
         <v>7</v>
       </c>
-      <c r="C33" s="13">
-        <v>1</v>
-      </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="13">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>499</v>
       </c>
-      <c r="E33" s="5" t="str">
+      <c r="F33" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Pork Meat',7,'Fatty meat for an unusual fish that is not afraid to try anything new.'),</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+    <row r="34" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>33</v>
+      </c>
+      <c r="B34" s="15" t="s">
         <v>456</v>
       </c>
-      <c r="B34" s="15">
+      <c r="C34" s="15">
         <v>7</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="D34" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="E34" s="18" t="s">
         <v>500</v>
       </c>
-      <c r="E34" s="5" t="str">
+      <c r="F34" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Chicken Meat',7,'Tender meat is used to attract omnivorous and predator fish alike.'),</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>34</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>459</v>
       </c>
-      <c r="B35" s="15">
+      <c r="C35" s="15">
         <v>7</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="D35" s="13" t="s">
         <v>466</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="E35" s="18" t="s">
         <v>501</v>
       </c>
-      <c r="E35" s="5" t="str">
+      <c r="F35" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Chicken Heart',7,'Dense and durable bait that stays on the hook even after being peck by predators.'),</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>35</v>
+      </c>
+      <c r="B36" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="B36" s="15">
+      <c r="C36" s="15">
         <v>7</v>
       </c>
-      <c r="C36" s="13">
-        <v>1</v>
-      </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="13">
+        <v>1</v>
+      </c>
+      <c r="E36" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="E36" s="5" t="str">
+      <c r="F36" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Pork Intestine',7,'Tough, oily intestine that release strong scent to attract big predator.'),</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>36</v>
+      </c>
+      <c r="B37" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="15">
+      <c r="C37" s="15">
         <v>8</v>
       </c>
-      <c r="C37" s="13">
-        <v>1</v>
-      </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="13">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="s">
         <v>503</v>
       </c>
-      <c r="E37" s="5" t="str">
+      <c r="F37" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Bread',8,'A simple bait to catch herbivorous and omnivorous fish.'),</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+    <row r="38" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>37</v>
+      </c>
+      <c r="B38" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="15">
+      <c r="C38" s="15">
         <v>8</v>
       </c>
-      <c r="C38" s="13">
-        <v>1</v>
-      </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="13">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>504</v>
       </c>
-      <c r="E38" s="5" t="str">
+      <c r="F38" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Dough',8,'Soft and moldable bait commonly used for fish that feed on plants and grain matter.'),</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>38</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="B39" s="15">
+      <c r="C39" s="15">
         <v>8</v>
       </c>
-      <c r="C39" s="13">
-        <v>1</v>
-      </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="13">
+        <v>1</v>
+      </c>
+      <c r="E39" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="E39" s="5" t="str">
+      <c r="F39" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Sweet Corn',8,'Attract curious omnivorous fish with its color and sweet scent.'),</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+    <row r="40" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>39</v>
+      </c>
+      <c r="B40" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="B40" s="15">
+      <c r="C40" s="15">
         <v>8</v>
       </c>
-      <c r="C40" s="13">
-        <v>1</v>
-      </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="13">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="E40" s="5" t="str">
+      <c r="F40" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Rice',8,'Small grain is occasionally eaten by fish lived near farm water.'),</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>40</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>427</v>
       </c>
-      <c r="B41" s="15">
+      <c r="C41" s="15">
         <v>8</v>
       </c>
-      <c r="C41" s="13">
-        <v>1</v>
-      </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="13">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="E41" s="5" t="str">
+      <c r="F41" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Cheese',8,'A pungent dairy bait whose rich aroma attracts omnivorous and scent-driven fish.'),</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="42" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>41</v>
+      </c>
+      <c r="B42" s="15" t="s">
         <v>461</v>
       </c>
-      <c r="B42" s="15">
+      <c r="C42" s="15">
         <v>9</v>
       </c>
-      <c r="C42" s="13">
+      <c r="D42" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="E42" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="E42" s="5" t="str">
+      <c r="F42" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Squid Strip',9,'Tough, chewy strip of flesh that stays on the hook attracting saltwater predators.'),</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>42</v>
+      </c>
+      <c r="B43" s="15" t="s">
         <v>462</v>
       </c>
-      <c r="B43" s="15">
+      <c r="C43" s="15">
         <v>9</v>
       </c>
-      <c r="C43" s="13">
+      <c r="D43" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="E43" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="E43" s="5" t="str">
+      <c r="F43" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Cuttlefish Strip',9,'Meaty strip of flesh with a rich scent, good for attracting marine predator.'),</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+    <row r="44" spans="1:6" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>43</v>
+      </c>
+      <c r="B44" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="B44" s="15">
+      <c r="C44" s="15">
         <v>9</v>
       </c>
-      <c r="C44" s="13">
+      <c r="D44" s="13">
         <v>2.2999999999999998</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="E44" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="E44" s="5" t="str">
+      <c r="F44" s="5" t="str">
         <f t="shared" si="0"/>
         <v>('Octopus Strip',9,'Firm flesh that is good for attracting powerful predator on the ocean.'),</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{BEE740DA-B477-45BF-81B5-E0EFA8CDE1AC}"/>
+  <autoFilter ref="B1:E44" xr:uid="{BEE740DA-B477-45BF-81B5-E0EFA8CDE1AC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -5583,7 +5710,7 @@
     <col min="1" max="1" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="46" style="2" customWidth="1"/>
-    <col min="4" max="4" width="0" style="6" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="192.44140625" style="6" hidden="1" customWidth="1"/>
     <col min="5" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
@@ -5883,15 +6010,15 @@
     <col min="2" max="2" width="10.5546875" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="52" style="14" customWidth="1"/>
+    <col min="5" max="6" width="9.33203125" style="13" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.109375" style="13" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="13" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="13" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="52" style="14" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="12.109375" style="14" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="15.109375" style="14" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="15.109375" style="14" customWidth="1"/>
     <col min="13" max="13" width="69.109375" style="14" hidden="1" customWidth="1"/>
-    <col min="14" max="17" width="8.88671875" style="3" customWidth="1"/>
+    <col min="14" max="17" width="8.88671875" style="3" hidden="1" customWidth="1"/>
     <col min="18" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
@@ -5947,154 +6074,154 @@
     </row>
     <row r="2" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>332</v>
+        <v>272</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E2" s="13">
-        <v>875</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>212</v>
+        <v>300</v>
+      </c>
+      <c r="F2" s="13">
+        <v>25</v>
       </c>
       <c r="G2" s="13">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="H2" s="13">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="I2" s="13">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="J2" s="14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K2" s="14" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>268</v>
+        <v>62</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>556</v>
+        <v>613</v>
       </c>
       <c r="N2" s="12" cm="1">
         <f t="array" ref="N2">_xlfn.IFS(B2="Freshwater",1,B2="Brackish",2,B2="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O2" s="12" cm="1">
         <f t="array" ref="O2">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B2)*('Fish Type'!C:C=C2),'Fish Type'!A:A)</f>
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="P2" s="12" cm="1">
         <f t="array" ref="P2">_xlfn.IFS(D2="Common",1,D2="Uncommon",2,D2="Rare",3,D2="Legendary",4,D2="Mythical",5,D2="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="5" t="str">
         <f>_xlfn.CONCAT("('",A2,"',",O2,",",P2,",",E2,",",F2,",",G2,",",H2,",",I2,",","'",J2,"'),")</f>
-        <v>('Banded Archerfish',2,1,875,0.1,1,5,30,'Known for its extraordinary marksmanship, the archerfish can accurately spit streams of water several body lengths to dislodge unsuspecting prey.'),</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
+        <v>('Alligator Gar',19,2,300,25,150,75,250,'The body of an alligator gar is torpedo-shaped, usually brown or olive colored, and occasionally black, fading to a lighter gray or yellow ventral surface.'),</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>267</v>
+        <v>22</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" s="13">
-        <v>350</v>
+        <v>85</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>212</v>
+        <v>27</v>
       </c>
       <c r="G3" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H3" s="13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I3" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J3" s="14" t="s">
-        <v>331</v>
+        <v>30</v>
       </c>
       <c r="K3" s="14" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>268</v>
+        <v>62</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>557</v>
+        <v>582</v>
       </c>
       <c r="N3" s="12" cm="1">
         <f t="array" ref="N3">_xlfn.IFS(B3="Freshwater",1,B3="Brackish",2,B3="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" s="12" cm="1">
         <f t="array" ref="O3">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B3)*('Fish Type'!C:C=C3),'Fish Type'!A:A)</f>
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="P3" s="12" cm="1">
         <f t="array" ref="P3">_xlfn.IFS(D3="Common",1,D3="Uncommon",2,D3="Rare",3,D3="Legendary",4,D3="Mythical",5,D3="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q3" s="5" t="str">
-        <f t="shared" ref="Q3:Q66" si="0">_xlfn.CONCAT("('",A3,"',",O3,",",P3,",",E3,",",F3,",",G3,",",H3,",",I3,",","'",J3,"'),")</f>
-        <v>('Northern Archerfish',2,2,350,0.1,1,6,40,'The largest of the archerfish, sporting a deeper body and irregular dark markings. Its powerful water jets and impressive size make it a formidable hunter of mangrove shores.'),</v>
+        <f>_xlfn.CONCAT("('",A3,"',",O3,",",P3,",",E3,",",F3,",",G3,",",H3,",",I3,",","'",J3,"'),")</f>
+        <v>('Aurora Trout',35,3,85,1.5,3,10,30,'Aurora trout can be differentiated by its coloration, grading from magenta hue to nearly orange along the belly.'),</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>171</v>
+        <v>332</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>181</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>33</v>
+        <v>267</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="13">
-        <v>350</v>
+        <v>875</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
       <c r="G4" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="13">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I4" s="13">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>177</v>
+        <v>269</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>63</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>55</v>
+        <v>268</v>
       </c>
       <c r="M4" s="14" t="s">
         <v>556</v>
@@ -6105,83 +6232,83 @@
       </c>
       <c r="O4" s="12" cm="1">
         <f t="array" ref="O4">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B4)*('Fish Type'!C:C=C4),'Fish Type'!A:A)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P4" s="12" cm="1">
         <f t="array" ref="P4">_xlfn.IFS(D4="Common",1,D4="Uncommon",2,D4="Rare",3,D4="Legendary",4,D4="Mythical",5,D4="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Black Bream',8,2,350,0.5,4,23,60,'A dark bronze estuarine bream with a deep body, known for its adaptability and strong fighting ability despite its modest size.'),</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A4,"',",O4,",",P4,",",E4,",",F4,",",G4,",",H4,",",I4,",","'",J4,"'),")</f>
+        <v>('Banded Archerfish',2,1,875,0.1,1,5,30,'Known for its extraordinary marksmanship, the archerfish can accurately spit streams of water several body lengths to dislodge unsuspecting prey.'),</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>33</v>
+        <v>220</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="13">
-        <v>450</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>173</v>
+        <v>100</v>
+      </c>
+      <c r="F5" s="13">
+        <v>40</v>
+      </c>
+      <c r="G5" s="13">
+        <v>300</v>
       </c>
       <c r="H5" s="13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I5" s="13">
-        <v>58</v>
+        <v>270</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>57</v>
+        <v>246</v>
       </c>
       <c r="M5" s="14" t="s">
-        <v>558</v>
+        <v>49</v>
       </c>
       <c r="N5" s="12" cm="1">
         <f t="array" ref="N5">_xlfn.IFS(B5="Freshwater",1,B5="Brackish",2,B5="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" s="12" cm="1">
         <f t="array" ref="O5">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B5)*('Fish Type'!C:C=C5),'Fish Type'!A:A)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P5" s="12" cm="1">
         <f t="array" ref="P5">_xlfn.IFS(D5="Common",1,D5="Uncommon",2,D5="Rare",3,D5="Legendary",4,D5="Mythical",5,D5="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Tarwhine Bream',8,2,450,0.75,4.5,20,58,'A sleek silver bream with bright yellow fins, thriving in estuaries and coastal waters while feeding on small bottom-dwelling prey.'),</v>
+        <f>_xlfn.CONCAT("('",A5,"',",O5,",",P5,",",E5,",",F5,",",G5,",",H5,",",I5,",","'",J5,"'),")</f>
+        <v>('Bengawan Giant Catfish',11,3,100,40,300,30,270,'In Ourea, they call this fish Iremia Giant Catfish. Known for its enormous size, its main diet is algae and aquatic vegetation.'),</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>250</v>
+        <v>408</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>220</v>
+        <v>359</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>16</v>
@@ -6190,142 +6317,142 @@
         <v>275</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>252</v>
+        <v>410</v>
       </c>
       <c r="G6" s="13">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="H6" s="13">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="I6" s="13">
-        <v>64</v>
+        <v>250</v>
       </c>
       <c r="J6" s="14" t="s">
-        <v>253</v>
+        <v>412</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>251</v>
+        <v>411</v>
       </c>
       <c r="M6" s="14" t="s">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="N6" s="12" cm="1">
         <f t="array" ref="N6">_xlfn.IFS(B6="Freshwater",1,B6="Brackish",2,B6="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O6" s="12" cm="1">
         <f t="array" ref="O6">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B6)*('Fish Type'!C:C=C6),'Fish Type'!A:A)</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="P6" s="12" cm="1">
         <f t="array" ref="P6">_xlfn.IFS(D6="Common",1,D6="Uncommon",2,D6="Rare",3,D6="Legendary",4,D6="Mythical",5,D6="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q6" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Hardhead Catfish',12,2,275,0.45,3,15,64,'Hardhead catfish are generally regarded as an undesirable catch because of the risk associated with handling the venomous fish.'),</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A6,"',",O6,",",P6,",",E6,",",F6,",",G6,",",H6,",",I6,",","'",J6,"'),")</f>
+        <v>('Bigeye Tuna',36,2,275,25.5,180,75,250,'The eyes of bigeye tuna are well developed and with a large spherical lens allowing their vision to function well in low light conditions.'),</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>254</v>
+        <v>149</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>220</v>
+        <v>13</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="13">
-        <v>210</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>255</v>
+        <v>350</v>
+      </c>
+      <c r="F7" s="13">
+        <v>9</v>
       </c>
       <c r="G7" s="13">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="H7" s="13">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="I7" s="13">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>256</v>
+        <v>150</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>62</v>
+        <v>242</v>
       </c>
       <c r="M7" s="14" t="s">
-        <v>132</v>
+        <v>607</v>
       </c>
       <c r="N7" s="12" cm="1">
         <f t="array" ref="N7">_xlfn.IFS(B7="Freshwater",1,B7="Brackish",2,B7="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" s="12" cm="1">
         <f t="array" ref="O7">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B7)*('Fish Type'!C:C=C7),'Fish Type'!A:A)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P7" s="12" cm="1">
         <f t="array" ref="P7">_xlfn.IFS(D7="Common",1,D7="Uncommon",2,D7="Rare",3,D7="Legendary",4,D7="Mythical",5,D7="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q7" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Gafftopsail Catfish',12,2,210,1.2,5,12,70,'The gafftopsail catfish is blue-grey to dark brown with a light grey belly. Its appearance is typical for a catfish except for the deeply forked tail and the venomous, serrated spines.'),</v>
+        <f>_xlfn.CONCAT("('",A7,"',",O7,",",P7,",",E7,",",F7,",",G7,",",H7,",",I7,",","'",J7,"'),")</f>
+        <v>('Bighead Carp',9,2,350,9,54,60,146,'The Bighead Carp has a large, scaleless head, a large mouth, and eyes that located very low on their head.'),</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>280</v>
+        <v>171</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>181</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>281</v>
+        <v>33</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E8" s="13">
-        <v>850</v>
+        <v>350</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="G8" s="13">
-        <v>2</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>282</v>
+        <v>4</v>
+      </c>
+      <c r="H8" s="13">
+        <v>23</v>
       </c>
       <c r="I8" s="13">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>283</v>
+        <v>177</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="L8" s="14" t="s">
         <v>55</v>
       </c>
       <c r="M8" s="14" t="s">
-        <v>132</v>
+        <v>556</v>
       </c>
       <c r="N8" s="12" cm="1">
         <f t="array" ref="N8">_xlfn.IFS(B8="Freshwater",1,B8="Brackish",2,B8="Seawater",3)</f>
@@ -6333,26 +6460,26 @@
       </c>
       <c r="O8" s="12" cm="1">
         <f t="array" ref="O8">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B8)*('Fish Type'!C:C=C8),'Fish Type'!A:A)</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P8" s="12" cm="1">
         <f t="array" ref="P8">_xlfn.IFS(D8="Common",1,D8="Uncommon",2,D8="Rare",3,D8="Legendary",4,D8="Mythical",5,D8="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Green Chromide',13,1,850,0.1,2,7.5,40,'It eats mainly aquatic plants, including filamentous algae and diatoms, but it consumes the occasional mollusk and other animal matter.'),</v>
+        <f>_xlfn.CONCAT("('",A8,"',",O8,",",P8,",",E8,",",F8,",",G8,",",H8,",",I8,",","'",J8,"'),")</f>
+        <v>('Black Bream',8,2,350,0.5,4,23,60,'A dark bronze estuarine bream with a deep body, known for its adaptability and strong fighting ability despite its modest size.'),</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>284</v>
+        <v>147</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>281</v>
+        <v>13</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>16</v>
@@ -6360,102 +6487,102 @@
       <c r="E9" s="13">
         <v>300</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>204</v>
+      <c r="F9" s="13">
+        <v>6</v>
+      </c>
+      <c r="G9" s="13">
+        <v>35</v>
       </c>
       <c r="H9" s="13">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="I9" s="13">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>285</v>
+        <v>148</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>60</v>
+        <v>243</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>556</v>
+        <v>606</v>
       </c>
       <c r="N9" s="12" cm="1">
         <f t="array" ref="N9">_xlfn.IFS(B9="Freshwater",1,B9="Brackish",2,B9="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" s="12" cm="1">
         <f t="array" ref="O9">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B9)*('Fish Type'!C:C=C9),'Fish Type'!A:A)</f>
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P9" s="12" cm="1">
         <f t="array" ref="P9">_xlfn.IFS(D9="Common",1,D9="Uncommon",2,D9="Rare",3,D9="Legendary",4,D9="Mythical",5,D9="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q9" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Orange Chromide',13,2,300,0.1,0.3,2,10,'A vivid orange cichlid that thrives in brackish lagoons and estuaries, where it grazes on algae and hunts tiny aquatic creatures among submerged vegetation.'),</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A9,"',",O9,",",P9,",",E9,",",F9,",",G9,",",H9,",",I9,",","'",J9,"'),")</f>
+        <v>('Black Carp',9,2,300,6,35,60,100,'Black Carp are an elongated fish with a fusiform body. They have a dusky gray, brown, or even bluish black color on their body.'),</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E10" s="13">
-        <v>600</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>26</v>
+        <v>51</v>
+      </c>
+      <c r="F10" s="13">
+        <v>100</v>
       </c>
       <c r="G10" s="13">
-        <v>5</v>
+        <v>720</v>
       </c>
       <c r="H10" s="13">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="I10" s="13">
-        <v>55</v>
+        <v>450</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>339</v>
+        <v>369</v>
       </c>
       <c r="K10" s="14" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>55</v>
+        <v>243</v>
       </c>
       <c r="M10" s="14" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="N10" s="12" cm="1">
         <f t="array" ref="N10">_xlfn.IFS(B10="Freshwater",1,B10="Brackish",2,B10="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" s="12" cm="1">
         <f t="array" ref="O10">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B10)*('Fish Type'!C:C=C10),'Fish Type'!A:A)</f>
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="P10" s="12" cm="1">
         <f t="array" ref="P10">_xlfn.IFS(D10="Common",1,D10="Uncommon",2,D10="Rare",3,D10="Legendary",4,D10="Mythical",5,D10="Event",6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Blue Tilapia',13,1,600,0.5,5,9,55,'It grazes on algae and aquatic vegetation while readily adapting to new habitats, making it both abundant and highly resilient.'),</v>
+        <f>_xlfn.CONCAT("('",A10,"',",O10,",",P10,",",E10,",",F10,",",G10,",",H10,",",I10,",","'",J10,"'),")</f>
+        <v>('Black Marlin',5,3,51,100,720,150,450,'One of the fastest fish known to sailors, this fish is said to be fast enough to leave a hole in a ship by swimming through it.'),</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
@@ -6511,163 +6638,163 @@
         <v>1</v>
       </c>
       <c r="Q11" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT("('",A11,"',",O11,",",P11,",",E11,",",F11,",",G11,",",H11,",",I11,",","'",J11,"'),")</f>
         <v>('Black Tilapia',13,1,550,0.7,3.2,7,50,'The most common tilapia in Endral, it has a long upper fins, the front part of which have spines.'),</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>344</v>
+        <v>184</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="13">
-        <v>650</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>26</v>
+        <v>300</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13">
+        <v>3</v>
       </c>
       <c r="H12" s="13">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I12" s="13">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="J12" s="14" t="s">
-        <v>347</v>
+        <v>185</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>346</v>
+        <v>55</v>
       </c>
       <c r="M12" s="14" t="s">
-        <v>550</v>
+        <v>604</v>
       </c>
       <c r="N12" s="12" cm="1">
         <f t="array" ref="N12">_xlfn.IFS(B12="Freshwater",1,B12="Brackish",2,B12="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" cm="1">
         <f t="array" ref="O12">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B12)*('Fish Type'!C:C=C12),'Fish Type'!A:A)</f>
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P12" s="12" cm="1">
         <f t="array" ref="P12">_xlfn.IFS(D12="Common",1,D12="Uncommon",2,D12="Rare",3,D12="Legendary",4,D12="Mythical",5,D12="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Hogchoker',16,1,650,0.1,0.5,5,28,'The overall body of this fish color is often broken by a series of spots and thin stripes, which can be lighter or darker than the main body color.'),</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A12,"',",O12,",",P12,",",E12,",",F12,",",G12,",",H12,",",I12,",","'",J12,"'),")</f>
+        <v>('Blue Bream',7,2,300,1,3,25,55,'A sleek silver-blue fish that travels in large schools through deep rivers and lakes, feeding on drifting insects and tiny aquatic prey.'),</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
-        <v>348</v>
+        <v>222</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>349</v>
+        <v>220</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="13">
-        <v>320</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>212</v>
+        <v>201</v>
+      </c>
+      <c r="F13" s="13">
+        <v>9</v>
       </c>
       <c r="G13" s="13">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="H13" s="13">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I13" s="13">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J13" s="14" t="s">
-        <v>350</v>
+        <v>854</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>346</v>
+        <v>59</v>
       </c>
       <c r="M13" s="14" t="s">
-        <v>557</v>
+        <v>605</v>
       </c>
       <c r="N13" s="12" cm="1">
         <f t="array" ref="N13">_xlfn.IFS(B13="Freshwater",1,B13="Brackish",2,B13="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" cm="1">
         <f t="array" ref="O13">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B13)*('Fish Type'!C:C=C13),'Fish Type'!A:A)</f>
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="P13" s="12" cm="1">
         <f t="array" ref="P13">_xlfn.IFS(D13="Common",1,D13="Uncommon",2,D13="Rare",3,D13="Legendary",4,D13="Mythical",5,D13="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q13" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Four-eyed Fish',18,2,320,0.1,1,5,30,'Four-eyed fish have only two eyes, but the eyes are specially adapted for their surface-dwelling lifestyle.'),</v>
+        <f>_xlfn.CONCAT("('",A13,"',",O13,",",P13,",",E13,",",F13,",",G13,",",H13,",",I13,",","'",J13,"'),")</f>
+        <v>('Blue Catfish',11,2,201,9,65,31,180,'Blue Catfish are often misidentified as Channel Catfish, the difference are the heavy bodied, blueish gray in color, and a upper hump.'),</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>263</v>
+        <v>338</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>181</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E14" s="13">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="G14" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H14" s="13">
-        <v>5</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>265</v>
+        <v>9</v>
+      </c>
+      <c r="I14" s="13">
+        <v>55</v>
       </c>
       <c r="J14" s="14" t="s">
-        <v>266</v>
+        <v>339</v>
       </c>
       <c r="K14" s="14" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="M14" s="14" t="s">
-        <v>561</v>
+        <v>132</v>
       </c>
       <c r="N14" s="12" cm="1">
         <f t="array" ref="N14">_xlfn.IFS(B14="Freshwater",1,B14="Brackish",2,B14="Seawater",3)</f>
@@ -6675,191 +6802,191 @@
       </c>
       <c r="O14" s="12" cm="1">
         <f t="array" ref="O14">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B14)*('Fish Type'!C:C=C14),'Fish Type'!A:A)</f>
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P14" s="12" cm="1">
         <f t="array" ref="P14">_xlfn.IFS(D14="Common",1,D14="Uncommon",2,D14="Rare",3,D14="Legendary",4,D14="Mythical",5,D14="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q14" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Giant Mudskipper',20,1,650,0.1,1,5,28.5,'A giant amphibious goby that prowls muddy shores and mangrove forests, skillfully walking on land and leaping between tidal pools in search of prey'),</v>
+        <f>_xlfn.CONCAT("('",A14,"',",O14,",",P14,",",E14,",",F14,",",G14,",",H14,",",I14,",","'",J14,"'),")</f>
+        <v>('Blue Tilapia',13,1,600,0.5,5,9,55,'It grazes on algae and aquatic vegetation while readily adapting to new habitats, making it both abundant and highly resilient.'),</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>264</v>
+        <v>359</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>19</v>
       </c>
       <c r="E15" s="13">
+        <v>90</v>
+      </c>
+      <c r="F15" s="13">
         <v>100</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>26</v>
+      <c r="G15" s="13">
+        <v>700</v>
       </c>
       <c r="H15" s="13">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="I15" s="13">
-        <v>61</v>
+        <v>400</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>279</v>
+        <v>360</v>
       </c>
       <c r="K15" s="14" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>243</v>
+        <v>158</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="N15" s="12" cm="1">
         <f t="array" ref="N15">_xlfn.IFS(B15="Freshwater",1,B15="Brackish",2,B15="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="12" cm="1">
         <f t="array" ref="O15">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B15)*('Fish Type'!C:C=C15),'Fish Type'!A:A)</f>
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="P15" s="12" cm="1">
         <f t="array" ref="P15">_xlfn.IFS(D15="Common",1,D15="Uncommon",2,D15="Rare",3,D15="Legendary",4,D15="Mythical",5,D15="Event",6)</f>
         <v>3</v>
       </c>
       <c r="Q15" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Dragon Goby',20,3,100,0.1,0.5,8,61,'Dragon Goby is said to be a baby water dragon in its infancy. This fish has a long, slender, eel-like body.'),</v>
+        <f>_xlfn.CONCAT("('",A15,"',",O15,",",P15,",",E15,",",F15,",",G15,",",H15,",",I15,",","'",J15,"'),")</f>
+        <v>('Bluefin Tuna',36,3,90,100,700,150,400,'Their color is dark blue above and gray below, with a gold coruscation covering the body and bright yellow caudal finlets.'),</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>276</v>
+        <v>35</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>264</v>
+        <v>168</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="13">
-        <v>251</v>
+        <v>650</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="G16" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="13">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I16" s="13">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="K16" s="14" t="s">
-        <v>182</v>
+        <v>53</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>251</v>
+        <v>596</v>
       </c>
       <c r="M16" s="14" t="s">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="N16" s="12" cm="1">
         <f t="array" ref="N16">_xlfn.IFS(B16="Freshwater",1,B16="Brackish",2,B16="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" cm="1">
         <f t="array" ref="O16">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B16)*('Fish Type'!C:C=C16),'Fish Type'!A:A)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="P16" s="12" cm="1">
         <f t="array" ref="P16">_xlfn.IFS(D16="Common",1,D16="Uncommon",2,D16="Rare",3,D16="Legendary",4,D16="Mythical",5,D16="Event",6)</f>
+        <v>1</v>
+      </c>
+      <c r="Q16" s="5" t="str">
+        <f>_xlfn.CONCAT("('",A16,"',",O16,",",P16,",",E16,",",F16,",",G16,",",H16,",",I16,",","'",J16,"'),")</f>
+        <v>('Bluegill',34,1,650,0.5,2,15,39,'This insect lover usually hide near a cover and ambush their prey.'),</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="13">
+        <v>250</v>
+      </c>
+      <c r="F17" s="13">
         <v>2</v>
       </c>
-      <c r="Q16" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Knight Goby',20,2,251,0.1,1,1,9,'This goby has a speckled pattern and an armored look reminiscent of a chainmal worn by a knight.'),</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>333</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="13">
-        <v>111</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G17" s="13">
-        <v>1</v>
+      <c r="G17" s="13" t="s">
+        <v>23</v>
       </c>
       <c r="H17" s="13">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I17" s="13">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14" t="s">
-        <v>335</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>334</v>
+        <v>53</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>251</v>
+        <v>55</v>
       </c>
       <c r="M17" s="14" t="s">
-        <v>563</v>
+        <v>623</v>
       </c>
       <c r="N17" s="12" cm="1">
         <f t="array" ref="N17">_xlfn.IFS(B17="Freshwater",1,B17="Brackish",2,B17="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12" cm="1">
         <f t="array" ref="O17">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B17)*('Fish Type'!C:C=C17),'Fish Type'!A:A)</f>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="P17" s="12" cm="1">
         <f t="array" ref="P17">_xlfn.IFS(D17="Common",1,D17="Uncommon",2,D17="Rare",3,D17="Legendary",4,D17="Mythical",5,D17="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Bumblebee Goby',20,3,111,0.1,1,1,4,'A miniature goby known for its bold yellow-and-black stripes. Despite its small size, it is an active predator that patrols muddy bottoms and dense vegetation in search of tiny prey.'),</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A17,"',",O17,",",P17,",",E17,",",F17,",",G17,",",H17,",",I17,",","'",J17,"'),")</f>
+        <v>('Brook Trout',35,2,250,2,6.5,20,61,'Brook trout also called Speckled trout has a green olive body with a yellow spot all over its body.'),</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>181</v>
@@ -6868,34 +6995,34 @@
         <v>264</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E18" s="13">
-        <v>300</v>
-      </c>
-      <c r="F18" s="13">
-        <v>1</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>282</v>
+        <v>111</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G18" s="13">
+        <v>1</v>
       </c>
       <c r="H18" s="13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I18" s="13">
-        <v>65</v>
+        <v>4</v>
       </c>
       <c r="J18" s="14" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>172</v>
+        <v>334</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="M18" s="14" t="s">
-        <v>132</v>
+        <v>563</v>
       </c>
       <c r="N18" s="12" cm="1">
         <f t="array" ref="N18">_xlfn.IFS(B18="Freshwater",1,B18="Brackish",2,B18="Seawater",3)</f>
@@ -6907,214 +7034,214 @@
       </c>
       <c r="P18" s="12" cm="1">
         <f t="array" ref="P18">_xlfn.IFS(D18="Common",1,D18="Uncommon",2,D18="Rare",3,D18="Legendary",4,D18="Mythical",5,D18="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Marble Goby',20,2,300,1,7.5,10,65,'It is a highly popular fish among rich families, said to be best eaten after a childbirth or Chirurgy.'),</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A18,"',",O18,",",P18,",",E18,",",F18,",",G18,",",H18,",",I18,",","'",J18,"'),")</f>
+        <v>('Bumblebee Goby',20,3,111,0.1,1,1,4,'A miniature goby known for its bold yellow-and-black stripes. Despite its small size, it is an active predator that patrols muddy bottoms and dense vegetation in search of tiny prey.'),</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>404</v>
+        <v>219</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>405</v>
+        <v>220</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E19" s="13">
-        <v>630</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>255</v>
+        <v>850</v>
+      </c>
+      <c r="F19" s="13">
+        <v>4</v>
+      </c>
+      <c r="G19" s="13">
+        <v>26</v>
+      </c>
+      <c r="H19" s="13">
+        <v>30</v>
       </c>
       <c r="I19" s="13">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="J19" s="14" t="s">
-        <v>406</v>
+        <v>221</v>
       </c>
       <c r="K19" s="14" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="L19" s="14" t="s">
-        <v>251</v>
+        <v>409</v>
       </c>
       <c r="M19" s="14" t="s">
-        <v>562</v>
+        <v>586</v>
       </c>
       <c r="N19" s="12" cm="1">
         <f t="array" ref="N19">_xlfn.IFS(B19="Freshwater",1,B19="Brackish",2,B19="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" cm="1">
         <f t="array" ref="O19">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B19)*('Fish Type'!C:C=C19),'Fish Type'!A:A)</f>
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="P19" s="12" cm="1">
         <f t="array" ref="P19">_xlfn.IFS(D19="Common",1,D19="Uncommon",2,D19="Rare",3,D19="Legendary",4,D19="Mythical",5,D19="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q19" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Wrestling Halfbeak',22,1,630,0.1,0.3,1.2,8,'Wrestling halfbeaks are surface-feeding fish and feed on a variety of small invertebrates, including crustaceans and insect larvae.'),</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A19,"',",O19,",",P19,",",E19,",",F19,",",G19,",",H19,",",I19,",","'",J19,"'),")</f>
+        <v>('Channel Catfish',11,1,850,4,26,30,132,'This cafish can be found all over Endral's river and stream. '),</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>393</v>
+        <v>1032</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>393</v>
+        <v>22</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" s="13">
-        <v>625</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>255</v>
+        <v>305</v>
+      </c>
+      <c r="F20" s="13">
+        <v>1</v>
       </c>
       <c r="G20" s="13">
+        <v>2</v>
+      </c>
+      <c r="H20" s="13">
         <v>20</v>
       </c>
-      <c r="H20" s="13">
-        <v>90</v>
-      </c>
       <c r="I20" s="13">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="J20" s="14" t="s">
-        <v>394</v>
+        <v>159</v>
       </c>
       <c r="K20" s="14" t="s">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="L20" s="14" t="s">
-        <v>374</v>
+        <v>243</v>
       </c>
       <c r="M20" s="14" t="s">
-        <v>560</v>
+        <v>44</v>
       </c>
       <c r="N20" s="12" cm="1">
         <f t="array" ref="N20">_xlfn.IFS(B20="Freshwater",1,B20="Brackish",2,B20="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" cm="1">
         <f t="array" ref="O20">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B20)*('Fish Type'!C:C=C20),'Fish Type'!A:A)</f>
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="P20" s="12" cm="1">
         <f t="array" ref="P20">_xlfn.IFS(D20="Common",1,D20="Uncommon",2,D20="Rare",3,D20="Legendary",4,D20="Mythical",5,D20="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Milkfish',24,1,625,1.2,20,90,180,'The milkfish is an important seafood in Seran and some Ourea places. This fish is infamous for being much bonier than other food fishes.'),</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A20,"',",O20,",",P20,",",E20,",",F20,",",G20,",",H20,",",I20,",","'",J20,"'),")</f>
+        <v>('Clearwater Cutthroat Trout',35,2,305,1,2,20,45,'Its neck has a bright red coloration, which makes it look like a slash wound; that's why it was called a Cutthroat Trout.'),</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
-        <v>271</v>
+        <v>32</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>270</v>
+        <v>33</v>
       </c>
       <c r="D21" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E21" s="13">
-        <v>555</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>212</v>
+        <v>950</v>
+      </c>
+      <c r="F21" s="13">
+        <v>4</v>
       </c>
       <c r="G21" s="13">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H21" s="13">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I21" s="13">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="J21" s="14" t="s">
-        <v>328</v>
+        <v>34</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M21" s="14" t="s">
-        <v>132</v>
+        <v>584</v>
       </c>
       <c r="N21" s="12" cm="1">
         <f t="array" ref="N21">_xlfn.IFS(B21="Freshwater",1,B21="Brackish",2,B21="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" cm="1">
         <f t="array" ref="O21">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B21)*('Fish Type'!C:C=C21),'Fish Type'!A:A)</f>
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P21" s="12" cm="1">
         <f t="array" ref="P21">_xlfn.IFS(D21="Common",1,D21="Uncommon",2,D21="Rare",3,D21="Legendary",4,D21="Mythical",5,D21="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Tidehaven Moony',25,1,555,0.1,1,7,25,'A silvery schooling fish with a diamond-shaped body and striking black markings native to Tidehaven water.'),</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A21,"',",O21,",",P21,",",E21,",",F21,",",G21,",",H21,",",I21,",","'",J21,"'),")</f>
+        <v>('Common Bream',7,1,950,4,11,30,86,'Common bream have a black fins and silver color in young bream that turn bronze when its got older'),</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="69" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>275</v>
+        <v>12</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>181</v>
+        <v>38</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>270</v>
+        <v>13</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="13">
-        <v>800</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>212</v>
+        <v>1000</v>
+      </c>
+      <c r="F22" s="13">
+        <v>5</v>
       </c>
       <c r="G22" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H22" s="13">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I22" s="13">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="J22" s="14" t="s">
-        <v>851</v>
+        <v>17</v>
       </c>
       <c r="K22" s="14" t="s">
         <v>63</v>
@@ -7123,235 +7250,235 @@
         <v>55</v>
       </c>
       <c r="M22" s="14" t="s">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="N22" s="12" cm="1">
         <f t="array" ref="N22">_xlfn.IFS(B22="Freshwater",1,B22="Brackish",2,B22="Seawater",3)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" cm="1">
         <f t="array" ref="O22">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B22)*('Fish Type'!C:C=C22),'Fish Type'!A:A)</f>
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P22" s="12" cm="1">
         <f t="array" ref="P22">_xlfn.IFS(D22="Common",1,D22="Uncommon",2,D22="Rare",3,D22="Legendary",4,D22="Mythical",5,D22="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q22" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Silver Moony',25,1,800,0.1,1,4,27,'This fish has a bright, shiny silver color with yellowish edges to the fins, and the upper and anal fins have black tips.'),</v>
+        <f>_xlfn.CONCAT("('",A22,"',",O22,",",P22,",",E22,",",F22,",",G22,",",H22,",",I22,",","'",J22,"'),")</f>
+        <v>('Common Carp',9,1,1000,5,40,40,110,'A common carp is a widespread freshwater fish that can be found on almost every freshwater habitat.'),</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
-        <v>401</v>
+        <v>287</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>402</v>
+        <v>96</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>286</v>
       </c>
       <c r="D23" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="13">
-        <v>615</v>
+        <v>950</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="13">
-        <v>8</v>
+        <v>204</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="H23" s="13">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I23" s="13">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="J23" s="14" t="s">
-        <v>403</v>
+        <v>289</v>
       </c>
       <c r="K23" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="L23" s="14" t="s">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="M23" s="14" t="s">
-        <v>132</v>
+        <v>565</v>
       </c>
       <c r="N23" s="12" cm="1">
         <f t="array" ref="N23">_xlfn.IFS(B23="Freshwater",1,B23="Brackish",2,B23="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" s="12" cm="1">
         <f t="array" ref="O23">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B23)*('Fish Type'!C:C=C23),'Fish Type'!A:A)</f>
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="P23" s="12" cm="1">
         <f t="array" ref="P23">_xlfn.IFS(D23="Common",1,D23="Uncommon",2,D23="Rare",3,D23="Legendary",4,D23="Mythical",5,D23="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q23" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Striped Mullet',26,1,615,1.1,8,30,100,'The back of the fish is olive-green, sides are silvery and shade to white towards the belly.'),</v>
+        <f>_xlfn.CONCAT("('",A23,"',",O23,",",P23,",",E23,",",F23,",",G23,",",H23,",",I23,",","'",J23,"'),")</f>
+        <v>('Common Clownfish',1,1,950,0.3,0.8,1,12,'The Common Clownfish has a stocky appearance and oval shape. It is compressed laterally, with a round profile.'),</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E24" s="13">
-        <v>800</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>26</v>
+        <v>201</v>
+      </c>
+      <c r="F24" s="13">
+        <v>8</v>
+      </c>
+      <c r="G24" s="13">
+        <v>40</v>
       </c>
       <c r="H24" s="13">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I24" s="13">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="J24" s="14" t="s">
-        <v>852</v>
+        <v>301</v>
       </c>
       <c r="K24" s="14" t="s">
-        <v>63</v>
+        <v>201</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>246</v>
+        <v>57</v>
       </c>
       <c r="M24" s="14" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="N24" s="12" cm="1">
         <f t="array" ref="N24">_xlfn.IFS(B24="Freshwater",1,B24="Brackish",2,B24="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="12" cm="1">
         <f t="array" ref="O24">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B24)*('Fish Type'!C:C=C24),'Fish Type'!A:A)</f>
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="P24" s="12" cm="1">
         <f t="array" ref="P24">_xlfn.IFS(D24="Common",1,D24="Uncommon",2,D24="Rare",3,D24="Legendary",4,D24="Mythical",5,D24="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Needlefish',27,1,800,0.1,0.5,3,30,'Needlefish are slender and have a single upper fin. Their most distinctive feature is their long, narrow beak, which bears multiple sharp teeth.'),</v>
+        <f>_xlfn.CONCAT("('",A24,"',",O24,",",P24,",",E24,",",F24,",",G24,",",H24,",",I24,",","'",J24,"'),")</f>
+        <v>('Common Dolphinfish',14,2,201,8,40,12,180,' Mature males have distinctive "foreheads"; it grows as the fish matures and often protrudes well above the body proper, which is streamlined by the musculature of the back'),</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
-        <v>395</v>
+        <v>292</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>181</v>
+        <v>96</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>396</v>
+        <v>293</v>
       </c>
       <c r="D25" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="13">
-        <v>585</v>
+        <v>875</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>399</v>
+        <v>212</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>398</v>
+        <v>294</v>
       </c>
       <c r="H25" s="13">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I25" s="13">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="J25" s="14" t="s">
-        <v>400</v>
+        <v>295</v>
       </c>
       <c r="K25" s="14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>397</v>
+        <v>59</v>
       </c>
       <c r="M25" s="14" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="N25" s="12" cm="1">
         <f t="array" ref="N25">_xlfn.IFS(B25="Freshwater",1,B25="Brackish",2,B25="Seawater",3)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" s="12" cm="1">
         <f t="array" ref="O25">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B25)*('Fish Type'!C:C=C25),'Fish Type'!A:A)</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P25" s="12" cm="1">
         <f t="array" ref="P25">_xlfn.IFS(D25="Common",1,D25="Uncommon",2,D25="Rare",3,D25="Legendary",4,D25="Mythical",5,D25="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q25" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Mangrove Jack',32,1,585,2.3,13.5,60,150,'Coloration of the Mangrove Jack ranges from burnt orange to copper, to bronze, and dark reddish-brown, depending on its age and environment.'),</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A25,"',",O25,",",P25,",",E25,",",F25,",",G25,",",H25,",",I25,",","'",J25,"'),")</f>
+        <v>('Common Lionfish',30,1,875,0.1,1.3,10,35,'The fin spines are highly venomous and have caused death to humans in some reported cases. Despite this, a sting from this species is rarely fatal to humans.'),</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" s="13">
-        <v>950</v>
+        <v>210</v>
       </c>
       <c r="F26" s="13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G26" s="13">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H26" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I26" s="13">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="J26" s="14" t="s">
-        <v>34</v>
+        <v>157</v>
       </c>
       <c r="K26" s="14" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="L26" s="14" t="s">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="M26" s="14" t="s">
-        <v>584</v>
+        <v>609</v>
       </c>
       <c r="N26" s="12" cm="1">
         <f t="array" ref="N26">_xlfn.IFS(B26="Freshwater",1,B26="Brackish",2,B26="Seawater",3)</f>
@@ -7359,113 +7486,113 @@
       </c>
       <c r="O26" s="12" cm="1">
         <f t="array" ref="O26">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B26)*('Fish Type'!C:C=C26),'Fish Type'!A:A)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P26" s="12" cm="1">
         <f t="array" ref="P26">_xlfn.IFS(D26="Common",1,D26="Uncommon",2,D26="Rare",3,D26="Legendary",4,D26="Mythical",5,D26="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Common Bream',7,1,950,4,11,30,86,'Common bream have a black fins and silver color in young bream that turn bronze when its got older'),</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A26,"',",O26,",",P26,",",E26,",",F26,",",G26,",",H26,",",I26,",","'",J26,"'),")</f>
+        <v>('Crucian Carp',9,2,210,1,3,15,64,'This fish mainly lived in nutrient-rich water, but it can also lived in an extreme condition and harsh winter.'),</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
-        <v>169</v>
+        <v>278</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>33</v>
+        <v>264</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E27" s="13">
-        <v>975</v>
+        <v>100</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="G27" s="13">
-        <v>2</v>
+        <v>212</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="H27" s="13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I27" s="13">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="J27" s="14" t="s">
-        <v>170</v>
+        <v>279</v>
       </c>
       <c r="K27" s="14" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>62</v>
+        <v>243</v>
       </c>
       <c r="M27" s="14" t="s">
-        <v>590</v>
+        <v>550</v>
       </c>
       <c r="N27" s="12" cm="1">
         <f t="array" ref="N27">_xlfn.IFS(B27="Freshwater",1,B27="Brackish",2,B27="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="12" cm="1">
         <f t="array" ref="O27">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B27)*('Fish Type'!C:C=C27),'Fish Type'!A:A)</f>
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="P27" s="12" cm="1">
         <f t="array" ref="P27">_xlfn.IFS(D27="Common",1,D27="Uncommon",2,D27="Rare",3,D27="Legendary",4,D27="Mythical",5,D27="Event",6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q27" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('White Bream',7,1,975,0.25,2,5,7,'White Bream / Silver Bream generally inhabit the lower reaches of rivers as well as lakes and ponds with muddy bottoms and plenty of algae to feed on.'),</v>
+        <f>_xlfn.CONCAT("('",A27,"',",O27,",",P27,",",E27,",",F27,",",G27,",",H27,",",I27,",","'",J27,"'),")</f>
+        <v>('Dragon Goby',20,3,100,0.1,0.5,8,61,'Dragon Goby is said to be a baby water dragon in its infancy. This fish has a long, slender, eel-like body.'),</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
-        <v>186</v>
+        <v>238</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>33</v>
+        <v>220</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E28" s="13">
-        <v>800</v>
-      </c>
-      <c r="F28" s="13">
-        <v>1</v>
+        <v>400</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>239</v>
       </c>
       <c r="G28" s="13">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="H28" s="13">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I28" s="13">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>853</v>
+        <v>249</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L28" s="14" t="s">
-        <v>60</v>
+        <v>804</v>
       </c>
       <c r="M28" s="14" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="N28" s="12" cm="1">
         <f t="array" ref="N28">_xlfn.IFS(B28="Freshwater",1,B28="Brackish",2,B28="Seawater",3)</f>
@@ -7473,191 +7600,191 @@
       </c>
       <c r="O28" s="12" cm="1">
         <f t="array" ref="O28">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B28)*('Fish Type'!C:C=C28),'Fish Type'!A:A)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P28" s="12" cm="1">
         <f t="array" ref="P28">_xlfn.IFS(D28="Common",1,D28="Uncommon",2,D28="Rare",3,D28="Legendary",4,D28="Mythical",5,D28="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Vimba Bream',7,1,800,1,2,20,50,'This fish is a deep bluish-green on the upper surface, and silvery along the flanks. The eyes are yellow, and the pectoral and pelvic fins have reddish-yellow bases.'),</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A28,"',",O28,",",P28,",",E28,",",F28,",",G28,",",H28,",",I28,",","'",J28,"'),")</f>
+        <v>('Flathead Catfish',11,2,400,8.5,56,32,175,'An ambush predator lurking beneath logs and rocks until unsuspecting prey fish get close.'),</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>33</v>
+        <v>349</v>
       </c>
       <c r="D29" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E29" s="13">
-        <v>300</v>
-      </c>
-      <c r="F29" s="13">
-        <v>1</v>
+        <v>320</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>212</v>
       </c>
       <c r="G29" s="13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="13">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I29" s="13">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J29" s="14" t="s">
-        <v>185</v>
+        <v>350</v>
       </c>
       <c r="K29" s="14" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>55</v>
+        <v>346</v>
       </c>
       <c r="M29" s="14" t="s">
-        <v>604</v>
+        <v>557</v>
       </c>
       <c r="N29" s="12" cm="1">
         <f t="array" ref="N29">_xlfn.IFS(B29="Freshwater",1,B29="Brackish",2,B29="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="12" cm="1">
         <f t="array" ref="O29">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B29)*('Fish Type'!C:C=C29),'Fish Type'!A:A)</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P29" s="12" cm="1">
         <f t="array" ref="P29">_xlfn.IFS(D29="Common",1,D29="Uncommon",2,D29="Rare",3,D29="Legendary",4,D29="Mythical",5,D29="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q29" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Blue Bream',7,2,300,1,3,25,55,'A sleek silver-blue fish that travels in large schools through deep rivers and lakes, feeding on drifting insects and tiny aquatic prey.'),</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="69" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A29,"',",O29,",",P29,",",E29,",",F29,",",G29,",",H29,",",I29,",","'",J29,"'),")</f>
+        <v>('Four-eyed Fish',18,2,320,0.1,1,5,30,'Four-eyed fish have only two eyes, but the eyes are specially adapted for their surface-dwelling lifestyle.'),</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="13">
+        <v>210</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="G30" s="13">
+        <v>5</v>
+      </c>
+      <c r="H30" s="13">
         <v>12</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E30" s="13">
-        <v>1000</v>
-      </c>
-      <c r="F30" s="13">
-        <v>5</v>
-      </c>
-      <c r="G30" s="13">
-        <v>40</v>
-      </c>
-      <c r="H30" s="13">
-        <v>40</v>
-      </c>
       <c r="I30" s="13">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="J30" s="14" t="s">
-        <v>17</v>
+        <v>256</v>
       </c>
       <c r="K30" s="14" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>592</v>
+        <v>132</v>
       </c>
       <c r="N30" s="12" cm="1">
         <f t="array" ref="N30">_xlfn.IFS(B30="Freshwater",1,B30="Brackish",2,B30="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" cm="1">
         <f t="array" ref="O30">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B30)*('Fish Type'!C:C=C30),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P30" s="12" cm="1">
         <f t="array" ref="P30">_xlfn.IFS(D30="Common",1,D30="Uncommon",2,D30="Rare",3,D30="Legendary",4,D30="Mythical",5,D30="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Common Carp',9,1,1000,5,40,40,110,'A common carp is a widespread freshwater fish that can be found on almost every freshwater habitat.'),</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A30,"',",O30,",",P30,",",E30,",",F30,",",G30,",",H30,",",I30,",","'",J30,"'),")</f>
+        <v>('Gafftopsail Catfish',12,2,210,1.2,5,12,70,'The gafftopsail catfish is blue-grey to dark brown with a light grey belly. Its appearance is typical for a catfish except for the deeply forked tail and the venomous, serrated spines.'),</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
-        <v>145</v>
+        <v>263</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>13</v>
+        <v>264</v>
       </c>
       <c r="D31" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E31" s="13">
-        <v>550</v>
-      </c>
-      <c r="F31" s="13">
+        <v>650</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G31" s="13">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13">
         <v>5</v>
       </c>
-      <c r="G31" s="13">
-        <v>45</v>
-      </c>
-      <c r="H31" s="13">
-        <v>20</v>
-      </c>
-      <c r="I31" s="13">
-        <v>95</v>
+      <c r="I31" s="13" t="s">
+        <v>265</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>146</v>
+        <v>266</v>
       </c>
       <c r="K31" s="14" t="s">
         <v>103</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="M31" s="14" t="s">
-        <v>585</v>
+        <v>561</v>
       </c>
       <c r="N31" s="12" cm="1">
         <f t="array" ref="N31">_xlfn.IFS(B31="Freshwater",1,B31="Brackish",2,B31="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="12" cm="1">
         <f t="array" ref="O31">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B31)*('Fish Type'!C:C=C31),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="P31" s="12" cm="1">
         <f t="array" ref="P31">_xlfn.IFS(D31="Common",1,D31="Uncommon",2,D31="Rare",3,D31="Legendary",4,D31="Mythical",5,D31="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q31" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Grass Carp',9,1,550,5,45,20,95,'Grass Carp eggs require a long river to survive, and the eggs will be considered dead when they hit the bottom of the river.'),</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A31,"',",O31,",",P31,",",E31,",",F31,",",G31,",",H31,",",I31,",","'",J31,"'),")</f>
+        <v>('Giant Mudskipper',20,1,650,0.1,1,5,28.5,'A giant amphibious goby that prowls muddy shores and mangrove forests, skillfully walking on land and leaping between tidal pools in search of prey'),</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
-        <v>151</v>
+        <v>323</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>38</v>
@@ -7666,34 +7793,34 @@
         <v>13</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E32" s="13">
-        <v>700</v>
+        <v>325</v>
       </c>
       <c r="F32" s="13">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G32" s="13">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="H32" s="13">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="I32" s="13">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>346</v>
+        <v>62</v>
       </c>
       <c r="M32" s="14" t="s">
-        <v>760</v>
+        <v>118</v>
       </c>
       <c r="N32" s="12" cm="1">
         <f t="array" ref="N32">_xlfn.IFS(B32="Freshwater",1,B32="Brackish",2,B32="Seawater",3)</f>
@@ -7705,16 +7832,16 @@
       </c>
       <c r="P32" s="12" cm="1">
         <f t="array" ref="P32">_xlfn.IFS(D32="Common",1,D32="Uncommon",2,D32="Rare",3,D32="Legendary",4,D32="Mythical",5,D32="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Mud Carp',9,1,700,2,5,20,74,'Mud Carp is considered to be inedible the first time people caught it, but after the great incident, this fish became popular.'),</v>
+        <f>_xlfn.CONCAT("('",A32,"',",O32,",",P32,",",E32,",",F32,",",G32,",",H32,",",I32,",","'",J32,"'),")</f>
+        <v>('Giant River Carp',9,2,325,10,105,30,180,'This carp usually lives in a large pond or lake, but seasonally find its way into the canal, reservoir and flooded forest.'),</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
-        <v>18</v>
+        <v>154</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>38</v>
@@ -7723,34 +7850,34 @@
         <v>13</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E33" s="13">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="F33" s="13">
         <v>2</v>
       </c>
       <c r="G33" s="13">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H33" s="13">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I33" s="13">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>242</v>
+        <v>55</v>
       </c>
       <c r="M33" s="14" t="s">
-        <v>580</v>
+        <v>608</v>
       </c>
       <c r="N33" s="12" cm="1">
         <f t="array" ref="N33">_xlfn.IFS(B33="Freshwater",1,B33="Brackish",2,B33="Seawater",3)</f>
@@ -7762,109 +7889,109 @@
       </c>
       <c r="P33" s="12" cm="1">
         <f t="array" ref="P33">_xlfn.IFS(D33="Common",1,D33="Uncommon",2,D33="Rare",3,D33="Legendary",4,D33="Mythical",5,D33="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Mrigal Carp',9,3,100,2,13,15,100,'This fish live in a lower water level and feeds on small insects and decomposed organic element.'),</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A33,"',",O33,",",P33,",",E33,",",F33,",",G33,",",H33,",",I33,",","'",J33,"'),")</f>
+        <v>('Gibel Carp',9,2,220,2,5,10,35,'Gibel Carp reproduce and spread so rapidly that it is said that it can fill an entire medium-sized pond in its species alone.'),</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
-        <v>15</v>
+        <v>1091</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E34" s="13">
-        <v>350</v>
-      </c>
-      <c r="F34" s="13">
-        <v>7</v>
+        <v>201</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="G34" s="13">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="H34" s="13">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="I34" s="13">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>308</v>
+        <v>189</v>
       </c>
       <c r="K34" s="14" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="L34" s="14" t="s">
         <v>58</v>
       </c>
       <c r="M34" s="14" t="s">
-        <v>605</v>
+        <v>566</v>
       </c>
       <c r="N34" s="12" cm="1">
         <f t="array" ref="N34">_xlfn.IFS(B34="Freshwater",1,B34="Brackish",2,B34="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O34" s="12" cm="1">
         <f t="array" ref="O34">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B34)*('Fish Type'!C:C=C34),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P34" s="12" cm="1">
         <f t="array" ref="P34">_xlfn.IFS(D34="Common",1,D34="Uncommon",2,D34="Rare",3,D34="Legendary",4,D34="Mythical",5,D34="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q34" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Silver Carp',9,2,350,7,50,35,105,'A fast-growing filter feeder that cruises open freshwater, consuming microscopic plankton and occasionally leaping high above the surface when startled.'),</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A34,"',",O34,",",P34,",",E34,",",F34,",",G34,",",H34,",",I34,",","'",J34,"'),")</f>
+        <v>('Gilthead Seabream',6,2,201,0.5,18,15,70,'The gilt-head bream has a deep body, with a large, deep head which has its relatively small eyes placed high on the head. The diameter of the eyes is shorter than the length of the snout.'),</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A35" s="12" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E35" s="13">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F35" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G35" s="13">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="H35" s="13">
+        <v>15</v>
+      </c>
+      <c r="I35" s="13">
+        <v>30</v>
+      </c>
+      <c r="J35" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L35" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="I35" s="13">
-        <v>100</v>
-      </c>
-      <c r="J35" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="K35" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L35" s="14" t="s">
-        <v>243</v>
-      </c>
       <c r="M35" s="14" t="s">
-        <v>606</v>
+        <v>583</v>
       </c>
       <c r="N35" s="12" cm="1">
         <f t="array" ref="N35">_xlfn.IFS(B35="Freshwater",1,B35="Brackish",2,B35="Seawater",3)</f>
@@ -7872,20 +7999,20 @@
       </c>
       <c r="O35" s="12" cm="1">
         <f t="array" ref="O35">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B35)*('Fish Type'!C:C=C35),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="P35" s="12" cm="1">
         <f t="array" ref="P35">_xlfn.IFS(D35="Common",1,D35="Uncommon",2,D35="Rare",3,D35="Legendary",4,D35="Mythical",5,D35="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Black Carp',9,2,300,6,35,60,100,'Black Carp are an elongated fish with a fusiform body. They have a dusky gray, brown, or even bluish black color on their body.'),</v>
+        <f>_xlfn.CONCAT("('",A35,"',",O35,",",P35,",",E35,",",F35,",",G35,",",H35,",",I35,",","'",J35,"'),")</f>
+        <v>('Golden Trout',35,3,100,1,5,15,30,'Every first Golden Trout that is caught that day needs to be given to the royal family.'),</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>38</v>
@@ -7894,34 +8021,34 @@
         <v>13</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E36" s="13">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="F36" s="13">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G36" s="13">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H36" s="13">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I36" s="13">
+        <v>95</v>
+      </c>
+      <c r="J36" s="14" t="s">
         <v>146</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>103</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M36" s="14" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="N36" s="12" cm="1">
         <f t="array" ref="N36">_xlfn.IFS(B36="Freshwater",1,B36="Brackish",2,B36="Seawater",3)</f>
@@ -7933,166 +8060,166 @@
       </c>
       <c r="P36" s="12" cm="1">
         <f t="array" ref="P36">_xlfn.IFS(D36="Common",1,D36="Uncommon",2,D36="Rare",3,D36="Legendary",4,D36="Mythical",5,D36="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Bighead Carp',9,2,350,9,54,60,146,'The Bighead Carp has a large, scaleless head, a large mouth, and eyes that located very low on their head.'),</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A36,"',",O36,",",P36,",",E36,",",F36,",",G36,",",H36,",",I36,",","'",J36,"'),")</f>
+        <v>('Grass Carp',9,1,550,5,45,20,95,'Grass Carp eggs require a long river to survive, and the eggs will be considered dead when they hit the bottom of the river.'),</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
       <c r="D37" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E37" s="13">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="F37" s="13">
         <v>10</v>
       </c>
       <c r="G37" s="13">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="H37" s="13">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I37" s="13">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="J37" s="14" t="s">
-        <v>153</v>
+        <v>304</v>
       </c>
       <c r="K37" s="14" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>62</v>
+        <v>158</v>
       </c>
       <c r="M37" s="14" t="s">
-        <v>118</v>
+        <v>566</v>
       </c>
       <c r="N37" s="12" cm="1">
         <f t="array" ref="N37">_xlfn.IFS(B37="Freshwater",1,B37="Brackish",2,B37="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" s="12" cm="1">
         <f t="array" ref="O37">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B37)*('Fish Type'!C:C=C37),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P37" s="12" cm="1">
         <f t="array" ref="P37">_xlfn.IFS(D37="Common",1,D37="Uncommon",2,D37="Rare",3,D37="Legendary",4,D37="Mythical",5,D37="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q37" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Giant River Carp',9,2,325,10,105,30,180,'This carp usually lives in a large pond or lake, but seasonally find its way into the canal, reservoir and flooded forest.'),</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A37,"',",O37,",",P37,",",E37,",",F37,",",G37,",",H37,",",I37,",","'",J37,"'),")</f>
+        <v>('Great Barracuda',3,2,250,10,47,50,300,'They are voracious predators and hunt by ambush. They rely on surprise and short bursts of speed to overrun their prey, sacrificing maneuverability.'),</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
-        <v>154</v>
+        <v>280</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>13</v>
+        <v>281</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E38" s="13">
-        <v>220</v>
-      </c>
-      <c r="F38" s="13">
+        <v>850</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G38" s="13">
         <v>2</v>
       </c>
-      <c r="G38" s="13">
-        <v>5</v>
-      </c>
-      <c r="H38" s="13">
-        <v>10</v>
+      <c r="H38" s="13" t="s">
+        <v>282</v>
       </c>
       <c r="I38" s="13">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J38" s="14" t="s">
-        <v>155</v>
+        <v>283</v>
       </c>
       <c r="K38" s="14" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="L38" s="14" t="s">
         <v>55</v>
       </c>
       <c r="M38" s="14" t="s">
-        <v>608</v>
+        <v>132</v>
       </c>
       <c r="N38" s="12" cm="1">
         <f t="array" ref="N38">_xlfn.IFS(B38="Freshwater",1,B38="Brackish",2,B38="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" s="12" cm="1">
         <f t="array" ref="O38">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B38)*('Fish Type'!C:C=C38),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P38" s="12" cm="1">
         <f t="array" ref="P38">_xlfn.IFS(D38="Common",1,D38="Uncommon",2,D38="Rare",3,D38="Legendary",4,D38="Mythical",5,D38="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Gibel Carp',9,2,220,2,5,10,35,'Gibel Carp reproduce and spread so rapidly that it is said that it can fill an entire medium-sized pond in its species alone.'),</v>
+        <f>_xlfn.CONCAT("('",A38,"',",O38,",",P38,",",E38,",",F38,",",G38,",",H38,",",I38,",","'",J38,"'),")</f>
+        <v>('Green Chromide',13,1,850,0.1,2,7.5,40,'It eats mainly aquatic plants, including filamentous algae and diatoms, but it consumes the occasional mollusk and other animal matter.'),</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A39" s="12" t="s">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E39" s="13">
-        <v>210</v>
-      </c>
-      <c r="F39" s="13">
-        <v>1</v>
-      </c>
-      <c r="G39" s="13">
-        <v>3</v>
+        <v>670</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="H39" s="13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I39" s="13">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="J39" s="14" t="s">
-        <v>157</v>
+        <v>202</v>
       </c>
       <c r="K39" s="14" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>158</v>
+        <v>62</v>
       </c>
       <c r="M39" s="14" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="N39" s="12" cm="1">
         <f t="array" ref="N39">_xlfn.IFS(B39="Freshwater",1,B39="Brackish",2,B39="Seawater",3)</f>
@@ -8100,227 +8227,227 @@
       </c>
       <c r="O39" s="12" cm="1">
         <f t="array" ref="O39">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B39)*('Fish Type'!C:C=C39),'Fish Type'!A:A)</f>
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="P39" s="12" cm="1">
         <f t="array" ref="P39">_xlfn.IFS(D39="Common",1,D39="Uncommon",2,D39="Rare",3,D39="Legendary",4,D39="Mythical",5,D39="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q39" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Crucian Carp',9,2,210,1,3,15,64,'This fish mainly lived in nutrient-rich water, but it can also lived in an extreme condition and harsh winter.'),</v>
+        <f>_xlfn.CONCAT("('",A39,"',",O39,",",P39,",",E39,",",F39,",",G39,",",H39,",",I39,",","'",J39,"'),")</f>
+        <v>('Green Sunfish',34,1,670,0.2,0.9,7,30,'This fish is highly territorial and aggressive, local fishermen refered to its as a bullies of the water.'),</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
-        <v>219</v>
+        <v>1075</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>220</v>
+        <v>1076</v>
       </c>
       <c r="D40" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E40" s="13">
-        <v>850</v>
-      </c>
-      <c r="F40" s="13">
-        <v>4</v>
-      </c>
-      <c r="G40" s="13">
-        <v>26</v>
+        <v>451</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>290</v>
       </c>
       <c r="H40" s="13">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I40" s="13">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>221</v>
+        <v>291</v>
       </c>
       <c r="K40" s="14" t="s">
         <v>63</v>
       </c>
       <c r="L40" s="14" t="s">
-        <v>409</v>
+        <v>55</v>
       </c>
       <c r="M40" s="14" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="N40" s="12" cm="1">
         <f t="array" ref="N40">_xlfn.IFS(B40="Freshwater",1,B40="Brackish",2,B40="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O40" s="12" cm="1">
         <f t="array" ref="O40">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B40)*('Fish Type'!C:C=C40),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P40" s="12" cm="1">
         <f t="array" ref="P40">_xlfn.IFS(D40="Common",1,D40="Uncommon",2,D40="Rare",3,D40="Legendary",4,D40="Mythical",5,D40="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q40" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Channel Catfish',11,1,850,4,26,30,132,'This cafish can be found all over Endral's river and stream. '),</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A40,"',",O40,",",P40,",",E40,",",F40,",",G40,",",H40,",",I40,",","'",J40,"'),")</f>
+        <v>('Grey Crossbowfish',15,1,451,0.4,2.5,20,60,'The small beak-like mouth at the tip of the snout has fleshy lips. The eyes are set far back near the top of the head.'),</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A41" s="12" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>220</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E41" s="13">
-        <v>100</v>
-      </c>
-      <c r="F41" s="13">
-        <v>40</v>
+        <v>275</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>252</v>
       </c>
       <c r="G41" s="13">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="H41" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I41" s="13">
-        <v>270</v>
+        <v>64</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>53</v>
+        <v>182</v>
       </c>
       <c r="L41" s="14" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M41" s="14" t="s">
-        <v>49</v>
+        <v>559</v>
       </c>
       <c r="N41" s="12" cm="1">
         <f t="array" ref="N41">_xlfn.IFS(B41="Freshwater",1,B41="Brackish",2,B41="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" s="12" cm="1">
         <f t="array" ref="O41">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B41)*('Fish Type'!C:C=C41),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P41" s="12" cm="1">
         <f t="array" ref="P41">_xlfn.IFS(D41="Common",1,D41="Uncommon",2,D41="Rare",3,D41="Legendary",4,D41="Mythical",5,D41="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Bengawan Giant Catfish',11,3,100,40,300,30,270,'In Ourea, they call this fish Iremia Giant Catfish. Known for its enormous size, its main diet is algae and aquatic vegetation.'),</v>
+        <f>_xlfn.CONCAT("('",A41,"',",O41,",",P41,",",E41,",",F41,",",G41,",",H41,",",I41,",","'",J41,"'),")</f>
+        <v>('Hardhead Catfish',12,2,275,0.45,3,15,64,'Hardhead catfish are generally regarded as an undesirable catch because of the risk associated with handling the venomous fish.'),</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
-        <v>222</v>
+        <v>344</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E42" s="13">
-        <v>201</v>
-      </c>
-      <c r="F42" s="13">
-        <v>9</v>
-      </c>
-      <c r="G42" s="13">
-        <v>65</v>
+        <v>650</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="H42" s="13">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I42" s="13">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>854</v>
+        <v>347</v>
       </c>
       <c r="K42" s="14" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="L42" s="14" t="s">
-        <v>59</v>
+        <v>346</v>
       </c>
       <c r="M42" s="14" t="s">
-        <v>605</v>
+        <v>550</v>
       </c>
       <c r="N42" s="12" cm="1">
         <f t="array" ref="N42">_xlfn.IFS(B42="Freshwater",1,B42="Brackish",2,B42="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="12" cm="1">
         <f t="array" ref="O42">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B42)*('Fish Type'!C:C=C42),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P42" s="12" cm="1">
         <f t="array" ref="P42">_xlfn.IFS(D42="Common",1,D42="Uncommon",2,D42="Rare",3,D42="Legendary",4,D42="Mythical",5,D42="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q42" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Blue Catfish',11,2,201,9,65,31,180,'Blue Catfish are often misidentified as Channel Catfish, the difference are the heavy bodied, blueish gray in color, and a upper hump.'),</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A42,"',",O42,",",P42,",",E42,",",F42,",",G42,",",H42,",",I42,",","'",J42,"'),")</f>
+        <v>('Hogchoker',16,1,650,0.1,0.5,5,28,'The overall body of this fish color is often broken by a series of spots and thin stripes, which can be lighter or darker than the main body color.'),</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A43" s="12" t="s">
-        <v>238</v>
+        <v>324</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>220</v>
+        <v>22</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E43" s="13">
-        <v>400</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>239</v>
+        <v>750</v>
+      </c>
+      <c r="F43" s="13">
+        <v>1</v>
       </c>
       <c r="G43" s="13">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="H43" s="13">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="I43" s="13">
-        <v>175</v>
+        <v>55</v>
       </c>
       <c r="J43" s="14" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="L43" s="14" t="s">
-        <v>804</v>
+        <v>62</v>
       </c>
       <c r="M43" s="14" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="N43" s="12" cm="1">
         <f t="array" ref="N43">_xlfn.IFS(B43="Freshwater",1,B43="Brackish",2,B43="Seawater",3)</f>
@@ -8328,170 +8455,170 @@
       </c>
       <c r="O43" s="12" cm="1">
         <f t="array" ref="O43">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B43)*('Fish Type'!C:C=C43),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="P43" s="12" cm="1">
         <f t="array" ref="P43">_xlfn.IFS(D43="Common",1,D43="Uncommon",2,D43="Rare",3,D43="Legendary",4,D43="Mythical",5,D43="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q43" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Flathead Catfish',11,2,400,8.5,56,32,175,'An ambush predator lurking beneath logs and rocks until unsuspecting prey fish get close.'),</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A43,"',",O43,",",P43,",",E43,",",F43,",",G43,",",H43,",",I43,",","'",J43,"'),")</f>
+        <v>('Hvitar Trout',35,1,750,1,2,17,55,'Hvitar Trout have a yellow body, and their upper body covered with a numerous small dark spot'),</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
-        <v>240</v>
+        <v>297</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="D44" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E44" s="13">
-        <v>390</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>241</v>
+        <v>300</v>
+      </c>
+      <c r="F44" s="13">
+        <v>5</v>
       </c>
       <c r="G44" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H44" s="13">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I44" s="13">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="J44" s="14" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="K44" s="14" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="L44" s="14" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="M44" s="14" t="s">
-        <v>611</v>
+        <v>126</v>
       </c>
       <c r="N44" s="12" cm="1">
         <f t="array" ref="N44">_xlfn.IFS(B44="Freshwater",1,B44="Brackish",2,B44="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O44" s="12" cm="1">
         <f t="array" ref="O44">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B44)*('Fish Type'!C:C=C44),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="P44" s="12" cm="1">
         <f t="array" ref="P44">_xlfn.IFS(D44="Common",1,D44="Uncommon",2,D44="Rare",3,D44="Legendary",4,D44="Mythical",5,D44="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q44" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Walking Catfish',11,2,390,7.2,30,25,100,'When the river dried out, this fish would "walk" around the river in wiggling motion to traverse the land.'),</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A44,"',",O44,",",P44,",",E44,",",F44,",",G44,",",H44,",",I44,",","'",J44,"'),")</f>
+        <v>('King Mackerel',23,2,300,5,40,11,184,'A swift ocean predator renowned for its speed and powerful runs. It patrols coastal waters in search of baitfish, making it a prized catch for fisherman.'),</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
-        <v>248</v>
+        <v>276</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="D45" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E45" s="13">
-        <v>250</v>
-      </c>
-      <c r="F45" s="13">
-        <v>20</v>
+        <v>251</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>212</v>
       </c>
       <c r="G45" s="13">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="H45" s="13">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I45" s="13">
-        <v>180</v>
+        <v>9</v>
       </c>
       <c r="J45" s="14" t="s">
-        <v>855</v>
+        <v>277</v>
       </c>
       <c r="K45" s="14" t="s">
-        <v>116</v>
+        <v>182</v>
       </c>
       <c r="L45" s="14" t="s">
-        <v>59</v>
+        <v>251</v>
       </c>
       <c r="M45" s="14" t="s">
-        <v>612</v>
+        <v>562</v>
       </c>
       <c r="N45" s="12" cm="1">
         <f t="array" ref="N45">_xlfn.IFS(B45="Freshwater",1,B45="Brackish",2,B45="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" s="12" cm="1">
         <f t="array" ref="O45">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B45)*('Fish Type'!C:C=C45),'Fish Type'!A:A)</f>
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P45" s="12" cm="1">
         <f t="array" ref="P45">_xlfn.IFS(D45="Common",1,D45="Uncommon",2,D45="Rare",3,D45="Legendary",4,D45="Mythical",5,D45="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q45" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Redtail Catfish',11,2,250,20,80,23,180,'These colorful large catfishes have a brownish back, with yellow sides, and characteristic orange-red upper fin and caudal fin'),</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A45,"',",O45,",",P45,",",E45,",",F45,",",G45,",",H45,",",I45,",","'",J45,"'),")</f>
+        <v>('Knight Goby',20,2,251,0.1,1,1,9,'This goby has a speckled pattern and an armored look reminiscent of a chainmal worn by a knight.'),</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>273</v>
+        <v>22</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E46" s="13">
-        <v>300</v>
+        <v>975</v>
       </c>
       <c r="F46" s="13">
+        <v>10</v>
+      </c>
+      <c r="G46" s="13">
+        <v>46</v>
+      </c>
+      <c r="H46" s="13">
         <v>25</v>
       </c>
-      <c r="G46" s="13">
-        <v>150</v>
-      </c>
-      <c r="H46" s="13">
-        <v>75</v>
-      </c>
       <c r="I46" s="13">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="J46" s="14" t="s">
-        <v>274</v>
+        <v>167</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>176</v>
+        <v>63</v>
       </c>
       <c r="L46" s="14" t="s">
-        <v>62</v>
+        <v>600</v>
       </c>
       <c r="M46" s="14" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="N46" s="12" cm="1">
         <f t="array" ref="N46">_xlfn.IFS(B46="Freshwater",1,B46="Brackish",2,B46="Seawater",3)</f>
@@ -8499,56 +8626,56 @@
       </c>
       <c r="O46" s="12" cm="1">
         <f t="array" ref="O46">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B46)*('Fish Type'!C:C=C46),'Fish Type'!A:A)</f>
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="P46" s="12" cm="1">
         <f t="array" ref="P46">_xlfn.IFS(D46="Common",1,D46="Uncommon",2,D46="Rare",3,D46="Legendary",4,D46="Mythical",5,D46="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Alligator Gar',19,2,300,25,150,75,250,'The body of an alligator gar is torpedo-shaped, usually brown or olive colored, and occasionally black, fading to a lighter gray or yellow ventral surface.'),</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
-        <v>380</v>
+        <f>_xlfn.CONCAT("('",A46,"',",O46,",",P46,",",E46,",",F46,",",G46,",",H46,",",I46,",","'",J46,"'),")</f>
+        <v>('Lake Trout',35,1,975,10,46,25,130,'Lake trout covered in light beige or white spots all over its olive-grey body.'),</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="15" t="s">
+        <v>884</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>381</v>
+        <v>168</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E47" s="13">
-        <v>625</v>
+        <v>450</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G47" s="13">
+        <v>197</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="H47" s="13">
         <v>9</v>
       </c>
-      <c r="H47" s="13" t="s">
-        <v>382</v>
-      </c>
       <c r="I47" s="13">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="J47" s="14" t="s">
-        <v>856</v>
+        <v>210</v>
       </c>
       <c r="K47" s="14" t="s">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="L47" s="14" t="s">
-        <v>374</v>
+        <v>62</v>
       </c>
       <c r="M47" s="14" t="s">
-        <v>587</v>
+        <v>620</v>
       </c>
       <c r="N47" s="12" cm="1">
         <f t="array" ref="N47">_xlfn.IFS(B47="Freshwater",1,B47="Brackish",2,B47="Seawater",3)</f>
@@ -8556,227 +8683,227 @@
       </c>
       <c r="O47" s="12" cm="1">
         <f t="array" ref="O47">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B47)*('Fish Type'!C:C=C47),'Fish Type'!A:A)</f>
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P47" s="12" cm="1">
         <f t="array" ref="P47">_xlfn.IFS(D47="Common",1,D47="Uncommon",2,D47="Rare",3,D47="Legendary",4,D47="Mythical",5,D47="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Walleye',28,1,625,1.2,9,12.5,80,'Walleyes are largely olive and gold in color. The upper side of a walleye is olive, grading into a golden hue on the flanks.'),</v>
+        <f>_xlfn.CONCAT("('",A47,"',",O47,",",P47,",",E47,",",F47,",",G47,",",H47,",",I47,",","'",J47,"'),")</f>
+        <v>('Long-ear Sunfish',34,2,450,0.2,0.8,9,24,'Unlike any other sunfish, this fish feeds more near the surface of the water targeting insects, crustaceans and even young sunfish.'),</v>
       </c>
     </row>
     <row r="48" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E48" s="13">
-        <v>660</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>200</v>
+        <v>350</v>
+      </c>
+      <c r="F48" s="13">
+        <v>15</v>
       </c>
       <c r="G48" s="13">
-        <v>4</v>
-      </c>
-      <c r="H48" s="13" t="s">
-        <v>384</v>
+        <v>40</v>
+      </c>
+      <c r="H48" s="13">
+        <v>90</v>
       </c>
       <c r="I48" s="13">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="J48" s="14" t="s">
-        <v>385</v>
+        <v>1164</v>
       </c>
       <c r="K48" s="14" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L48" s="14" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="M48" s="14" t="s">
-        <v>593</v>
+        <v>138</v>
       </c>
       <c r="N48" s="12" cm="1">
         <f t="array" ref="N48">_xlfn.IFS(B48="Freshwater",1,B48="Brackish",2,B48="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O48" s="12" cm="1">
         <f t="array" ref="O48">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B48)*('Fish Type'!C:C=C48),'Fish Type'!A:A)</f>
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="P48" s="12" cm="1">
         <f t="array" ref="P48">_xlfn.IFS(D48="Common",1,D48="Uncommon",2,D48="Rare",3,D48="Legendary",4,D48="Mythical",5,D48="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Sauger',28,1,660,0.9,4,10.5,56,'Saugers generally move upstream to spawn during Autumn, depending on where they are. They move downstream to their home locations from Summer after their spawning period is over.'),</v>
+        <f>_xlfn.CONCAT("('",A48,"',",O48,",",P48,",",E48,",",F48,",",G48,",",H48,",",I48,",","'",J48,"'),")</f>
+        <v>('Longfin Tuna',36,2,350,15,40,90,150,'The longfin tuna has a streamlined, fusiform body with a conical snout, a large mouth, and big eyes. Its body is dark blue above, shades of silvery white ventrally, and covered by small scales.'),</v>
       </c>
     </row>
     <row r="49" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E49" s="13">
-        <v>425</v>
+        <v>585</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="13">
-        <v>2</v>
-      </c>
-      <c r="H49" s="13" t="s">
-        <v>387</v>
+        <v>399</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="H49" s="13">
+        <v>60</v>
       </c>
       <c r="I49" s="13">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K49" s="14" t="s">
-        <v>201</v>
+        <v>53</v>
       </c>
       <c r="L49" s="14" t="s">
-        <v>55</v>
+        <v>397</v>
       </c>
       <c r="M49" s="14" t="s">
-        <v>594</v>
+        <v>558</v>
       </c>
       <c r="N49" s="12" cm="1">
         <f t="array" ref="N49">_xlfn.IFS(B49="Freshwater",1,B49="Brackish",2,B49="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" s="12" cm="1">
         <f t="array" ref="O49">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B49)*('Fish Type'!C:C=C49),'Fish Type'!A:A)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P49" s="12" cm="1">
         <f t="array" ref="P49">_xlfn.IFS(D49="Common",1,D49="Uncommon",2,D49="Rare",3,D49="Legendary",4,D49="Mythical",5,D49="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q49" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Yellow Perch',28,1,425,0.5,2,10.2,50,'The yellow perch has an elongate, laterally compressed body with a subterminal mouth and a relatively long but blunt snout, which is surpassed in length by the lower jaw.'),</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A49,"',",O49,",",P49,",",E49,",",F49,",",G49,",",H49,",",I49,",","'",J49,"'),")</f>
+        <v>('Mangrove Jack',32,1,585,2.3,13.5,60,150,'Coloration of the Mangrove Jack ranges from burnt orange to copper, to bronze, and dark reddish-brown, depending on its age and environment.'),</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>381</v>
+        <v>264</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E50" s="13">
-        <v>275</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="G50" s="13">
-        <v>15</v>
+        <v>300</v>
+      </c>
+      <c r="F50" s="13">
+        <v>1</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>282</v>
       </c>
       <c r="H50" s="13">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I50" s="13">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>390</v>
+        <v>337</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L50" s="14" t="s">
-        <v>346</v>
+        <v>158</v>
       </c>
       <c r="M50" s="14" t="s">
-        <v>614</v>
+        <v>132</v>
       </c>
       <c r="N50" s="12" cm="1">
         <f t="array" ref="N50">_xlfn.IFS(B50="Freshwater",1,B50="Brackish",2,B50="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="12" cm="1">
         <f t="array" ref="O50">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B50)*('Fish Type'!C:C=C50),'Fish Type'!A:A)</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="P50" s="12" cm="1">
         <f t="array" ref="P50">_xlfn.IFS(D50="Common",1,D50="Uncommon",2,D50="Rare",3,D50="Legendary",4,D50="Mythical",5,D50="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q50" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Pikeperch',28,2,275,1.2,15,25,100,'The Pikeperch is the largest member of the perch family. The upper part of its body is green-brown in colour, and this extends onto the sides as dark vertical bars.'),</v>
+        <f>_xlfn.CONCAT("('",A50,"',",O50,",",P50,",",E50,",",F50,",",G50,",",H50,",",I50,",","'",J50,"'),")</f>
+        <v>('Marble Goby',20,2,300,1,7.5,10,65,'It is a highly popular fish among rich families, said to be best eaten after a childbirth or Chirurgy.'),</v>
       </c>
     </row>
     <row r="51" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
-        <v>391</v>
+        <v>161</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>381</v>
+        <v>22</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E51" s="13">
-        <v>300</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="H51" s="13" t="s">
-        <v>392</v>
+        <v>375</v>
+      </c>
+      <c r="F51" s="13">
+        <v>5</v>
+      </c>
+      <c r="G51" s="13">
+        <v>30</v>
+      </c>
+      <c r="H51" s="13">
+        <v>30</v>
       </c>
       <c r="I51" s="13">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="J51" s="14" t="s">
-        <v>857</v>
+        <v>164</v>
       </c>
       <c r="K51" s="14" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="L51" s="14" t="s">
-        <v>288</v>
+        <v>158</v>
       </c>
       <c r="M51" s="14" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="N51" s="12" cm="1">
         <f t="array" ref="N51">_xlfn.IFS(B51="Freshwater",1,B51="Brackish",2,B51="Seawater",3)</f>
@@ -8784,170 +8911,170 @@
       </c>
       <c r="O51" s="12" cm="1">
         <f t="array" ref="O51">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B51)*('Fish Type'!C:C=C51),'Fish Type'!A:A)</f>
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="P51" s="12" cm="1">
         <f t="array" ref="P51">_xlfn.IFS(D51="Common",1,D51="Uncommon",2,D51="Rare",3,D51="Legendary",4,D51="Mythical",5,D51="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q51" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Ruffe',28,2,300,0.1,0.2,5.2,25,'It is a very aggressive fish for its size. The ruffe also has a large, spiny upper fin which is likely distasteful to its predators'),</v>
+        <f>_xlfn.CONCAT("('",A51,"',",O51,",",P51,",",E51,",",F51,",",G51,",",H51,",",I51,",","'",J51,"'),")</f>
+        <v>('Marbled Trout',35,2,375,5,30,30,120,'The marble trout has a long, cylindrical body, slightly compressed laterally, with a large head. '),</v>
       </c>
     </row>
     <row r="52" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
-        <v>370</v>
+        <v>422</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>371</v>
+        <v>417</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E52" s="13">
-        <v>825</v>
-      </c>
-      <c r="F52" s="13">
-        <v>10</v>
+        <v>230</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>204</v>
       </c>
       <c r="G52" s="13">
-        <v>30</v>
-      </c>
-      <c r="H52" s="13">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="H52" s="13" t="s">
+        <v>424</v>
       </c>
       <c r="I52" s="13">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="J52" s="14" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="K52" s="14" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="L52" s="14" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="M52" s="14" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="N52" s="12" cm="1">
         <f t="array" ref="N52">_xlfn.IFS(B52="Freshwater",1,B52="Brackish",2,B52="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O52" s="12" cm="1">
         <f t="array" ref="O52">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B52)*('Fish Type'!C:C=C52),'Fish Type'!A:A)</f>
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="P52" s="12" cm="1">
         <f t="array" ref="P52">_xlfn.IFS(D52="Common",1,D52="Uncommon",2,D52="Rare",3,D52="Legendary",4,D52="Mythical",5,D52="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q52" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Northern Pike',29,1,825,10,30,30,150,'Northern pike are most often olive green, shading from yellow to white along the belly. The flank is marked with short, light bar-like spots and a few to many dark spots on the fins.'),</v>
+        <f>_xlfn.CONCAT("('",A52,"',",O52,",",P52,",",E52,",",F52,",",G52,",",H52,",",I52,",","'",J52,"'),")</f>
+        <v>('Masked Grouper',21,2,230,0.3,2,9.5,45,'The masked grouper has an oblong, rather compressed body, with the gill cover having a central spine which is located at one-third of the gap between the lower and upper spines.'),</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E53" s="13">
-        <v>725</v>
+        <v>625</v>
       </c>
       <c r="F53" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="G53" s="13" t="s">
-        <v>173</v>
+      <c r="G53" s="13">
+        <v>20</v>
       </c>
       <c r="H53" s="13">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="I53" s="13">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="J53" s="14" t="s">
-        <v>864</v>
+        <v>394</v>
       </c>
       <c r="K53" s="14" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="L53" s="14" t="s">
         <v>374</v>
       </c>
       <c r="M53" s="14" t="s">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="N53" s="12" cm="1">
         <f t="array" ref="N53">_xlfn.IFS(B53="Freshwater",1,B53="Brackish",2,B53="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" s="12" cm="1">
         <f t="array" ref="O53">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B53)*('Fish Type'!C:C=C53),'Fish Type'!A:A)</f>
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="P53" s="12" cm="1">
         <f t="array" ref="P53">_xlfn.IFS(D53="Common",1,D53="Uncommon",2,D53="Rare",3,D53="Legendary",4,D53="Mythical",5,D53="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q53" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Southern Pike',29,1,725,1.2,4.5,40,79,'The southern pike has a distinctive, dark, chain-like pattern on its greenish sides. There is a vertical dark marking underneath the eye'),</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A53,"',",O53,",",P53,",",E53,",",F53,",",G53,",",H53,",",I53,",","'",J53,"'),")</f>
+        <v>('Milkfish',24,1,625,1.2,20,90,180,'The milkfish is an important seafood in Seran and some Ourea places. This fish is infamous for being much bonier than other food fishes.'),</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
-        <v>375</v>
+        <v>18</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>371</v>
+        <v>13</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E54" s="13">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F54" s="13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G54" s="13">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H54" s="13">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I54" s="13">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="J54" s="14" t="s">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="K54" s="14" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="L54" s="14" t="s">
-        <v>57</v>
+        <v>242</v>
       </c>
       <c r="M54" s="14" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="N54" s="12" cm="1">
         <f t="array" ref="N54">_xlfn.IFS(B54="Freshwater",1,B54="Brackish",2,B54="Seawater",3)</f>
@@ -8955,56 +9082,56 @@
       </c>
       <c r="O54" s="12" cm="1">
         <f t="array" ref="O54">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B54)*('Fish Type'!C:C=C54),'Fish Type'!A:A)</f>
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="P54" s="12" cm="1">
         <f t="array" ref="P54">_xlfn.IFS(D54="Common",1,D54="Uncommon",2,D54="Rare",3,D54="Legendary",4,D54="Mythical",5,D54="Event",6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q54" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Muskie',29,1,500,5,32,45,180,'Muskies are the top predator in any body of water where they occur, and they will eat larger prey than most other freshwater fish.'),</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A54,"',",O54,",",P54,",",E54,",",F54,",",G54,",",H54,",",I54,",","'",J54,"'),")</f>
+        <v>('Mrigal Carp',9,3,100,2,13,15,100,'This fish live in a lower water level and feeds on small insects and decomposed organic element.'),</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
-        <v>377</v>
+        <v>151</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>371</v>
+        <v>13</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E55" s="13">
-        <v>250</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="G55" s="13" t="s">
-        <v>27</v>
+        <v>700</v>
+      </c>
+      <c r="F55" s="13">
+        <v>2</v>
+      </c>
+      <c r="G55" s="13">
+        <v>5</v>
       </c>
       <c r="H55" s="13">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I55" s="13">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="J55" s="14" t="s">
-        <v>379</v>
+        <v>152</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="L55" s="14" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="M55" s="14" t="s">
-        <v>616</v>
+        <v>760</v>
       </c>
       <c r="N55" s="12" cm="1">
         <f t="array" ref="N55">_xlfn.IFS(B55="Freshwater",1,B55="Brackish",2,B55="Seawater",3)</f>
@@ -9012,56 +9139,56 @@
       </c>
       <c r="O55" s="12" cm="1">
         <f t="array" ref="O55">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B55)*('Fish Type'!C:C=C55),'Fish Type'!A:A)</f>
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="P55" s="12" cm="1">
         <f t="array" ref="P55">_xlfn.IFS(D55="Common",1,D55="Uncommon",2,D55="Rare",3,D55="Legendary",4,D55="Mythical",5,D55="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Redfin Pickerel',29,2,250,0.3,1.5,3,31,'The redfin pickerel is an ambush predator, lying in wait for unsuspecting prey animals to get within striking range.'),</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A55,"',",O55,",",P55,",",E55,",",F55,",",G55,",",H55,",",I55,",","'",J55,"'),")</f>
+        <v>('Mud Carp',9,1,700,2,5,20,74,'Mud Carp is considered to be inedible the first time people caught it, but after the great incident, this fish became popular.'),</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
-        <v>35</v>
+        <v>375</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>168</v>
+        <v>371</v>
       </c>
       <c r="D56" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E56" s="13">
-        <v>650</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>26</v>
+        <v>500</v>
+      </c>
+      <c r="F56" s="13">
+        <v>5</v>
       </c>
       <c r="G56" s="13">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H56" s="13">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I56" s="13">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="J56" s="14" t="s">
-        <v>37</v>
+        <v>376</v>
       </c>
       <c r="K56" s="14" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="L56" s="14" t="s">
-        <v>596</v>
+        <v>57</v>
       </c>
       <c r="M56" s="14" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="N56" s="12" cm="1">
         <f t="array" ref="N56">_xlfn.IFS(B56="Freshwater",1,B56="Brackish",2,B56="Seawater",3)</f>
@@ -9069,170 +9196,170 @@
       </c>
       <c r="O56" s="12" cm="1">
         <f t="array" ref="O56">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B56)*('Fish Type'!C:C=C56),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P56" s="12" cm="1">
         <f t="array" ref="P56">_xlfn.IFS(D56="Common",1,D56="Uncommon",2,D56="Rare",3,D56="Legendary",4,D56="Mythical",5,D56="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q56" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Bluegill',34,1,650,0.5,2,15,39,'This insect lover usually hide near a cover and ambush their prey.'),</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A56,"',",O56,",",P56,",",E56,",",F56,",",G56,",",H56,",",I56,",","'",J56,"'),")</f>
+        <v>('Muskie',29,1,500,5,32,45,180,'Muskies are the top predator in any body of water where they occur, and they will eat larger prey than most other freshwater fish.'),</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
-        <v>193</v>
+        <v>351</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>168</v>
+        <v>351</v>
       </c>
       <c r="D57" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E57" s="13">
-        <v>660</v>
+        <v>800</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="G57" s="13">
-        <v>1</v>
+        <v>212</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="H57" s="13">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I57" s="13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J57" s="14" t="s">
-        <v>195</v>
+        <v>852</v>
       </c>
       <c r="K57" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="L57" s="14" t="s">
-        <v>62</v>
+        <v>246</v>
       </c>
       <c r="M57" s="14" t="s">
-        <v>598</v>
+        <v>564</v>
       </c>
       <c r="N57" s="12" cm="1">
         <f t="array" ref="N57">_xlfn.IFS(B57="Freshwater",1,B57="Brackish",2,B57="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" s="12" cm="1">
         <f t="array" ref="O57">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B57)*('Fish Type'!C:C=C57),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="P57" s="12" cm="1">
         <f t="array" ref="P57">_xlfn.IFS(D57="Common",1,D57="Uncommon",2,D57="Rare",3,D57="Legendary",4,D57="Mythical",5,D57="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q57" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Pumpkinseed',34,1,660,0.4,1,10,28,'Pumpkinseeds have a body shaped much like a pumpkin seed with a vibrant orange, green, yellow, or blue body.'),</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A57,"',",O57,",",P57,",",E57,",",F57,",",G57,",",H57,",",I57,",","'",J57,"'),")</f>
+        <v>('Needlefish',27,1,800,0.1,0.5,3,30,'Needlefish are slender and have a single upper fin. Their most distinctive feature is their long, narrow beak, which bears multiple sharp teeth.'),</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
-        <v>199</v>
+        <v>330</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>168</v>
+        <v>267</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E58" s="13">
-        <v>670</v>
+        <v>350</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G58" s="13" t="s">
-        <v>200</v>
+        <v>212</v>
+      </c>
+      <c r="G58" s="13">
+        <v>1</v>
       </c>
       <c r="H58" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I58" s="13">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J58" s="14" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="L58" s="14" t="s">
-        <v>62</v>
+        <v>268</v>
       </c>
       <c r="M58" s="14" t="s">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="N58" s="12" cm="1">
         <f t="array" ref="N58">_xlfn.IFS(B58="Freshwater",1,B58="Brackish",2,B58="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="12" cm="1">
         <f t="array" ref="O58">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B58)*('Fish Type'!C:C=C58),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="P58" s="12" cm="1">
         <f t="array" ref="P58">_xlfn.IFS(D58="Common",1,D58="Uncommon",2,D58="Rare",3,D58="Legendary",4,D58="Mythical",5,D58="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q58" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Green Sunfish',34,1,670,0.2,0.9,7,30,'This fish is highly territorial and aggressive, local fishermen refered to its as a bullies of the water.'),</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A58,"',",O58,",",P58,",",E58,",",F58,",",G58,",",H58,",",I58,",","'",J58,"'),")</f>
+        <v>('Northern Archerfish',2,2,350,0.1,1,6,40,'The largest of the archerfish, sporting a deeper body and irregular dark markings. Its powerful water jets and impressive size make it a formidable hunter of mangrove shores.'),</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
-        <v>217</v>
+        <v>370</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>168</v>
+        <v>371</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E59" s="13">
-        <v>125</v>
-      </c>
-      <c r="F59" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G59" s="13" t="s">
-        <v>26</v>
+        <v>825</v>
+      </c>
+      <c r="F59" s="13">
+        <v>10</v>
+      </c>
+      <c r="G59" s="13">
+        <v>30</v>
       </c>
       <c r="H59" s="13">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I59" s="13">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="J59" s="14" t="s">
-        <v>218</v>
+        <v>372</v>
       </c>
       <c r="K59" s="14" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="L59" s="14" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
       <c r="M59" s="14" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="N59" s="12" cm="1">
         <f t="array" ref="N59">_xlfn.IFS(B59="Freshwater",1,B59="Brackish",2,B59="Seawater",3)</f>
@@ -9240,134 +9367,134 @@
       </c>
       <c r="O59" s="12" cm="1">
         <f t="array" ref="O59">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B59)*('Fish Type'!C:C=C59),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P59" s="12" cm="1">
         <f t="array" ref="P59">_xlfn.IFS(D59="Common",1,D59="Uncommon",2,D59="Rare",3,D59="Legendary",4,D59="Mythical",5,D59="Event",6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Pocket Sunfish',34,3,125,0.1,0.5,5,8,'A tiny fish that can fit into a fisherman's pocket, it has ten vertical stripes visible along its dark body.'),</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A59,"',",O59,",",P59,",",E59,",",F59,",",G59,",",H59,",",I59,",","'",J59,"'),")</f>
+        <v>('Northern Pike',29,1,825,10,30,30,150,'Northern pike are most often olive green, shading from yellow to white along the belly. The flank is marked with short, light bar-like spots and a few to many dark spots on the fins.'),</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
-        <v>196</v>
+        <v>413</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>168</v>
+        <v>396</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E60" s="13">
-        <v>300</v>
-      </c>
-      <c r="F60" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G60" s="13" t="s">
-        <v>27</v>
+        <v>900</v>
+      </c>
+      <c r="F60" s="13">
+        <v>2</v>
+      </c>
+      <c r="G60" s="13">
+        <v>23</v>
       </c>
       <c r="H60" s="13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I60" s="13">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="J60" s="14" t="s">
-        <v>198</v>
+        <v>415</v>
       </c>
       <c r="K60" s="14" t="s">
-        <v>166</v>
+        <v>63</v>
       </c>
       <c r="L60" s="14" t="s">
-        <v>55</v>
+        <v>414</v>
       </c>
       <c r="M60" s="14" t="s">
-        <v>617</v>
+        <v>575</v>
       </c>
       <c r="N60" s="12" cm="1">
         <f t="array" ref="N60">_xlfn.IFS(B60="Freshwater",1,B60="Brackish",2,B60="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O60" s="12" cm="1">
         <f t="array" ref="O60">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B60)*('Fish Type'!C:C=C60),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P60" s="12" cm="1">
         <f t="array" ref="P60">_xlfn.IFS(D60="Common",1,D60="Uncommon",2,D60="Rare",3,D60="Legendary",4,D60="Mythical",5,D60="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Redear Sunfish',34,2,300,0.2,1.5,20,44,'Also widely known as the shellcracker, this fish's main diet is snails. These fish meander along lakebeds, seeking and cracking open snails and other shelled creatures.'),</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A60,"',",O60,",",P60,",",E60,",",F60,",",G60,",",H60,",",I60,",","'",J60,"'),")</f>
+        <v>('Northern Red Snapper',33,1,900,2,23,23,88,'They eat almost anything, but prefer small fish and crustaceans. They can be caught on both live and cut bait'),</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
-        <v>203</v>
+        <v>284</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>38</v>
+        <v>181</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>168</v>
+        <v>281</v>
       </c>
       <c r="D61" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E61" s="13">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="F61" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G61" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="G61" s="13" t="s">
-        <v>31</v>
-      </c>
       <c r="H61" s="13">
+        <v>2</v>
+      </c>
+      <c r="I61" s="13">
         <v>10</v>
       </c>
-      <c r="I61" s="13">
-        <v>30</v>
-      </c>
       <c r="J61" s="14" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="L61" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M61" s="14" t="s">
-        <v>618</v>
+        <v>556</v>
       </c>
       <c r="N61" s="12" cm="1">
         <f t="array" ref="N61">_xlfn.IFS(B61="Freshwater",1,B61="Brackish",2,B61="Seawater",3)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" s="12" cm="1">
         <f t="array" ref="O61">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B61)*('Fish Type'!C:C=C61),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="P61" s="12" cm="1">
         <f t="array" ref="P61">_xlfn.IFS(D61="Common",1,D61="Uncommon",2,D61="Rare",3,D61="Legendary",4,D61="Mythical",5,D61="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q61" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Warmouth',34,2,375,0.3,1.1,10,30,'The Warmouth is an aggressive and hardy fish that can survive in streams with low oxygen level.'),</v>
+        <f>_xlfn.CONCAT("('",A61,"',",O61,",",P61,",",E61,",",F61,",",G61,",",H61,",",I61,",","'",J61,"'),")</f>
+        <v>('Orange Chromide',13,2,300,0.1,0.3,2,10,'A vivid orange cichlid that thrives in brackish lagoons and estuaries, where it grazes on algae and hunts tiny aquatic creatures among submerged vegetation.'),</v>
       </c>
     </row>
     <row r="62" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="15" t="s">
-        <v>206</v>
+      <c r="A62" s="12" t="s">
+        <v>211</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>38</v>
@@ -9379,31 +9506,31 @@
         <v>16</v>
       </c>
       <c r="E62" s="13">
-        <v>425</v>
+        <v>375</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H62" s="13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I62" s="13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J62" s="14" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="L62" s="14" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
       <c r="M62" s="14" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="N62" s="12" cm="1">
         <f t="array" ref="N62">_xlfn.IFS(B62="Freshwater",1,B62="Brackish",2,B62="Seawater",3)</f>
@@ -9418,49 +9545,49 @@
         <v>2</v>
       </c>
       <c r="Q62" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Redbreast Sunfish',34,2,425,0.2,0.8,10,30,'This fish becomes more aggressive when winter comes and striking almost anything that moving near them.'),</v>
+        <f>_xlfn.CONCAT("('",A62,"',",O62,",",P62,",",E62,",",F62,",",G62,",",H62,",",I62,",","'",J62,"'),")</f>
+        <v>('Orangespotted Sunfish',34,2,375,0.1,0.6,8,15,'This fish prefers vegetated areas in sluggish backwaters or lakes, and can also be found in turbid rivers.'),</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="15" t="s">
-        <v>884</v>
+      <c r="A63" s="12" t="s">
+        <v>389</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>168</v>
+        <v>381</v>
       </c>
       <c r="D63" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E63" s="13">
-        <v>450</v>
+        <v>275</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G63" s="13" t="s">
-        <v>207</v>
+        <v>255</v>
+      </c>
+      <c r="G63" s="13">
+        <v>15</v>
       </c>
       <c r="H63" s="13">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I63" s="13">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="J63" s="14" t="s">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="K63" s="14" t="s">
         <v>166</v>
       </c>
       <c r="L63" s="14" t="s">
-        <v>62</v>
+        <v>346</v>
       </c>
       <c r="M63" s="14" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="N63" s="12" cm="1">
         <f t="array" ref="N63">_xlfn.IFS(B63="Freshwater",1,B63="Brackish",2,B63="Seawater",3)</f>
@@ -9468,20 +9595,20 @@
       </c>
       <c r="O63" s="12" cm="1">
         <f t="array" ref="O63">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B63)*('Fish Type'!C:C=C63),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="P63" s="12" cm="1">
         <f t="array" ref="P63">_xlfn.IFS(D63="Common",1,D63="Uncommon",2,D63="Rare",3,D63="Legendary",4,D63="Mythical",5,D63="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q63" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Long-ear Sunfish',34,2,450,0.2,0.8,9,24,'Unlike any other sunfish, this fish feeds more near the surface of the water targeting insects, crustaceans and even young sunfish.'),</v>
+        <f>_xlfn.CONCAT("('",A63,"',",O63,",",P63,",",E63,",",F63,",",G63,",",H63,",",I63,",","'",J63,"'),")</f>
+        <v>('Pikeperch',28,2,275,1.2,15,25,100,'The Pikeperch is the largest member of the perch family. The upper part of its body is green-brown in colour, and this extends onto the sides as dark vertical bars.'),</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>38</v>
@@ -9490,34 +9617,34 @@
         <v>168</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E64" s="13">
-        <v>375</v>
+        <v>125</v>
       </c>
       <c r="F64" s="13" t="s">
         <v>212</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="H64" s="13">
+        <v>5</v>
+      </c>
+      <c r="I64" s="13">
         <v>8</v>
       </c>
-      <c r="I64" s="13">
-        <v>15</v>
-      </c>
       <c r="J64" s="14" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="L64" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M64" s="14" t="s">
-        <v>621</v>
+        <v>581</v>
       </c>
       <c r="N64" s="12" cm="1">
         <f t="array" ref="N64">_xlfn.IFS(B64="Freshwater",1,B64="Brackish",2,B64="Seawater",3)</f>
@@ -9529,52 +9656,52 @@
       </c>
       <c r="P64" s="12" cm="1">
         <f t="array" ref="P64">_xlfn.IFS(D64="Common",1,D64="Uncommon",2,D64="Rare",3,D64="Legendary",4,D64="Mythical",5,D64="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q64" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Orangespotted Sunfish',34,2,375,0.1,0.6,8,15,'This fish prefers vegetated areas in sluggish backwaters or lakes, and can also be found in turbid rivers.'),</v>
+        <f>_xlfn.CONCAT("('",A64,"',",O64,",",P64,",",E64,",",F64,",",G64,",",H64,",",I64,",","'",J64,"'),")</f>
+        <v>('Pocket Sunfish',34,3,125,0.1,0.5,5,8,'A tiny fish that can fit into a fisherman's pocket, it has ten vertical stripes visible along its dark body.'),</v>
       </c>
     </row>
     <row r="65" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A65" s="12" t="s">
-        <v>215</v>
+        <v>321</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>168</v>
+        <v>22</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E65" s="13">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>212</v>
+        <v>26</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H65" s="13">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I65" s="13">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="J65" s="14" t="s">
-        <v>216</v>
+        <v>322</v>
       </c>
       <c r="K65" s="14" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L65" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="M65" s="14" t="s">
-        <v>622</v>
+        <v>40</v>
       </c>
       <c r="N65" s="12" cm="1">
         <f t="array" ref="N65">_xlfn.IFS(B65="Freshwater",1,B65="Brackish",2,B65="Seawater",3)</f>
@@ -9582,56 +9709,56 @@
       </c>
       <c r="O65" s="12" cm="1">
         <f t="array" ref="O65">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B65)*('Fish Type'!C:C=C65),'Fish Type'!A:A)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P65" s="12" cm="1">
         <f t="array" ref="P65">_xlfn.IFS(D65="Common",1,D65="Uncommon",2,D65="Rare",3,D65="Legendary",4,D65="Mythical",5,D65="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q65" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Roundel Sunfish',34,2,230,0.1,0.5,8,15,'Its deep, rounded body is said to resemble the ancient roundel coins once traded across the continent before the dragons era.'),</v>
+        <f>_xlfn.CONCAT("('",A65,"',",O65,",",P65,",",E65,",",F65,",",G65,",",H65,",",I65,",","'",J65,"'),")</f>
+        <v>('Prasinos Cutthroat Trout',35,3,75,0.5,1.1,15,46,'This trout only live on the creek. Prasinos have a purple coloration and have some black spot along their body'),</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D66" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E66" s="13">
-        <v>900</v>
-      </c>
-      <c r="F66" s="13">
-        <v>3</v>
+        <v>660</v>
+      </c>
+      <c r="F66" s="13" t="s">
+        <v>194</v>
       </c>
       <c r="G66" s="13">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H66" s="13">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I66" s="13">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="J66" s="14" t="s">
-        <v>28</v>
+        <v>195</v>
       </c>
       <c r="K66" s="14" t="s">
-        <v>63</v>
+        <v>172</v>
       </c>
       <c r="L66" s="14" t="s">
-        <v>354</v>
+        <v>62</v>
       </c>
       <c r="M66" s="14" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="N66" s="12" cm="1">
         <f t="array" ref="N66">_xlfn.IFS(B66="Freshwater",1,B66="Brackish",2,B66="Seawater",3)</f>
@@ -9639,20 +9766,20 @@
       </c>
       <c r="O66" s="12" cm="1">
         <f t="array" ref="O66">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B66)*('Fish Type'!C:C=C66),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P66" s="12" cm="1">
         <f t="array" ref="P66">_xlfn.IFS(D66="Common",1,D66="Uncommon",2,D66="Rare",3,D66="Legendary",4,D66="Mythical",5,D66="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q66" s="5" t="str">
-        <f t="shared" si="0"/>
-        <v>('Rainbow Trout',35,1,900,3,14,20,76,'Fish with a silvery body, and purple, pink and bluish streak down its flank'),</v>
+        <f>_xlfn.CONCAT("('",A66,"',",O66,",",P66,",",E66,",",F66,",",G66,",",H66,",",I66,",","'",J66,"'),")</f>
+        <v>('Pumpkinseed',34,1,660,0.4,1,10,28,'Pumpkinseeds have a body shaped much like a pumpkin seed with a vibrant orange, green, yellow, or blue body.'),</v>
       </c>
     </row>
     <row r="67" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
-        <v>324</v>
+        <v>25</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>38</v>
@@ -9664,31 +9791,31 @@
         <v>14</v>
       </c>
       <c r="E67" s="13">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="F67" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G67" s="13">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H67" s="13">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I67" s="13">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="J67" s="14" t="s">
-        <v>327</v>
+        <v>28</v>
       </c>
       <c r="K67" s="14" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="L67" s="14" t="s">
-        <v>62</v>
+        <v>354</v>
       </c>
       <c r="M67" s="14" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N67" s="12" cm="1">
         <f t="array" ref="N67">_xlfn.IFS(B67="Freshwater",1,B67="Brackish",2,B67="Seawater",3)</f>
@@ -9703,88 +9830,88 @@
         <v>1</v>
       </c>
       <c r="Q67" s="5" t="str">
-        <f t="shared" ref="Q67:Q101" si="1">_xlfn.CONCAT("('",A67,"',",O67,",",P67,",",E67,",",F67,",",G67,",",H67,",",I67,",","'",J67,"'),")</f>
-        <v>('Hvitar Trout',35,1,750,1,2,17,55,'Hvitar Trout have a yellow body, and their upper body covered with a numerous small dark spot'),</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A67,"',",O67,",",P67,",",E67,",",F67,",",G67,",",H67,",",I67,",","'",J67,"'),")</f>
+        <v>('Rainbow Trout',35,1,900,3,14,20,76,'Fish with a silvery body, and purple, pink and bluish streak down its flank'),</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E68" s="13">
-        <v>975</v>
-      </c>
-      <c r="F68" s="13">
+        <v>850</v>
+      </c>
+      <c r="F68" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="G68" s="13">
         <v>10</v>
       </c>
-      <c r="G68" s="13">
-        <v>46</v>
-      </c>
       <c r="H68" s="13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I68" s="13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J68" s="14" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K68" s="14" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="L68" s="14" t="s">
-        <v>600</v>
+        <v>62</v>
       </c>
       <c r="M68" s="14" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
       <c r="N68" s="12" cm="1">
         <f t="array" ref="N68">_xlfn.IFS(B68="Freshwater",1,B68="Brackish",2,B68="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O68" s="12" cm="1">
         <f t="array" ref="O68">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B68)*('Fish Type'!C:C=C68),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="P68" s="12" cm="1">
         <f t="array" ref="P68">_xlfn.IFS(D68="Common",1,D68="Uncommon",2,D68="Rare",3,D68="Legendary",4,D68="Mythical",5,D68="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q68" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Lake Trout',35,1,975,10,46,25,130,'Lake trout covered in light beige or white spots all over its olive-grey body.'),</v>
+        <f>_xlfn.CONCAT("('",A68,"',",O68,",",P68,",",E68,",",F68,",",G68,",",H68,",",I68,",","'",J68,"'),")</f>
+        <v>('Red Seabream',6,1,850,0.75,10,20,120,'The body is oblong and laterally flattened, with the jaws protruding slightly forward. The pectoral fins are long and slender, reaching nearly half of the total length.'),</v>
       </c>
     </row>
     <row r="69" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="12" t="s">
-        <v>29</v>
+      <c r="A69" s="15" t="s">
+        <v>206</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E69" s="13">
-        <v>85</v>
+        <v>425</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G69" s="13">
-        <v>3</v>
+        <v>197</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>207</v>
       </c>
       <c r="H69" s="13">
         <v>10</v>
@@ -9793,16 +9920,16 @@
         <v>30</v>
       </c>
       <c r="J69" s="14" t="s">
-        <v>30</v>
+        <v>209</v>
       </c>
       <c r="K69" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L69" s="14" t="s">
-        <v>62</v>
+        <v>208</v>
       </c>
       <c r="M69" s="14" t="s">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="N69" s="12" cm="1">
         <f t="array" ref="N69">_xlfn.IFS(B69="Freshwater",1,B69="Brackish",2,B69="Seawater",3)</f>
@@ -9810,56 +9937,56 @@
       </c>
       <c r="O69" s="12" cm="1">
         <f t="array" ref="O69">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B69)*('Fish Type'!C:C=C69),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P69" s="12" cm="1">
         <f t="array" ref="P69">_xlfn.IFS(D69="Common",1,D69="Uncommon",2,D69="Rare",3,D69="Legendary",4,D69="Mythical",5,D69="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q69" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Aurora Trout',35,3,85,1.5,3,10,30,'Aurora trout can be differentiated by its coloration, grading from magenta hue to nearly orange along the belly.'),</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A69,"',",O69,",",P69,",",E69,",",F69,",",G69,",",H69,",",I69,",","'",J69,"'),")</f>
+        <v>('Redbreast Sunfish',34,2,425,0.2,0.8,10,30,'This fish becomes more aggressive when winter comes and striking almost anything that moving near them.'),</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
-        <v>321</v>
+        <v>196</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E70" s="13">
-        <v>75</v>
+        <v>300</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H70" s="13">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I70" s="13">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J70" s="14" t="s">
-        <v>322</v>
+        <v>198</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="L70" s="14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M70" s="14" t="s">
-        <v>40</v>
+        <v>617</v>
       </c>
       <c r="N70" s="12" cm="1">
         <f t="array" ref="N70">_xlfn.IFS(B70="Freshwater",1,B70="Brackish",2,B70="Seawater",3)</f>
@@ -9867,56 +9994,56 @@
       </c>
       <c r="O70" s="12" cm="1">
         <f t="array" ref="O70">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B70)*('Fish Type'!C:C=C70),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P70" s="12" cm="1">
         <f t="array" ref="P70">_xlfn.IFS(D70="Common",1,D70="Uncommon",2,D70="Rare",3,D70="Legendary",4,D70="Mythical",5,D70="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q70" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Prasinos Cutthroat Trout',35,3,75,0.5,1.1,15,46,'This trout only live on the creek. Prasinos have a purple coloration and have some black spot along their body'),</v>
+        <f>_xlfn.CONCAT("('",A70,"',",O70,",",P70,",",E70,",",F70,",",G70,",",H70,",",I70,",","'",J70,"'),")</f>
+        <v>('Redear Sunfish',34,2,300,0.2,1.5,20,44,'Also widely known as the shellcracker, this fish's main diet is snails. These fish meander along lakebeds, seeking and cracking open snails and other shelled creatures.'),</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
-        <v>160</v>
+        <v>377</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>22</v>
+        <v>371</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E71" s="13">
-        <v>100</v>
-      </c>
-      <c r="F71" s="13">
-        <v>1</v>
-      </c>
-      <c r="G71" s="13">
-        <v>5</v>
+        <v>250</v>
+      </c>
+      <c r="F71" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G71" s="13" t="s">
+        <v>27</v>
       </c>
       <c r="H71" s="13">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="I71" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J71" s="14" t="s">
-        <v>163</v>
+        <v>379</v>
       </c>
       <c r="K71" s="14" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L71" s="14" t="s">
-        <v>60</v>
+        <v>378</v>
       </c>
       <c r="M71" s="14" t="s">
-        <v>583</v>
+        <v>616</v>
       </c>
       <c r="N71" s="12" cm="1">
         <f t="array" ref="N71">_xlfn.IFS(B71="Freshwater",1,B71="Brackish",2,B71="Seawater",3)</f>
@@ -9924,113 +10051,113 @@
       </c>
       <c r="O71" s="12" cm="1">
         <f t="array" ref="O71">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B71)*('Fish Type'!C:C=C71),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P71" s="12" cm="1">
         <f t="array" ref="P71">_xlfn.IFS(D71="Common",1,D71="Uncommon",2,D71="Rare",3,D71="Legendary",4,D71="Mythical",5,D71="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q71" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Golden Trout',35,3,100,1,5,15,30,'Every first Golden Trout that is caught that day needs to be given to the royal family.'),</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A71,"',",O71,",",P71,",",E71,",",F71,",",G71,",",H71,",",I71,",","'",J71,"'),")</f>
+        <v>('Redfin Pickerel',29,2,250,0.3,1.5,3,31,'The redfin pickerel is an ambush predator, lying in wait for unsuspecting prey animals to get within striking range.'),</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
-        <v>21</v>
+        <v>416</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>22</v>
+        <v>417</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E72" s="13">
-        <v>250</v>
-      </c>
-      <c r="F72" s="13">
-        <v>2</v>
-      </c>
-      <c r="G72" s="13" t="s">
-        <v>23</v>
+        <v>825</v>
+      </c>
+      <c r="F72" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" s="13">
+        <v>15</v>
       </c>
       <c r="H72" s="13">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I72" s="13">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J72" s="14" t="s">
-        <v>24</v>
+        <v>418</v>
       </c>
       <c r="K72" s="14" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="L72" s="14" t="s">
-        <v>55</v>
+        <v>409</v>
       </c>
       <c r="M72" s="14" t="s">
-        <v>623</v>
+        <v>565</v>
       </c>
       <c r="N72" s="12" cm="1">
         <f t="array" ref="N72">_xlfn.IFS(B72="Freshwater",1,B72="Brackish",2,B72="Seawater",3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O72" s="12" cm="1">
         <f t="array" ref="O72">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B72)*('Fish Type'!C:C=C72),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="P72" s="12" cm="1">
         <f t="array" ref="P72">_xlfn.IFS(D72="Common",1,D72="Uncommon",2,D72="Rare",3,D72="Legendary",4,D72="Mythical",5,D72="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q72" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Brook Trout',35,2,250,2,6.5,20,61,'Brook trout also called Speckled trout has a green olive body with a yellow spot all over its body.'),</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A72,"',",O72,",",P72,",",E72,",",F72,",",G72,",",H72,",",I72,",","'",J72,"'),")</f>
+        <v>('Redmouth Grouper',21,1,825,0.9,15,15,60,'The redmouth grouper is laterally compressed and oval-shaped with a relatively deep body, which is around half of the standard length, and a large head.'),</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
-        <v>1032</v>
+        <v>248</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>22</v>
+        <v>220</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E73" s="13">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="F73" s="13">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G73" s="13">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="H73" s="13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I73" s="13">
-        <v>45</v>
+        <v>180</v>
       </c>
       <c r="J73" s="14" t="s">
-        <v>159</v>
+        <v>855</v>
       </c>
       <c r="K73" s="14" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="L73" s="14" t="s">
-        <v>243</v>
+        <v>59</v>
       </c>
       <c r="M73" s="14" t="s">
-        <v>44</v>
+        <v>612</v>
       </c>
       <c r="N73" s="12" cm="1">
         <f t="array" ref="N73">_xlfn.IFS(B73="Freshwater",1,B73="Brackish",2,B73="Seawater",3)</f>
@@ -10038,56 +10165,56 @@
       </c>
       <c r="O73" s="12" cm="1">
         <f t="array" ref="O73">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B73)*('Fish Type'!C:C=C73),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="P73" s="12" cm="1">
         <f t="array" ref="P73">_xlfn.IFS(D73="Common",1,D73="Uncommon",2,D73="Rare",3,D73="Legendary",4,D73="Mythical",5,D73="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q73" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Clearwater Cutthroat Trout',35,2,305,1,2,20,45,'Its neck has a bright red coloration, which makes it look like a slash wound; that's why it was called a Cutthroat Trout.'),</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A73,"',",O73,",",P73,",",E73,",",F73,",",G73,",",H73,",",I73,",","'",J73,"'),")</f>
+        <v>('Redtail Catfish',11,2,250,20,80,23,180,'These colorful large catfishes have a brownish back, with yellow sides, and characteristic orange-red upper fin and caudal fin'),</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E74" s="13">
-        <v>201</v>
-      </c>
-      <c r="F74" s="13">
-        <v>1</v>
-      </c>
-      <c r="G74" s="13">
-        <v>3</v>
+        <v>230</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="H74" s="13">
+        <v>8</v>
+      </c>
+      <c r="I74" s="13">
         <v>15</v>
       </c>
-      <c r="I74" s="13">
-        <v>61</v>
-      </c>
       <c r="J74" s="14" t="s">
-        <v>326</v>
+        <v>216</v>
       </c>
       <c r="K74" s="14" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="L74" s="14" t="s">
-        <v>243</v>
+        <v>55</v>
       </c>
       <c r="M74" s="14" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="N74" s="12" cm="1">
         <f t="array" ref="N74">_xlfn.IFS(B74="Freshwater",1,B74="Brackish",2,B74="Seawater",3)</f>
@@ -10095,56 +10222,56 @@
       </c>
       <c r="O74" s="12" cm="1">
         <f t="array" ref="O74">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B74)*('Fish Type'!C:C=C74),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P74" s="12" cm="1">
         <f t="array" ref="P74">_xlfn.IFS(D74="Common",1,D74="Uncommon",2,D74="Rare",3,D74="Legendary",4,D74="Mythical",5,D74="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q74" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Yakad Trout',35,2,201,1,3,15,61,'Yakad Trout can be identified by its distinctive yellowish-gold color, with a golden belly. The top of its head and back are a dark olive color.'),</v>
+        <f>_xlfn.CONCAT("('",A74,"',",O74,",",P74,",",E74,",",F74,",",G74,",",H74,",",I74,",","'",J74,"'),")</f>
+        <v>('Roundel Sunfish',34,2,230,0.1,0.5,8,15,'Its deep, rounded body is said to resemble the ancient roundel coins once traded across the continent before the dragons era.'),</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A75" s="12" t="s">
-        <v>161</v>
+        <v>391</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>22</v>
+        <v>381</v>
       </c>
       <c r="D75" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E75" s="13">
-        <v>375</v>
-      </c>
-      <c r="F75" s="13">
-        <v>5</v>
-      </c>
-      <c r="G75" s="13">
-        <v>30</v>
-      </c>
-      <c r="H75" s="13">
-        <v>30</v>
+        <v>300</v>
+      </c>
+      <c r="F75" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G75" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="H75" s="13" t="s">
+        <v>392</v>
       </c>
       <c r="I75" s="13">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="J75" s="14" t="s">
-        <v>164</v>
+        <v>857</v>
       </c>
       <c r="K75" s="14" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="L75" s="14" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="M75" s="14" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="N75" s="12" cm="1">
         <f t="array" ref="N75">_xlfn.IFS(B75="Freshwater",1,B75="Brackish",2,B75="Seawater",3)</f>
@@ -10152,56 +10279,56 @@
       </c>
       <c r="O75" s="12" cm="1">
         <f t="array" ref="O75">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B75)*('Fish Type'!C:C=C75),'Fish Type'!A:A)</f>
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="P75" s="12" cm="1">
         <f t="array" ref="P75">_xlfn.IFS(D75="Common",1,D75="Uncommon",2,D75="Rare",3,D75="Legendary",4,D75="Mythical",5,D75="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q75" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Marbled Trout',35,2,375,5,30,30,120,'The marble trout has a long, cylindrical body, slightly compressed laterally, with a large head. '),</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A75,"',",O75,",",P75,",",E75,",",F75,",",G75,",",H75,",",I75,",","'",J75,"'),")</f>
+        <v>('Ruffe',28,2,300,0.1,0.2,5.2,25,'It is a very aggressive fish for its size. The ruffe also has a large, spiny upper fin which is likely distasteful to its predators'),</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
-        <v>287</v>
+        <v>366</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="C76" s="16" t="s">
-        <v>286</v>
+      <c r="C76" s="12" t="s">
+        <v>306</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E76" s="13">
-        <v>950</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="G76" s="13" t="s">
-        <v>207</v>
+        <v>60</v>
+      </c>
+      <c r="F76" s="13">
+        <v>70</v>
+      </c>
+      <c r="G76" s="13">
+        <v>350</v>
       </c>
       <c r="H76" s="13">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="I76" s="13">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="J76" s="14" t="s">
-        <v>289</v>
+        <v>367</v>
       </c>
       <c r="K76" s="14" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="L76" s="14" t="s">
-        <v>288</v>
+        <v>158</v>
       </c>
       <c r="M76" s="14" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="N76" s="12" cm="1">
         <f t="array" ref="N76">_xlfn.IFS(B76="Freshwater",1,B76="Brackish",2,B76="Seawater",3)</f>
@@ -10209,227 +10336,227 @@
       </c>
       <c r="O76" s="12" cm="1">
         <f t="array" ref="O76">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B76)*('Fish Type'!C:C=C76),'Fish Type'!A:A)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P76" s="12" cm="1">
         <f t="array" ref="P76">_xlfn.IFS(D76="Common",1,D76="Uncommon",2,D76="Rare",3,D76="Legendary",4,D76="Mythical",5,D76="Event",6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q76" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Common Clownfish',1,1,950,0.3,0.8,1,12,'The Common Clownfish has a stocky appearance and oval shape. It is compressed laterally, with a round profile.'),</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A76,"',",O76,",",P76,",",E76,",",F76,",",G76,",",H76,",",I76,",","'",J76,"'),")</f>
+        <v>('Sailfish',5,3,60,70,350,40,100,'Old sailors claim that they see Sailfish change colors when they get catch. Some people even said that was Sailfish way to communicate between them.'),</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
-        <v>302</v>
+        <v>383</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E77" s="13">
-        <v>250</v>
-      </c>
-      <c r="F77" s="13">
-        <v>10</v>
+        <v>660</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="G77" s="13">
-        <v>47</v>
-      </c>
-      <c r="H77" s="13">
-        <v>50</v>
+        <v>4</v>
+      </c>
+      <c r="H77" s="13" t="s">
+        <v>384</v>
       </c>
       <c r="I77" s="13">
-        <v>300</v>
+        <v>56</v>
       </c>
       <c r="J77" s="14" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
       <c r="K77" s="14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L77" s="14" t="s">
         <v>158</v>
       </c>
       <c r="M77" s="14" t="s">
-        <v>566</v>
+        <v>593</v>
       </c>
       <c r="N77" s="12" cm="1">
         <f t="array" ref="N77">_xlfn.IFS(B77="Freshwater",1,B77="Brackish",2,B77="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O77" s="12" cm="1">
         <f t="array" ref="O77">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B77)*('Fish Type'!C:C=C77),'Fish Type'!A:A)</f>
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="P77" s="12" cm="1">
         <f t="array" ref="P77">_xlfn.IFS(D77="Common",1,D77="Uncommon",2,D77="Rare",3,D77="Legendary",4,D77="Mythical",5,D77="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q77" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Great Barracuda',3,2,250,10,47,50,300,'They are voracious predators and hunt by ambush. They rely on surprise and short bursts of speed to overrun their prey, sacrificing maneuverability.'),</v>
+        <f>_xlfn.CONCAT("('",A77,"',",O77,",",P77,",",E77,",",F77,",",G77,",",H77,",",I77,",","'",J77,"'),")</f>
+        <v>('Sauger',28,1,660,0.9,4,10.5,56,'Saugers generally move upstream to spawn during Autumn, depending on where they are. They move downstream to their home locations from Summer after their spawning period is over.'),</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
-        <v>352</v>
+        <v>15</v>
       </c>
       <c r="B78" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>353</v>
+        <v>13</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E78" s="13">
-        <v>900</v>
+        <v>350</v>
       </c>
       <c r="F78" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G78" s="13">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H78" s="13">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="I78" s="13">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="J78" s="14" t="s">
-        <v>355</v>
+        <v>308</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L78" s="14" t="s">
-        <v>354</v>
+        <v>58</v>
       </c>
       <c r="M78" s="14" t="s">
-        <v>565</v>
+        <v>605</v>
       </c>
       <c r="N78" s="12" cm="1">
         <f t="array" ref="N78">_xlfn.IFS(B78="Freshwater",1,B78="Brackish",2,B78="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O78" s="12" cm="1">
         <f t="array" ref="O78">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B78)*('Fish Type'!C:C=C78),'Fish Type'!A:A)</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P78" s="12" cm="1">
         <f t="array" ref="P78">_xlfn.IFS(D78="Common",1,D78="Uncommon",2,D78="Rare",3,D78="Legendary",4,D78="Mythical",5,D78="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Striped Bass',4,1,900,5,60,40,120,'The Striped Bass has a streamlined, silvery body marked with longitudinal dark stripes running from behind the gills to the base of the tail.'),</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A78,"',",O78,",",P78,",",E78,",",F78,",",G78,",",H78,",",I78,",","'",J78,"'),")</f>
+        <v>('Silver Carp',9,2,350,7,50,35,105,'A fast-growing filter feeder that cruises open freshwater, consuming microscopic plankton and occasionally leaping high above the surface when startled.'),</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E79" s="13">
-        <v>150</v>
-      </c>
-      <c r="F79" s="13">
-        <v>100</v>
+        <v>800</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>212</v>
       </c>
       <c r="G79" s="13">
-        <v>700</v>
+        <v>1</v>
       </c>
       <c r="H79" s="13">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="I79" s="13">
-        <v>455</v>
+        <v>27</v>
       </c>
       <c r="J79" s="14" t="s">
-        <v>307</v>
+        <v>851</v>
       </c>
       <c r="K79" s="14" t="s">
         <v>63</v>
       </c>
       <c r="L79" s="14" t="s">
-        <v>288</v>
+        <v>55</v>
       </c>
       <c r="M79" s="14" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="N79" s="12" cm="1">
         <f t="array" ref="N79">_xlfn.IFS(B79="Freshwater",1,B79="Brackish",2,B79="Seawater",3)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O79" s="12" cm="1">
         <f t="array" ref="O79">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B79)*('Fish Type'!C:C=C79),'Fish Type'!A:A)</f>
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="P79" s="12" cm="1">
         <f t="array" ref="P79">_xlfn.IFS(D79="Common",1,D79="Uncommon",2,D79="Rare",3,D79="Legendary",4,D79="Mythical",5,D79="Event",6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Swordfish',5,3,150,100,700,100,455,'Swordfish can swim extremely fast; it is said that Swordfish will jumped out of the water and then attack the fishermen when threatened.'),</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A79,"',",O79,",",P79,",",E79,",",F79,",",G79,",",H79,",",I79,",","'",J79,"'),")</f>
+        <v>('Silver Moony',25,1,800,0.1,1,4,27,'This fish has a bright, shiny silver color with yellowish edges to the fins, and the upper and anal fins have black tips.'),</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
-        <v>366</v>
+        <v>261</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>306</v>
+        <v>220</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E80" s="13">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="F80" s="13">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="G80" s="13">
-        <v>350</v>
+        <v>9</v>
       </c>
       <c r="H80" s="13">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="I80" s="13">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="J80" s="14" t="s">
-        <v>367</v>
+        <v>262</v>
       </c>
       <c r="K80" s="14" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="L80" s="14" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="M80" s="14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N80" s="12" cm="1">
         <f t="array" ref="N80">_xlfn.IFS(B80="Freshwater",1,B80="Brackish",2,B80="Seawater",3)</f>
@@ -10437,56 +10564,56 @@
       </c>
       <c r="O80" s="12" cm="1">
         <f t="array" ref="O80">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B80)*('Fish Type'!C:C=C80),'Fish Type'!A:A)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P80" s="12" cm="1">
         <f t="array" ref="P80">_xlfn.IFS(D80="Common",1,D80="Uncommon",2,D80="Rare",3,D80="Legendary",4,D80="Mythical",5,D80="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Sailfish',5,3,60,70,350,40,100,'Old sailors claim that they see Sailfish change colors when they get catch. Some people even said that was Sailfish way to communicate between them.'),</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A80,"',",O80,",",P80,",",E80,",",F80,",",G80,",",H80,",",I80,",","'",J80,"'),")</f>
+        <v>('Silverwhisker Sea Catfish',10,2,215,3,9,12,55,'A medium-sized coastal catfish with a silvery-gray body, long sensitive barbels, and sharp defensive spines. '),</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A81" s="12" t="s">
-        <v>368</v>
+        <v>419</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>306</v>
+        <v>417</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E81" s="13">
-        <v>51</v>
-      </c>
-      <c r="F81" s="13">
-        <v>100</v>
+        <v>775</v>
+      </c>
+      <c r="F81" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="G81" s="13">
-        <v>720</v>
-      </c>
-      <c r="H81" s="13">
-        <v>150</v>
+        <v>2</v>
+      </c>
+      <c r="H81" s="13" t="s">
+        <v>382</v>
       </c>
       <c r="I81" s="13">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="J81" s="14" t="s">
-        <v>369</v>
+        <v>421</v>
       </c>
       <c r="K81" s="14" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="L81" s="14" t="s">
-        <v>243</v>
+        <v>420</v>
       </c>
       <c r="M81" s="14" t="s">
-        <v>95</v>
+        <v>565</v>
       </c>
       <c r="N81" s="12" cm="1">
         <f t="array" ref="N81">_xlfn.IFS(B81="Freshwater",1,B81="Brackish",2,B81="Seawater",3)</f>
@@ -10494,113 +10621,113 @@
       </c>
       <c r="O81" s="12" cm="1">
         <f t="array" ref="O81">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B81)*('Fish Type'!C:C=C81),'Fish Type'!A:A)</f>
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="P81" s="12" cm="1">
         <f t="array" ref="P81">_xlfn.IFS(D81="Common",1,D81="Uncommon",2,D81="Rare",3,D81="Legendary",4,D81="Mythical",5,D81="Event",6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Black Marlin',5,3,51,100,720,150,450,'One of the fastest fish known to sailors, this fish is said to be fast enough to leave a hole in a ship by swimming through it.'),</v>
+        <f>_xlfn.CONCAT("('",A81,"',",O81,",",P81,",",E81,",",F81,",",G81,",",H81,",",I81,",","'",J81,"'),")</f>
+        <v>('Slender Grouper',21,1,775,0.5,2,12.5,75,'The slender grouper is a medium-sized fish with a head that occupies 40% of the total length, and the mouth is large.'),</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
-        <v>190</v>
+        <v>373</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>33</v>
+        <v>371</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E82" s="13">
-        <v>150</v>
+        <v>725</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="G82" s="13">
-        <v>3</v>
+        <v>255</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="H82" s="13">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="I82" s="13">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="J82" s="14" t="s">
-        <v>192</v>
+        <v>864</v>
       </c>
       <c r="K82" s="14" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="L82" s="14" t="s">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="M82" s="14" t="s">
-        <v>95</v>
+        <v>589</v>
       </c>
       <c r="N82" s="12" cm="1">
         <f t="array" ref="N82">_xlfn.IFS(B82="Freshwater",1,B82="Brackish",2,B82="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O82" s="12" cm="1">
         <f t="array" ref="O82">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B82)*('Fish Type'!C:C=C82),'Fish Type'!A:A)</f>
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="P82" s="12" cm="1">
         <f t="array" ref="P82">_xlfn.IFS(D82="Common",1,D82="Uncommon",2,D82="Rare",3,D82="Legendary",4,D82="Mythical",5,D82="Event",6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Zebra Seabream',6,3,150,1.25,3,25,55,'This fish has an oval shaped body which is deep and compressed with a moderately sharp snout and a thick lipped slightly protrusible mouth.'),</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A82,"',",O82,",",P82,",",E82,",",F82,",",G82,",",H82,",",I82,",","'",J82,"'),")</f>
+        <v>('Southern Pike',29,1,725,1.2,4.5,40,79,'The southern pike has a distinctive, dark, chain-like pattern on its greenish sides. There is a vertical dark marking underneath the eye'),</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A83" s="12" t="s">
-        <v>180</v>
+        <v>363</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>33</v>
+        <v>364</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E83" s="13">
-        <v>425</v>
+        <v>295</v>
       </c>
       <c r="F83" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G83" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H83" s="13">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="I83" s="13">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="J83" s="14" t="s">
-        <v>183</v>
+        <v>858</v>
       </c>
       <c r="K83" s="14" t="s">
         <v>182</v>
       </c>
       <c r="L83" s="14" t="s">
-        <v>55</v>
+        <v>365</v>
       </c>
       <c r="M83" s="14" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="N83" s="12" cm="1">
         <f t="array" ref="N83">_xlfn.IFS(B83="Freshwater",1,B83="Brackish",2,B83="Seawater",3)</f>
@@ -10608,56 +10735,56 @@
       </c>
       <c r="O83" s="12" cm="1">
         <f t="array" ref="O83">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B83)*('Fish Type'!C:C=C83),'Fish Type'!A:A)</f>
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="P83" s="12" cm="1">
         <f t="array" ref="P83">_xlfn.IFS(D83="Common",1,D83="Uncommon",2,D83="Rare",3,D83="Legendary",4,D83="Mythical",5,D83="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q83" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Two-bar Bream',6,2,425,1,3,10,60,'Two-bar Bream has an oval-shaped, deep, compressed body with a moderately fleshy-lipped, slightly protrusible mouth.'),</v>
+        <f>_xlfn.CONCAT("('",A83,"',",O83,",",P83,",",E83,",",F83,",",G83,",",H83,",",I83,",","'",J83,"'),")</f>
+        <v>('Spiny Dogfish',31,2,295,2,10,90,160,'Spiny Dogfish is distinguished by two spines (one anterior to each upper fin) and no anal fin. It lives in shallow waters and further offshore in most parts of the world, especially in temperate waters.'),</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
-        <v>187</v>
+        <v>352</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>33</v>
+        <v>353</v>
       </c>
       <c r="D84" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E84" s="13">
-        <v>850</v>
-      </c>
-      <c r="F84" s="13" t="s">
-        <v>175</v>
+        <v>900</v>
+      </c>
+      <c r="F84" s="13">
+        <v>5</v>
       </c>
       <c r="G84" s="13">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="H84" s="13">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I84" s="13">
         <v>120</v>
       </c>
       <c r="J84" s="14" t="s">
-        <v>188</v>
+        <v>355</v>
       </c>
       <c r="K84" s="14" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="L84" s="14" t="s">
-        <v>62</v>
+        <v>354</v>
       </c>
       <c r="M84" s="14" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="N84" s="12" cm="1">
         <f t="array" ref="N84">_xlfn.IFS(B84="Freshwater",1,B84="Brackish",2,B84="Seawater",3)</f>
@@ -10665,113 +10792,113 @@
       </c>
       <c r="O84" s="12" cm="1">
         <f t="array" ref="O84">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B84)*('Fish Type'!C:C=C84),'Fish Type'!A:A)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P84" s="12" cm="1">
         <f t="array" ref="P84">_xlfn.IFS(D84="Common",1,D84="Uncommon",2,D84="Rare",3,D84="Legendary",4,D84="Mythical",5,D84="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q84" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Red Seabream',6,1,850,0.75,10,20,120,'The body is oblong and laterally flattened, with the jaws protruding slightly forward. The pectoral fins are long and slender, reaching nearly half of the total length.'),</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A84,"',",O84,",",P84,",",E84,",",F84,",",G84,",",H84,",",I84,",","'",J84,"'),")</f>
+        <v>('Striped Bass',4,1,900,5,60,40,120,'The Striped Bass has a streamlined, silvery body marked with longitudinal dark stripes running from behind the gills to the base of the tail.'),</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A85" s="12" t="s">
-        <v>1091</v>
+        <v>401</v>
       </c>
       <c r="B85" s="12" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>33</v>
+        <v>402</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E85" s="13">
-        <v>201</v>
+        <v>615</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G85" s="13">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H85" s="13">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="I85" s="13">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J85" s="14" t="s">
-        <v>189</v>
+        <v>403</v>
       </c>
       <c r="K85" s="14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L85" s="14" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M85" s="14" t="s">
-        <v>566</v>
+        <v>132</v>
       </c>
       <c r="N85" s="12" cm="1">
         <f t="array" ref="N85">_xlfn.IFS(B85="Freshwater",1,B85="Brackish",2,B85="Seawater",3)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O85" s="12" cm="1">
         <f t="array" ref="O85">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B85)*('Fish Type'!C:C=C85),'Fish Type'!A:A)</f>
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="P85" s="12" cm="1">
         <f t="array" ref="P85">_xlfn.IFS(D85="Common",1,D85="Uncommon",2,D85="Rare",3,D85="Legendary",4,D85="Mythical",5,D85="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q85" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Gilthead Seabream',6,2,201,0.5,18,15,70,'The gilt-head bream has a deep body, with a large, deep head which has its relatively small eyes placed high on the head. The diameter of the eyes is shorter than the length of the snout.'),</v>
+        <f>_xlfn.CONCAT("('",A85,"',",O85,",",P85,",",E85,",",F85,",",G85,",",H85,",",I85,",","'",J85,"'),")</f>
+        <v>('Striped Mullet',26,1,615,1.1,8,30,100,'The back of the fish is olive-green, sides are silvery and shade to white towards the belly.'),</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
-        <v>258</v>
+        <v>356</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E86" s="13">
-        <v>205</v>
-      </c>
-      <c r="F86" s="13">
+        <v>430</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="13">
         <v>9</v>
       </c>
-      <c r="G86" s="13">
-        <v>25</v>
-      </c>
       <c r="H86" s="13">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I86" s="13">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="J86" s="14" t="s">
-        <v>259</v>
+        <v>357</v>
       </c>
       <c r="K86" s="14" t="s">
-        <v>127</v>
+        <v>172</v>
       </c>
       <c r="L86" s="14" t="s">
-        <v>257</v>
+        <v>62</v>
       </c>
       <c r="M86" s="14" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N86" s="12" cm="1">
         <f t="array" ref="N86">_xlfn.IFS(B86="Freshwater",1,B86="Brackish",2,B86="Seawater",3)</f>
@@ -10779,56 +10906,56 @@
       </c>
       <c r="O86" s="12" cm="1">
         <f t="array" ref="O86">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B86)*('Fish Type'!C:C=C86),'Fish Type'!A:A)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P86" s="12" cm="1">
         <f t="array" ref="P86">_xlfn.IFS(D86="Common",1,D86="Uncommon",2,D86="Rare",3,D86="Legendary",4,D86="Mythical",5,D86="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q86" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Swordhilt Sea Catfish',10,2,205,9,25,35,100,'A coastal catfish is recognized by the distinctive arrangement of bones beneath its head, forming a hilt of a sword structure.'),</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A86,"',",O86,",",P86,",",E86,",",F86,",",G86,",",H86,",",I86,",","'",J86,"'),")</f>
+        <v>('Summer Flounder',17,2,430,0.5,9,20,51,'This fish is called the chameleon of the sea because their ability to change color to blend in with their surrounding.'),</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A87" s="12" t="s">
-        <v>261</v>
+        <v>305</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>220</v>
+        <v>306</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E87" s="13">
-        <v>215</v>
+        <v>150</v>
       </c>
       <c r="F87" s="13">
-        <v>3</v>
+        <v>100</v>
       </c>
       <c r="G87" s="13">
-        <v>9</v>
+        <v>700</v>
       </c>
       <c r="H87" s="13">
-        <v>12</v>
+        <v>100</v>
       </c>
       <c r="I87" s="13">
-        <v>55</v>
+        <v>455</v>
       </c>
       <c r="J87" s="14" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="K87" s="14" t="s">
-        <v>182</v>
+        <v>63</v>
       </c>
       <c r="L87" s="14" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="M87" s="14" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="N87" s="12" cm="1">
         <f t="array" ref="N87">_xlfn.IFS(B87="Freshwater",1,B87="Brackish",2,B87="Seawater",3)</f>
@@ -10836,56 +10963,56 @@
       </c>
       <c r="O87" s="12" cm="1">
         <f t="array" ref="O87">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B87)*('Fish Type'!C:C=C87),'Fish Type'!A:A)</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P87" s="12" cm="1">
         <f t="array" ref="P87">_xlfn.IFS(D87="Common",1,D87="Uncommon",2,D87="Rare",3,D87="Legendary",4,D87="Mythical",5,D87="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q87" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Silverwhisker Sea Catfish',10,2,215,3,9,12,55,'A medium-sized coastal catfish with a silvery-gray body, long sensitive barbels, and sharp defensive spines. '),</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A87,"',",O87,",",P87,",",E87,",",F87,",",G87,",",H87,",",I87,",","'",J87,"'),")</f>
+        <v>('Swordfish',5,3,150,100,700,100,455,'Swordfish can swim extremely fast; it is said that Swordfish will jumped out of the water and then attack the fishermen when threatened.'),</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>296</v>
+        <v>220</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E88" s="13">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="F88" s="13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G88" s="13">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H88" s="13">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="I88" s="13">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="J88" s="14" t="s">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="K88" s="14" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="L88" s="14" t="s">
-        <v>57</v>
+        <v>257</v>
       </c>
       <c r="M88" s="14" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="N88" s="12" cm="1">
         <f t="array" ref="N88">_xlfn.IFS(B88="Freshwater",1,B88="Brackish",2,B88="Seawater",3)</f>
@@ -10893,170 +11020,170 @@
       </c>
       <c r="O88" s="12" cm="1">
         <f t="array" ref="O88">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B88)*('Fish Type'!C:C=C88),'Fish Type'!A:A)</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="P88" s="12" cm="1">
         <f t="array" ref="P88">_xlfn.IFS(D88="Common",1,D88="Uncommon",2,D88="Rare",3,D88="Legendary",4,D88="Mythical",5,D88="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q88" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Common Dolphinfish',14,2,201,8,40,12,180,' Mature males have distinctive "foreheads"; it grows as the fish matures and often protrudes well above the body proper, which is streamlined by the musculature of the back'),</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A88,"',",O88,",",P88,",",E88,",",F88,",",G88,",",H88,",",I88,",","'",J88,"'),")</f>
+        <v>('Swordhilt Sea Catfish',10,2,205,9,25,35,100,'A coastal catfish is recognized by the distinctive arrangement of bones beneath its head, forming a hilt of a sword structure.'),</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A89" s="12" t="s">
-        <v>356</v>
+        <v>179</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="D89" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E89" s="13">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="F89" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="13">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>173</v>
       </c>
       <c r="H89" s="13">
         <v>20</v>
       </c>
       <c r="I89" s="13">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J89" s="14" t="s">
-        <v>357</v>
+        <v>178</v>
       </c>
       <c r="K89" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="L89" s="14" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="M89" s="14" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="N89" s="12" cm="1">
         <f t="array" ref="N89">_xlfn.IFS(B89="Freshwater",1,B89="Brackish",2,B89="Seawater",3)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O89" s="12" cm="1">
         <f t="array" ref="O89">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B89)*('Fish Type'!C:C=C89),'Fish Type'!A:A)</f>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="P89" s="12" cm="1">
         <f t="array" ref="P89">_xlfn.IFS(D89="Common",1,D89="Uncommon",2,D89="Rare",3,D89="Legendary",4,D89="Mythical",5,D89="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q89" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Summer Flounder',17,2,430,0.5,9,20,51,'This fish is called the chameleon of the sea because their ability to change color to blend in with their surrounding.'),</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A89,"',",O89,",",P89,",",E89,",",F89,",",G89,",",H89,",",I89,",","'",J89,"'),")</f>
+        <v>('Tarwhine Bream',8,2,450,0.75,4.5,20,58,'A sleek silver bream with bright yellow fins, thriving in estuaries and coastal waters while feeding on small bottom-dwelling prey.'),</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A90" s="12" t="s">
-        <v>416</v>
+        <v>271</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>417</v>
+        <v>270</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E90" s="13">
-        <v>825</v>
+        <v>555</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G90" s="13">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H90" s="13">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I90" s="13">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J90" s="14" t="s">
-        <v>418</v>
+        <v>328</v>
       </c>
       <c r="K90" s="14" t="s">
-        <v>63</v>
+        <v>127</v>
       </c>
       <c r="L90" s="14" t="s">
-        <v>409</v>
+        <v>57</v>
       </c>
       <c r="M90" s="14" t="s">
-        <v>565</v>
+        <v>132</v>
       </c>
       <c r="N90" s="12" cm="1">
         <f t="array" ref="N90">_xlfn.IFS(B90="Freshwater",1,B90="Brackish",2,B90="Seawater",3)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" s="12" cm="1">
         <f t="array" ref="O90">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B90)*('Fish Type'!C:C=C90),'Fish Type'!A:A)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P90" s="12" cm="1">
         <f t="array" ref="P90">_xlfn.IFS(D90="Common",1,D90="Uncommon",2,D90="Rare",3,D90="Legendary",4,D90="Mythical",5,D90="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q90" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Redmouth Grouper',21,1,825,0.9,15,15,60,'The redmouth grouper is laterally compressed and oval-shaped with a relatively deep body, which is around half of the standard length, and a large head.'),</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A90,"',",O90,",",P90,",",E90,",",F90,",",G90,",",H90,",",I90,",","'",J90,"'),")</f>
+        <v>('Tidehaven Moony',25,1,555,0.1,1,7,25,'A silvery schooling fish with a diamond-shaped body and striking black markings native to Tidehaven water.'),</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A91" s="12" t="s">
-        <v>419</v>
+        <v>180</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>417</v>
+        <v>33</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E91" s="13">
-        <v>775</v>
-      </c>
-      <c r="F91" s="13" t="s">
-        <v>26</v>
+        <v>425</v>
+      </c>
+      <c r="F91" s="13">
+        <v>1</v>
       </c>
       <c r="G91" s="13">
-        <v>2</v>
-      </c>
-      <c r="H91" s="13" t="s">
-        <v>382</v>
+        <v>3</v>
+      </c>
+      <c r="H91" s="13">
+        <v>10</v>
       </c>
       <c r="I91" s="13">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="J91" s="14" t="s">
-        <v>421</v>
+        <v>183</v>
       </c>
       <c r="K91" s="14" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="L91" s="14" t="s">
-        <v>420</v>
+        <v>55</v>
       </c>
       <c r="M91" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N91" s="12" cm="1">
         <f t="array" ref="N91">_xlfn.IFS(B91="Freshwater",1,B91="Brackish",2,B91="Seawater",3)</f>
@@ -11064,476 +11191,476 @@
       </c>
       <c r="O91" s="12" cm="1">
         <f t="array" ref="O91">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B91)*('Fish Type'!C:C=C91),'Fish Type'!A:A)</f>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="P91" s="12" cm="1">
         <f t="array" ref="P91">_xlfn.IFS(D91="Common",1,D91="Uncommon",2,D91="Rare",3,D91="Legendary",4,D91="Mythical",5,D91="Event",6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q91" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Slender Grouper',21,1,775,0.5,2,12.5,75,'The slender grouper is a medium-sized fish with a head that occupies 40% of the total length, and the mouth is large.'),</v>
+        <f>_xlfn.CONCAT("('",A91,"',",O91,",",P91,",",E91,",",F91,",",G91,",",H91,",",I91,",","'",J91,"'),")</f>
+        <v>('Two-bar Bream',6,2,425,1,3,10,60,'Two-bar Bream has an oval-shaped, deep, compressed body with a moderately fleshy-lipped, slightly protrusible mouth.'),</v>
       </c>
     </row>
     <row r="92" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A92" s="12" t="s">
-        <v>422</v>
+        <v>186</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>417</v>
+        <v>33</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E92" s="13">
-        <v>230</v>
-      </c>
-      <c r="F92" s="13" t="s">
-        <v>204</v>
+        <v>800</v>
+      </c>
+      <c r="F92" s="13">
+        <v>1</v>
       </c>
       <c r="G92" s="13">
         <v>2</v>
       </c>
-      <c r="H92" s="13" t="s">
-        <v>424</v>
+      <c r="H92" s="13">
+        <v>20</v>
       </c>
       <c r="I92" s="13">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J92" s="14" t="s">
-        <v>425</v>
+        <v>853</v>
       </c>
       <c r="K92" s="14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L92" s="14" t="s">
-        <v>251</v>
+        <v>60</v>
       </c>
       <c r="M92" s="14" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="N92" s="12" cm="1">
         <f t="array" ref="N92">_xlfn.IFS(B92="Freshwater",1,B92="Brackish",2,B92="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O92" s="12" cm="1">
         <f t="array" ref="O92">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B92)*('Fish Type'!C:C=C92),'Fish Type'!A:A)</f>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="P92" s="12" cm="1">
         <f t="array" ref="P92">_xlfn.IFS(D92="Common",1,D92="Uncommon",2,D92="Rare",3,D92="Legendary",4,D92="Mythical",5,D92="Event",6)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q92" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Masked Grouper',21,2,230,0.3,2,9.5,45,'The masked grouper has an oblong, rather compressed body, with the gill cover having a central spine which is located at one-third of the gap between the lower and upper spines.'),</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A92,"',",O92,",",P92,",",E92,",",F92,",",G92,",",H92,",",I92,",","'",J92,"'),")</f>
+        <v>('Vimba Bream',7,1,800,1,2,20,50,'This fish is a deep bluish-green on the upper surface, and silvery along the flanks. The eyes are yellow, and the pectoral and pelvic fins have reddish-yellow bases.'),</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A93" s="12" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>298</v>
+        <v>220</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E93" s="13">
-        <v>300</v>
-      </c>
-      <c r="F93" s="13">
-        <v>5</v>
+        <v>390</v>
+      </c>
+      <c r="F93" s="13" t="s">
+        <v>241</v>
       </c>
       <c r="G93" s="13">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H93" s="13">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="I93" s="13">
-        <v>184</v>
+        <v>100</v>
       </c>
       <c r="J93" s="14" t="s">
-        <v>299</v>
+        <v>244</v>
       </c>
       <c r="K93" s="14" t="s">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="L93" s="14" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="M93" s="14" t="s">
-        <v>126</v>
+        <v>611</v>
       </c>
       <c r="N93" s="12" cm="1">
         <f t="array" ref="N93">_xlfn.IFS(B93="Freshwater",1,B93="Brackish",2,B93="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O93" s="12" cm="1">
         <f t="array" ref="O93">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B93)*('Fish Type'!C:C=C93),'Fish Type'!A:A)</f>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="P93" s="12" cm="1">
         <f t="array" ref="P93">_xlfn.IFS(D93="Common",1,D93="Uncommon",2,D93="Rare",3,D93="Legendary",4,D93="Mythical",5,D93="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q93" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('King Mackerel',23,2,300,5,40,11,184,'A swift ocean predator renowned for its speed and powerful runs. It patrols coastal waters in search of baitfish, making it a prized catch for fisherman.'),</v>
+        <f>_xlfn.CONCAT("('",A93,"',",O93,",",P93,",",E93,",",F93,",",G93,",",H93,",",I93,",","'",J93,"'),")</f>
+        <v>('Walking Catfish',11,2,390,7.2,30,25,100,'When the river dried out, this fish would "walk" around the river in wiggling motion to traverse the land.'),</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="12" t="s">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>293</v>
+        <v>381</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E94" s="13">
-        <v>875</v>
+        <v>625</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G94" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="H94" s="13">
-        <v>10</v>
+        <v>255</v>
+      </c>
+      <c r="G94" s="13">
+        <v>9</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>382</v>
       </c>
       <c r="I94" s="13">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J94" s="14" t="s">
-        <v>295</v>
+        <v>856</v>
       </c>
       <c r="K94" s="14" t="s">
         <v>63</v>
       </c>
       <c r="L94" s="14" t="s">
-        <v>59</v>
+        <v>374</v>
       </c>
       <c r="M94" s="14" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="N94" s="12" cm="1">
         <f t="array" ref="N94">_xlfn.IFS(B94="Freshwater",1,B94="Brackish",2,B94="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O94" s="12" cm="1">
         <f t="array" ref="O94">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B94)*('Fish Type'!C:C=C94),'Fish Type'!A:A)</f>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P94" s="12" cm="1">
         <f t="array" ref="P94">_xlfn.IFS(D94="Common",1,D94="Uncommon",2,D94="Rare",3,D94="Legendary",4,D94="Mythical",5,D94="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q94" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Common Lionfish',30,1,875,0.1,1.3,10,35,'The fin spines are highly venomous and have caused death to humans in some reported cases. Despite this, a sting from this species is rarely fatal to humans.'),</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A94,"',",O94,",",P94,",",E94,",",F94,",",G94,",",H94,",",I94,",","'",J94,"'),")</f>
+        <v>('Walleye',28,1,625,1.2,9,12.5,80,'Walleyes are largely olive and gold in color. The upper side of a walleye is olive, grading into a golden hue on the flanks.'),</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="12" t="s">
-        <v>363</v>
+        <v>203</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>364</v>
+        <v>168</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>16</v>
       </c>
       <c r="E95" s="13">
-        <v>295</v>
-      </c>
-      <c r="F95" s="13">
-        <v>2</v>
-      </c>
-      <c r="G95" s="13">
+        <v>375</v>
+      </c>
+      <c r="F95" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H95" s="13">
         <v>10</v>
       </c>
-      <c r="H95" s="13">
-        <v>90</v>
-      </c>
       <c r="I95" s="13">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="J95" s="14" t="s">
-        <v>858</v>
+        <v>205</v>
       </c>
       <c r="K95" s="14" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="L95" s="14" t="s">
-        <v>365</v>
+        <v>61</v>
       </c>
       <c r="M95" s="14" t="s">
-        <v>574</v>
+        <v>618</v>
       </c>
       <c r="N95" s="12" cm="1">
         <f t="array" ref="N95">_xlfn.IFS(B95="Freshwater",1,B95="Brackish",2,B95="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O95" s="12" cm="1">
         <f t="array" ref="O95">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B95)*('Fish Type'!C:C=C95),'Fish Type'!A:A)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P95" s="12" cm="1">
         <f t="array" ref="P95">_xlfn.IFS(D95="Common",1,D95="Uncommon",2,D95="Rare",3,D95="Legendary",4,D95="Mythical",5,D95="Event",6)</f>
         <v>2</v>
       </c>
       <c r="Q95" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Spiny Dogfish',31,2,295,2,10,90,160,'Spiny Dogfish is distinguished by two spines (one anterior to each upper fin) and no anal fin. It lives in shallow waters and further offshore in most parts of the world, especially in temperate waters.'),</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A95,"',",O95,",",P95,",",E95,",",F95,",",G95,",",H95,",",I95,",","'",J95,"'),")</f>
+        <v>('Warmouth',34,2,375,0.3,1.1,10,30,'The Warmouth is an aggressive and hardy fish that can survive in streams with low oxygen level.'),</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A96" s="12" t="s">
-        <v>413</v>
+        <v>169</v>
       </c>
       <c r="B96" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>396</v>
+        <v>33</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E96" s="13">
-        <v>900</v>
-      </c>
-      <c r="F96" s="13">
+        <v>975</v>
+      </c>
+      <c r="F96" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G96" s="13">
         <v>2</v>
       </c>
-      <c r="G96" s="13">
-        <v>23</v>
-      </c>
       <c r="H96" s="13">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I96" s="13">
-        <v>88</v>
+        <v>7</v>
       </c>
       <c r="J96" s="14" t="s">
-        <v>415</v>
+        <v>170</v>
       </c>
       <c r="K96" s="14" t="s">
         <v>63</v>
       </c>
       <c r="L96" s="14" t="s">
-        <v>414</v>
+        <v>62</v>
       </c>
       <c r="M96" s="14" t="s">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="N96" s="12" cm="1">
         <f t="array" ref="N96">_xlfn.IFS(B96="Freshwater",1,B96="Brackish",2,B96="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O96" s="12" cm="1">
         <f t="array" ref="O96">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B96)*('Fish Type'!C:C=C96),'Fish Type'!A:A)</f>
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="P96" s="12" cm="1">
         <f t="array" ref="P96">_xlfn.IFS(D96="Common",1,D96="Uncommon",2,D96="Rare",3,D96="Legendary",4,D96="Mythical",5,D96="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q96" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Northern Red Snapper',33,1,900,2,23,23,88,'They eat almost anything, but prefer small fish and crustaceans. They can be caught on both live and cut bait'),</v>
+        <f>_xlfn.CONCAT("('",A96,"',",O96,",",P96,",",E96,",",F96,",",G96,",",H96,",",I96,",","'",J96,"'),")</f>
+        <v>('White Bream',7,1,975,0.25,2,5,7,'White Bream / Silver Bream generally inhabit the lower reaches of rivers as well as lakes and ponds with muddy bottoms and plenty of algae to feed on.'),</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="12" t="s">
-        <v>1075</v>
+        <v>404</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>96</v>
+        <v>181</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>1076</v>
+        <v>405</v>
       </c>
       <c r="D97" s="12" t="s">
         <v>14</v>
       </c>
       <c r="E97" s="13">
-        <v>451</v>
+        <v>630</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="G97" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="H97" s="13">
-        <v>20</v>
+        <v>204</v>
+      </c>
+      <c r="H97" s="13" t="s">
+        <v>255</v>
       </c>
       <c r="I97" s="13">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="J97" s="14" t="s">
-        <v>291</v>
+        <v>406</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>63</v>
+        <v>182</v>
       </c>
       <c r="L97" s="14" t="s">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="M97" s="14" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="N97" s="12" cm="1">
         <f t="array" ref="N97">_xlfn.IFS(B97="Freshwater",1,B97="Brackish",2,B97="Seawater",3)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O97" s="12" cm="1">
         <f t="array" ref="O97">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B97)*('Fish Type'!C:C=C97),'Fish Type'!A:A)</f>
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P97" s="12" cm="1">
         <f t="array" ref="P97">_xlfn.IFS(D97="Common",1,D97="Uncommon",2,D97="Rare",3,D97="Legendary",4,D97="Mythical",5,D97="Event",6)</f>
         <v>1</v>
       </c>
       <c r="Q97" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Grey Crossbowfish',15,1,451,0.4,2.5,20,60,'The small beak-like mouth at the tip of the snout has fleshy lips. The eyes are set far back near the top of the head.'),</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="27.6" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A97,"',",O97,",",P97,",",E97,",",F97,",",G97,",",H97,",",I97,",","'",J97,"'),")</f>
+        <v>('Wrestling Halfbeak',22,1,630,0.1,0.3,1.2,8,'Wrestling halfbeaks are surface-feeding fish and feed on a variety of small invertebrates, including crustaceans and insect larvae.'),</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="B98" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>359</v>
+        <v>22</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E98" s="13">
-        <v>90</v>
+        <v>201</v>
       </c>
       <c r="F98" s="13">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G98" s="13">
-        <v>700</v>
+        <v>3</v>
       </c>
       <c r="H98" s="13">
-        <v>150</v>
+        <v>15</v>
       </c>
       <c r="I98" s="13">
-        <v>400</v>
+        <v>61</v>
       </c>
       <c r="J98" s="14" t="s">
-        <v>360</v>
+        <v>326</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="L98" s="14" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="M98" s="14" t="s">
-        <v>578</v>
+        <v>624</v>
       </c>
       <c r="N98" s="12" cm="1">
         <f t="array" ref="N98">_xlfn.IFS(B98="Freshwater",1,B98="Brackish",2,B98="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O98" s="12" cm="1">
         <f t="array" ref="O98">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B98)*('Fish Type'!C:C=C98),'Fish Type'!A:A)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P98" s="12" cm="1">
         <f t="array" ref="P98">_xlfn.IFS(D98="Common",1,D98="Uncommon",2,D98="Rare",3,D98="Legendary",4,D98="Mythical",5,D98="Event",6)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q98" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Bluefin Tuna',36,3,90,100,700,150,400,'Their color is dark blue above and gray below, with a gold coruscation covering the body and bright yellow caudal finlets.'),</v>
+        <f>_xlfn.CONCAT("('",A98,"',",O98,",",P98,",",E98,",",F98,",",G98,",",H98,",",I98,",","'",J98,"'),")</f>
+        <v>('Yakad Trout',35,2,201,1,3,15,61,'Yakad Trout can be identified by its distinctive yellowish-gold color, with a golden belly. The top of its head and back are a dark olive color.'),</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A99" s="12" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B99" s="12" t="s">
-        <v>96</v>
+        <v>38</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E99" s="13">
-        <v>95</v>
-      </c>
-      <c r="F99" s="13">
-        <v>90</v>
+        <v>425</v>
+      </c>
+      <c r="F99" s="13" t="s">
+        <v>26</v>
       </c>
       <c r="G99" s="13">
-        <v>450</v>
-      </c>
-      <c r="H99" s="13">
-        <v>120</v>
+        <v>2</v>
+      </c>
+      <c r="H99" s="13" t="s">
+        <v>387</v>
       </c>
       <c r="I99" s="13">
-        <v>240</v>
+        <v>50</v>
       </c>
       <c r="J99" s="14" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="K99" s="14" t="s">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="L99" s="14" t="s">
-        <v>243</v>
+        <v>55</v>
       </c>
       <c r="M99" s="14" t="s">
-        <v>95</v>
+        <v>594</v>
       </c>
       <c r="N99" s="12" cm="1">
         <f t="array" ref="N99">_xlfn.IFS(B99="Freshwater",1,B99="Brackish",2,B99="Seawater",3)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O99" s="12" cm="1">
         <f t="array" ref="O99">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B99)*('Fish Type'!C:C=C99),'Fish Type'!A:A)</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P99" s="12" cm="1">
         <f t="array" ref="P99">_xlfn.IFS(D99="Common",1,D99="Uncommon",2,D99="Rare",3,D99="Legendary",4,D99="Mythical",5,D99="Event",6)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Yellowfin Tuna',36,3,95,90,450,120,240,'Their body shape is particularly adapted for speed, enabling them to pursue and capture fast-moving baitfish, such as flying fish, sauries, and mackerel.'),</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="55.2" x14ac:dyDescent="0.3">
+        <f>_xlfn.CONCAT("('",A99,"',",O99,",",P99,",",E99,",",F99,",",G99,",",H99,",",I99,",","'",J99,"'),")</f>
+        <v>('Yellow Perch',28,1,425,0.5,2,10.2,50,'The yellow perch has an elongate, laterally compressed body with a subterminal mouth and a relatively long but blunt snout, which is surpassed in length by the lower jaw.'),</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A100" s="12" t="s">
-        <v>407</v>
+        <v>361</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>96</v>
@@ -11542,34 +11669,34 @@
         <v>359</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E100" s="13">
-        <v>350</v>
+        <v>95</v>
       </c>
       <c r="F100" s="13">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="G100" s="13">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="H100" s="13">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="I100" s="13">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="J100" s="14" t="s">
-        <v>1164</v>
+        <v>362</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="L100" s="14" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="M100" s="14" t="s">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="N100" s="12" cm="1">
         <f t="array" ref="N100">_xlfn.IFS(B100="Freshwater",1,B100="Brackish",2,B100="Seawater",3)</f>
@@ -11581,52 +11708,52 @@
       </c>
       <c r="P100" s="12" cm="1">
         <f t="array" ref="P100">_xlfn.IFS(D100="Common",1,D100="Uncommon",2,D100="Rare",3,D100="Legendary",4,D100="Mythical",5,D100="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q100" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Longfin Tuna',36,2,350,15,40,90,150,'The longfin tuna has a streamlined, fusiform body with a conical snout, a large mouth, and big eyes. Its body is dark blue above, shades of silvery white ventrally, and covered by small scales.'),</v>
+        <f>_xlfn.CONCAT("('",A100,"',",O100,",",P100,",",E100,",",F100,",",G100,",",H100,",",I100,",","'",J100,"'),")</f>
+        <v>('Yellowfin Tuna',36,3,95,90,450,120,240,'Their body shape is particularly adapted for speed, enabling them to pursue and capture fast-moving baitfish, such as flying fish, sauries, and mackerel.'),</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A101" s="12" t="s">
-        <v>408</v>
+        <v>190</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>96</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>359</v>
+        <v>33</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E101" s="13">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>410</v>
+        <v>191</v>
       </c>
       <c r="G101" s="13">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="H101" s="13">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="I101" s="13">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="J101" s="14" t="s">
-        <v>412</v>
+        <v>192</v>
       </c>
       <c r="K101" s="14" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="L101" s="14" t="s">
-        <v>411</v>
+        <v>243</v>
       </c>
       <c r="M101" s="14" t="s">
-        <v>579</v>
+        <v>95</v>
       </c>
       <c r="N101" s="12" cm="1">
         <f t="array" ref="N101">_xlfn.IFS(B101="Freshwater",1,B101="Brackish",2,B101="Seawater",3)</f>
@@ -11634,15 +11761,15 @@
       </c>
       <c r="O101" s="12" cm="1">
         <f t="array" ref="O101">_xlfn.XLOOKUP(1,('Fish Type'!B:B=B101)*('Fish Type'!C:C=C101),'Fish Type'!A:A)</f>
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="P101" s="12" cm="1">
         <f t="array" ref="P101">_xlfn.IFS(D101="Common",1,D101="Uncommon",2,D101="Rare",3,D101="Legendary",4,D101="Mythical",5,D101="Event",6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q101" s="5" t="str">
-        <f t="shared" si="1"/>
-        <v>('Bigeye Tuna',36,2,275,25.5,180,75,250,'The eyes of bigeye tuna are well developed and with a large spherical lens allowing their vision to function well in low light conditions.'),</v>
+        <f>_xlfn.CONCAT("('",A101,"',",O101,",",P101,",",E101,",",F101,",",G101,",",H101,",",I101,",","'",J101,"'),")</f>
+        <v>('Zebra Seabream',6,3,150,1.25,3,25,55,'This fish has an oval shaped body which is deep and compressed with a moderately sharp snout and a thick lipped slightly protrusible mouth.'),</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.3">
@@ -11654,9 +11781,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M102" xr:uid="{D72DDB04-9343-4C49-91F5-9D2C45772DD9}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M102">
-    <sortCondition ref="B2:B102"/>
-    <sortCondition ref="C2:C102"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q103">
+    <sortCondition ref="A2:A103"/>
+    <sortCondition ref="C2:C103"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11710,8 +11837,8 @@
         <f>_xlfn.CONCAT("('",C2,"',",D2,"),")</f>
         <v>('Anemone',3),</v>
       </c>
-      <c r="J2" s="30"/>
-      <c r="K2" s="31"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="30"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="27">
@@ -11731,8 +11858,8 @@
         <f t="shared" ref="E3:E37" si="0">_xlfn.CONCAT("('",C3,"',",D3,"),")</f>
         <v>('Archer',2),</v>
       </c>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="27">
@@ -11752,8 +11879,8 @@
         <f t="shared" si="0"/>
         <v>('Barracuda',3),</v>
       </c>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
@@ -11773,8 +11900,8 @@
         <f t="shared" si="0"/>
         <v>('Bass',3),</v>
       </c>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="27">
@@ -11794,8 +11921,8 @@
         <f t="shared" si="0"/>
         <v>('Billfish',3),</v>
       </c>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
@@ -11815,8 +11942,8 @@
         <f t="shared" si="0"/>
         <v>('Bream',2),</v>
       </c>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
@@ -11836,8 +11963,8 @@
         <f t="shared" si="0"/>
         <v>('Bream',1),</v>
       </c>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="27">
@@ -11857,8 +11984,8 @@
         <f t="shared" si="0"/>
         <v>('Bream',3),</v>
       </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
@@ -11878,8 +12005,8 @@
         <f t="shared" si="0"/>
         <v>('Carp',1),</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="27">
@@ -11899,8 +12026,8 @@
         <f t="shared" si="0"/>
         <v>('Catfish',2),</v>
       </c>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
@@ -11920,8 +12047,8 @@
         <f t="shared" si="0"/>
         <v>('Catfish',1),</v>
       </c>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="27">
@@ -11941,8 +12068,8 @@
         <f t="shared" si="0"/>
         <v>('Catfish',3),</v>
       </c>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
@@ -11962,8 +12089,8 @@
         <f t="shared" si="0"/>
         <v>('Cichlid',2),</v>
       </c>
-      <c r="J14" s="30"/>
-      <c r="K14" s="30"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="27">
@@ -11983,8 +12110,8 @@
         <f t="shared" si="0"/>
         <v>('Dolphinfish',3),</v>
       </c>
-      <c r="J15" s="30"/>
-      <c r="K15" s="30"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
@@ -12004,8 +12131,8 @@
         <f t="shared" si="0"/>
         <v>('Filefish',3),</v>
       </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="27">
@@ -12025,8 +12152,8 @@
         <f t="shared" si="0"/>
         <v>('Flatfish',2),</v>
       </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="27">
@@ -12046,8 +12173,8 @@
         <f t="shared" si="0"/>
         <v>('Flatfish',3),</v>
       </c>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="27">
@@ -12067,8 +12194,8 @@
         <f t="shared" si="0"/>
         <v>('Four Eyed',2),</v>
       </c>
-      <c r="J19" s="30"/>
-      <c r="K19" s="30"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="27">
@@ -12088,8 +12215,8 @@
         <f t="shared" si="0"/>
         <v>('Gar',1),</v>
       </c>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="27">
@@ -12109,8 +12236,8 @@
         <f t="shared" si="0"/>
         <v>('Goby',2),</v>
       </c>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="27">
@@ -12130,8 +12257,8 @@
         <f t="shared" si="0"/>
         <v>('Grouper',3),</v>
       </c>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="27">
@@ -12151,8 +12278,8 @@
         <f t="shared" si="0"/>
         <v>('Halfbeak',2),</v>
       </c>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="27">
@@ -12172,8 +12299,8 @@
         <f t="shared" si="0"/>
         <v>('Mackerel',3),</v>
       </c>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="27">
@@ -12193,8 +12320,8 @@
         <f t="shared" si="0"/>
         <v>('Milkfish',2),</v>
       </c>
-      <c r="J25" s="30"/>
-      <c r="K25" s="30"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="27">
@@ -12214,8 +12341,8 @@
         <f t="shared" si="0"/>
         <v>('Moony',2),</v>
       </c>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="27">
@@ -12235,8 +12362,8 @@
         <f t="shared" si="0"/>
         <v>('Mullet',2),</v>
       </c>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="27">
@@ -12256,8 +12383,8 @@
         <f t="shared" si="0"/>
         <v>('Needlefish',2),</v>
       </c>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="27">
@@ -12277,8 +12404,8 @@
         <f t="shared" si="0"/>
         <v>('Perch',1),</v>
       </c>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="27">
@@ -12298,8 +12425,8 @@
         <f t="shared" si="0"/>
         <v>('Pike',1),</v>
       </c>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="3"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="27">
@@ -12319,8 +12446,8 @@
         <f t="shared" si="0"/>
         <v>('Scorpionfish',3),</v>
       </c>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="27">
@@ -12340,8 +12467,8 @@
         <f t="shared" si="0"/>
         <v>('Shark',3),</v>
       </c>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="27">
@@ -12361,8 +12488,8 @@
         <f t="shared" si="0"/>
         <v>('Snapper',2),</v>
       </c>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="27">
@@ -12382,8 +12509,8 @@
         <f t="shared" si="0"/>
         <v>('Snapper',3),</v>
       </c>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="27">
@@ -12403,8 +12530,8 @@
         <f t="shared" si="0"/>
         <v>('Sunfish',1),</v>
       </c>
-      <c r="J35" s="30"/>
-      <c r="K35" s="30"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="27">
@@ -12424,8 +12551,8 @@
         <f t="shared" si="0"/>
         <v>('Trout',1),</v>
       </c>
-      <c r="J36" s="30"/>
-      <c r="K36" s="30"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="27">
@@ -12445,8 +12572,8 @@
         <f t="shared" si="0"/>
         <v>('Tuna',3),</v>
       </c>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J2:K101">
@@ -19318,7 +19445,7 @@
     <col min="2" max="2" width="14.33203125" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.6640625" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="9" hidden="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="9"/>
   </cols>
   <sheetData>
@@ -20022,7 +20149,7 @@
         <v>38</v>
       </c>
       <c r="D2" s="6" cm="1">
-        <f t="array" ref="D2">SUMPRODUCT(--ISNUMBER(SEARCH("1",Bait!C2:C100)))</f>
+        <f t="array" ref="D2">SUMPRODUCT(--ISNUMBER(SEARCH("1",Bait!D2:D100)))</f>
         <v>33</v>
       </c>
       <c r="F2" s="6" t="s">
@@ -20049,7 +20176,7 @@
         <v>309</v>
       </c>
       <c r="N2" s="6">
-        <f>COUNTA(Bait!A:A)-1</f>
+        <f>COUNTA(Bait!B:B)-1</f>
         <v>43</v>
       </c>
     </row>
@@ -20064,7 +20191,7 @@
         <v>181</v>
       </c>
       <c r="D3" s="6" cm="1">
-        <f t="array" ref="D3">SUMPRODUCT(--ISNUMBER(SEARCH("2",Bait!C2:C100)))</f>
+        <f t="array" ref="D3">SUMPRODUCT(--ISNUMBER(SEARCH("2",Bait!D2:D100)))</f>
         <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
@@ -20106,7 +20233,7 @@
         <v>96</v>
       </c>
       <c r="D4" s="6" cm="1">
-        <f t="array" ref="D4">SUMPRODUCT(--ISNUMBER(SEARCH("3",Bait!C2:C100)))</f>
+        <f t="array" ref="D4">SUMPRODUCT(--ISNUMBER(SEARCH("3",Bait!D2:D100)))</f>
         <v>16</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -20395,14 +20522,14 @@
       </c>
       <c r="G12" s="6" t="str">
         <f>_xlfn.XLOOKUP(H12,Fish!C:C,Fish!B:B,"")</f>
-        <v>Brackish</v>
+        <v>Freshwater</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>220</v>
       </c>
       <c r="I12" s="6">
         <f>COUNTIFS(Fish!C:C,H12,Fish!B:B,G12)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
